--- a/data/history_sounds.xlsx
+++ b/data/history_sounds.xlsx
@@ -168,7 +168,7 @@
     <t>«Дорогая моя столица» («Моя Москва»)</t>
   </si>
   <si>
-    <t>советская песня о Москве времён Великой Отечественной войны, произведение родилось как отклик на тяжелые дни обороны города. Песня стала настоящим символом мужества, олицетворяющим стойкость, гордость и любовь к столице. С 14 июля 1995 года — официальный гимн Москвы.</t>
+    <t>Советская песня о Москве времён Великой Отечественной войны, произведение родилось как отклик на тяжелые дни обороны города. Песня стала настоящим символом мужества, олицетворяющим стойкость, гордость и любовь к столице. С 14 июля 1995 года — официальный гимн Москвы.</t>
   </si>
   <si>
     <t>https://vk.com/audio40956111_274786834_666be1720632ba0bc6</t>
@@ -234,7 +234,7 @@
     <t xml:space="preserve">Авиамарш </t>
   </si>
   <si>
-    <t>советская песня (в жанре марша), автор музыки Ю. А. Хайт, автор текста П. Д. Герман. Песня впервые опубликована весной 1923 года. Дата создания музыки неизвестна, сам Хайт утверждал, что написал мелодию в 1920 году. С 1933 года являлась официальным гимном Военно-воздушных сил СССР (Приказ РВС СССР от 7 августа).</t>
+    <t>Советская песня (в жанре марша), автор музыки Ю. А. Хайт, автор текста П. Д. Герман. Песня впервые опубликована весной 1923 года. Дата создания музыки неизвестна, сам Хайт утверждал, что написал мелодию в 1920 году. С 1933 года являлась официальным гимном Военно-воздушных сил СССР (Приказ РВС СССР от 7 августа).</t>
   </si>
   <si>
     <t>https://vk.com/audio2000062321_456245045</t>
@@ -321,8 +321,7 @@
     <t>1960-е</t>
   </si>
   <si>
-    <t>Марш, написанный советским композитором Матвеем Блантером в 1938 году. Традиционно звучал на футбольных матчах в СССР. Ныне звучит на матчах первого, второго и третьего дивизионов чемпионата России, а также некоторых других футбольных турниров на территории бывшего СССР. Также иногда звучит на товарищеских и еврокубковых встречах с участием команд из бывшего СССР.
-Написан Блантером по просьбе известного спортивного радиокомментатора Вадима Синявского. Первыми мелодию услышали композитор Дмитрий Шостакович и его сын Максим, будущий пианист и дирижёр.</t>
+    <t>Марш, написанный советским композитором Матвеем Блантером в 1938 году по просьбе известного спортивного радиокомментатора Вадима Синявского. Традиционно звучал на футбольных матчах в СССР. Ныне звучит на матчах первого, второго и третьего дивизионов чемпионата России, а также некоторых других футбольных турниров на территории бывшего СССР. Также иногда звучит на товарищеских и еврокубковых встречах с участием команд из бывшего СССР.</t>
   </si>
   <si>
     <t>https://vk.com/audio573270837_456239540_43de0f3c05da395548</t>
@@ -535,7 +534,7 @@
     <t>«Песня о Щорсе»</t>
   </si>
   <si>
-    <t xml:space="preserve">советская песня, посвящённая начальнику дивизии Красной армии времён Гражданской войны в России Николаю Щорсу. Текст был сочинен очевидцем Гражданоской войны на Украине Михаилом Голодным. </t>
+    <t xml:space="preserve">Советская песня, посвящённая начальнику дивизии Красной армии времён Гражданской войны в России Николаю Щорсу. Текст был сочинен очевидцем Гражданоской войны на Украине Михаилом Голодным. </t>
   </si>
   <si>
     <t>https://vk.com/audio371745454_456433084_7e0a73b9ac2bc62146</t>
@@ -556,7 +555,7 @@
     <t>«Там вдали, за рекой»</t>
   </si>
   <si>
-    <t xml:space="preserve">Популярная советская пенся, которая повествует о сражении отряда буденновских войск в ходе Гражданской войны. Она исполнялась в качестве строевой, поскольку новых красноармейских песен в то время было мало. </t>
+    <t xml:space="preserve">Популярная советская песня, которая повествует о сражении отряда буденновских войск в ходе Гражданской войны. Она исполнялась в качестве строевой, поскольку новых красноармейских песен в то время было мало. </t>
   </si>
   <si>
     <t>https://vk.com/audio339418809_456239129_5bcf59aa5529ace988</t>
@@ -803,7 +802,6 @@
   </si>
   <si>
     <t xml:space="preserve">Советский композитор, народный артист СССР (1985), автор популярных песен («Течёт Волга», «За того парня») и музыки к более чем 50 фильмам. Учился в Ленинградском театральном институте, в годы войны руководил фронтовыми ансамблями. 
-Википедия
 </t>
   </si>
   <si>
@@ -940,7 +938,7 @@
     <t>Высадка французских войск в Одессе началась 4 декабря 1918 года (по другим данным — 2 декабря 1918 года) в рамках интервенции Антанты на Юге России. Целью было поддержание порядка, борьба с большевизмом и помощь «белым» силам. Интервенты заняли город, сменив украинские войска, но уже весной 1919 года покинули его из-за неудач.</t>
   </si>
   <si>
-    <t>Отражение наступления восйк наступления войск Денкина на Москву</t>
+    <t>Отражение наступления войск наступления войск Денкина на Москву</t>
   </si>
   <si>
     <t>03.07.1919 г.</t>
@@ -1123,7 +1121,7 @@
     <t>12 апреля 1961 года советский летчик Юрий Гагарин совершил первый в истории человечества полет в космос. На корабле «Восток-1», стартовавшем с Байконура, он облетел Землю за 108 минут и успешно приземлился в Саратовской области. Этот подвиг открыл эру пилотируемых космических полетов.</t>
   </si>
   <si>
-    <t>Сборная СССР по футболу выигрывала олимпийское золото в Мельбруне</t>
+    <t>Сборная СССР по футболу выигрывала олимпийское золото в Мельбурне</t>
   </si>
   <si>
     <t>08.12.1956 г.</t>
@@ -1352,7 +1350,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1450,6 +1448,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5888,7 +5889,7 @@
       <c r="A9" s="29">
         <v>43.0</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="34" t="s">
         <v>306</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -6163,7 +6164,7 @@
       <c r="A26" s="29">
         <v>165.0</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="34" t="s">
         <v>367</v>
       </c>
       <c r="C26" s="30" t="s">

--- a/data/history_sounds.xlsx
+++ b/data/history_sounds.xlsx
@@ -1,14 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="132" yWindow="516" windowWidth="30396" windowHeight="15276"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="music" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="composers" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="events" sheetId="3" r:id="rId7"/>
+    <sheet name="music" sheetId="1" r:id="rId1"/>
+    <sheet name="composers" sheetId="2" r:id="rId2"/>
+    <sheet name="events" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -426,9 +429,6 @@
     <t>Илья Алексеевич Шатров</t>
   </si>
   <si>
-    <t>вальс «На сопках Маньчжурии»</t>
-  </si>
-  <si>
     <t>Русский вальс, посвященный погибшим в Русско-японской войне воинам 214-го резервного Мошканского пехотного полка. В феврале 1904 полк попал в японское окружение, в критический этап командир отдал приказ "Знамя и оркестр - вперед!". Капельмейстер под колонный марш повел оркестр вперед за знаменем полка. Воодушевленные солдаты ринулись в штыковую атаку. В ходе боя полк ценой огромных потерь прорвал окружение.</t>
   </si>
   <si>
@@ -1161,82 +1161,93 @@
   </si>
   <si>
     <t>XXII Летние Олимпийские игры проходили с 19 июля по 3 августа 1980 года в Москве, СССР. Это были первые Игры в Восточной Европе и социалистической стране. Несмотря на бойкот более 60 стран, в соревнованиях приняли участие атлеты из 80 государств. СССР занял первое место в общекомандном зачёте</t>
+  </si>
+  <si>
+    <t>Вальс «На сопках Маньчжурии»</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="d mmmm yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
-    <numFmt numFmtId="166" formatCode="d.m.yyyy"/>
+    <numFmt numFmtId="164" formatCode="d\ mmmm\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="166" formatCode="d\.m\.yyyy"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
@@ -1246,7 +1257,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1262,17 +1273,25 @@
     </fill>
   </fills>
   <borders count="8">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1287,17 +1306,20 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1312,6 +1334,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1320,9 +1343,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1334,8 +1359,11 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1345,131 +1373,78 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1477,7 +1452,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1667,25 +1642,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H152"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.86"/>
-    <col customWidth="1" min="2" max="2" width="33.86"/>
-    <col customWidth="1" min="3" max="3" width="42.29"/>
-    <col customWidth="1" min="4" max="4" width="24.0"/>
-    <col customWidth="1" min="5" max="5" width="74.0"/>
-    <col customWidth="1" min="8" max="8" width="58.14"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="74" customWidth="1"/>
+    <col min="8" max="8" width="58.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="13.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1711,9 +1689,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="13.8">
       <c r="A2" s="6">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -1722,24 +1700,24 @@
         <v>9</v>
       </c>
       <c r="D2" s="8">
-        <v>1925.0</v>
+        <v>1925</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="9">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="13.2">
       <c r="A3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>12</v>
@@ -1748,24 +1726,24 @@
         <v>13</v>
       </c>
       <c r="D3" s="6">
-        <v>1914.0</v>
+        <v>1914</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="9">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" ht="13.2">
       <c r="A4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>16</v>
@@ -1780,16 +1758,16 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" ht="13.2">
       <c r="A5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>16</v>
@@ -1798,24 +1776,24 @@
         <v>21</v>
       </c>
       <c r="D5" s="13">
-        <v>1915.0</v>
+        <v>1915</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="4">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="G5" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" ht="13.2">
       <c r="A6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>24</v>
@@ -1824,24 +1802,24 @@
         <v>25</v>
       </c>
       <c r="D6" s="6">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="G6" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" ht="13.2">
       <c r="A7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>28</v>
@@ -1850,24 +1828,24 @@
         <v>29</v>
       </c>
       <c r="D7" s="6">
-        <v>1965.0</v>
+        <v>1965</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="G7" s="9">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" ht="13.2">
       <c r="A8" s="6">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>32</v>
@@ -1876,24 +1854,24 @@
         <v>33</v>
       </c>
       <c r="D8" s="6">
-        <v>1940.0</v>
+        <v>1940</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G8" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" ht="13.2">
       <c r="A9" s="14">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
@@ -1902,24 +1880,24 @@
         <v>37</v>
       </c>
       <c r="D9" s="6">
-        <v>1929.0</v>
+        <v>1929</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G9" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" ht="13.2">
       <c r="A10" s="6">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>36</v>
@@ -1928,24 +1906,24 @@
         <v>40</v>
       </c>
       <c r="D10" s="6">
-        <v>1930.0</v>
+        <v>1930</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G10" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" ht="13.2">
       <c r="A11" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -1954,24 +1932,24 @@
         <v>43</v>
       </c>
       <c r="D11" s="15">
-        <v>15155.0</v>
+        <v>15155</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="4">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="G11" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" ht="13.2">
       <c r="A12" s="6">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>46</v>
@@ -1980,24 +1958,24 @@
         <v>47</v>
       </c>
       <c r="D12" s="6">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="4">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="G12" s="9">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" ht="13.2">
       <c r="A13" s="6">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>32</v>
@@ -2006,24 +1984,24 @@
         <v>50</v>
       </c>
       <c r="D13" s="16">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="4">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="G13" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" ht="13.2">
       <c r="A14" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>53</v>
@@ -2032,24 +2010,24 @@
         <v>54</v>
       </c>
       <c r="D14" s="6">
-        <v>1964.0</v>
+        <v>1964</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="4">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G14" s="9">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" ht="13.2">
       <c r="A15" s="6">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>57</v>
@@ -2058,24 +2036,24 @@
         <v>58</v>
       </c>
       <c r="D15" s="6">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="4">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="G15" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" ht="13.2">
       <c r="A16" s="6">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>61</v>
@@ -2084,24 +2062,24 @@
         <v>62</v>
       </c>
       <c r="D16" s="6">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="4">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G16" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" ht="13.2">
       <c r="A17" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>24</v>
@@ -2110,24 +2088,24 @@
         <v>65</v>
       </c>
       <c r="D17" s="6">
-        <v>1938.0</v>
+        <v>1938</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F17" s="4">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="G17" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" ht="13.2">
       <c r="A18" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>32</v>
@@ -2136,24 +2114,24 @@
         <v>68</v>
       </c>
       <c r="D18" s="6">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="4">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="G18" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" ht="13.2">
       <c r="A19" s="6">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>71</v>
@@ -2162,24 +2140,24 @@
         <v>72</v>
       </c>
       <c r="D19" s="17">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F19" s="4">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="G19" s="9">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" ht="13.2">
       <c r="A20" s="19">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>75</v>
@@ -2188,24 +2166,24 @@
         <v>76</v>
       </c>
       <c r="D20" s="6">
-        <v>1951.0</v>
+        <v>1951</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="F20" s="4">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="G20" s="9">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" ht="13.2">
       <c r="A21" s="19">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>79</v>
@@ -2214,24 +2192,24 @@
         <v>80</v>
       </c>
       <c r="D21" s="6">
-        <v>1953.0</v>
+        <v>1953</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="4">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="G21" s="9">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" ht="13.2">
       <c r="A22" s="19">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>57</v>
@@ -2240,24 +2218,24 @@
         <v>83</v>
       </c>
       <c r="D22" s="15">
-        <v>22555.0</v>
+        <v>22555</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="F22" s="4">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" ht="13.2">
       <c r="A23" s="19">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>86</v>
@@ -2266,24 +2244,24 @@
         <v>87</v>
       </c>
       <c r="D23" s="6">
-        <v>1983.0</v>
+        <v>1983</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>88</v>
       </c>
       <c r="F23" s="4">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="G23" s="9">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" ht="13.2">
       <c r="A24" s="19">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
@@ -2292,24 +2270,24 @@
         <v>90</v>
       </c>
       <c r="D24" s="6">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="4">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="G24" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" ht="13.2">
       <c r="A25" s="19">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>93</v>
@@ -2318,24 +2296,24 @@
         <v>94</v>
       </c>
       <c r="D25" s="6">
-        <v>1961.0</v>
+        <v>1961</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>95</v>
       </c>
       <c r="F25" s="4">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="G25" s="9">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" ht="13.2">
       <c r="A26" s="19">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>61</v>
@@ -2344,24 +2322,24 @@
         <v>97</v>
       </c>
       <c r="D26" s="6">
-        <v>1958.0</v>
+        <v>1958</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
       </c>
       <c r="F26" s="4">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="G26" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" ht="13.2">
       <c r="A27" s="19">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>79</v>
@@ -2376,18 +2354,18 @@
         <v>102</v>
       </c>
       <c r="F27" s="4">
-        <v>165.0</v>
+        <v>165</v>
       </c>
       <c r="G27" s="9">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" ht="13.2">
       <c r="A28" s="19">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
@@ -2396,24 +2374,24 @@
         <v>104</v>
       </c>
       <c r="D28" s="6">
-        <v>1979.0</v>
+        <v>1979</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
       </c>
       <c r="F28" s="4">
-        <v>165.0</v>
+        <v>165</v>
       </c>
       <c r="G28" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" ht="13.2">
       <c r="A29" s="19">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>107</v>
@@ -2422,24 +2400,24 @@
         <v>108</v>
       </c>
       <c r="D29" s="6">
-        <v>1960.0</v>
+        <v>1960</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>109</v>
       </c>
       <c r="F29" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G29" s="9">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" ht="13.2">
       <c r="A30" s="19">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>111</v>
@@ -2448,24 +2426,24 @@
         <v>112</v>
       </c>
       <c r="D30" s="6">
-        <v>1957.0</v>
+        <v>1957</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
       </c>
       <c r="F30" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G30" s="9">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" ht="13.2">
       <c r="A31" s="19">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>115</v>
@@ -2474,24 +2452,24 @@
         <v>116</v>
       </c>
       <c r="D31" s="6">
-        <v>1947.0</v>
+        <v>1947</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G31" s="9">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" ht="13.2">
       <c r="A32" s="19">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
@@ -2500,24 +2478,24 @@
         <v>120</v>
       </c>
       <c r="D32" s="6">
-        <v>1977.0</v>
+        <v>1977</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
       </c>
       <c r="F32" s="4">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="G32" s="9">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:8" ht="13.2">
       <c r="A33" s="19">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>61</v>
@@ -2526,46 +2504,46 @@
         <v>123</v>
       </c>
       <c r="D33" s="6">
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>124</v>
       </c>
       <c r="F33" s="4">
-        <v>221.0</v>
+        <v>221</v>
       </c>
       <c r="G33" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" ht="13.2">
       <c r="A34" s="19">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="6">
-        <v>1981.0</v>
+        <v>1981</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
       </c>
       <c r="F34" s="4">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" ht="13.2">
       <c r="A35" s="19">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>57</v>
@@ -2574,24 +2552,24 @@
         <v>129</v>
       </c>
       <c r="D35" s="6">
-        <v>1957.0</v>
+        <v>1957</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>130</v>
       </c>
       <c r="F35" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G35" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" ht="13.2">
       <c r="A36" s="19">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>132</v>
@@ -2600,632 +2578,632 @@
         <v>133</v>
       </c>
       <c r="D36" s="6">
-        <v>1981.0</v>
+        <v>1981</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="4">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G36" s="9">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" ht="13.2">
       <c r="A37" s="19">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1906</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="6">
-        <v>1906.0</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9">
+        <v>3</v>
+      </c>
+      <c r="H37" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="F37" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H37" s="11" t="s">
+    </row>
+    <row r="38" spans="1:8" ht="13.2">
+      <c r="A38" s="19">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19">
-        <v>40.0</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9">
+        <v>4</v>
+      </c>
+      <c r="H38" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F38" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="H38" s="11" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="13.2">
+      <c r="A39" s="19">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19">
-        <v>41.0</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>5</v>
+      </c>
+      <c r="H39" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D39" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H39" s="11" t="s">
+    </row>
+    <row r="40" spans="1:8" ht="13.2">
+      <c r="A40" s="19">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="19">
-        <v>42.0</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>6</v>
+      </c>
+      <c r="H40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F40" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>6.0</v>
-      </c>
-      <c r="H40" s="11" t="s">
+    </row>
+    <row r="41" spans="1:8" ht="13.2">
+      <c r="A41" s="19">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19">
-        <v>43.0</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="6">
+        <v>1912</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="6">
-        <v>1912.0</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>7</v>
+      </c>
+      <c r="H41" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F41" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>7.0</v>
-      </c>
-      <c r="H41" s="11" t="s">
+    </row>
+    <row r="42" spans="1:8" ht="13.2">
+      <c r="A42" s="19">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19">
-        <v>44.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H42" s="11" t="s">
+    </row>
+    <row r="43" spans="1:8" ht="13.2">
+      <c r="A43" s="19">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="D43" s="6">
+        <v>1905</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D43" s="6">
-        <v>1905.0</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:8" ht="13.2">
       <c r="A44" s="19">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1920</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D44" s="6">
-        <v>1920.0</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="F44" s="4">
+        <v>45</v>
+      </c>
+      <c r="G44" s="9">
+        <v>9</v>
+      </c>
+      <c r="H44" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F44" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="H44" s="11" t="s">
+    </row>
+    <row r="45" spans="1:8" ht="13.2">
+      <c r="A45" s="19">
+        <v>47</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19">
-        <v>47.0</v>
-      </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="6">
+        <v>1933</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="6">
-        <v>1933.0</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="F45" s="4">
+        <v>40</v>
+      </c>
+      <c r="G45" s="9">
+        <v>10</v>
+      </c>
+      <c r="H45" s="20"/>
+    </row>
+    <row r="46" spans="1:8" ht="13.2">
+      <c r="A46" s="19">
+        <v>48</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="G45" s="9">
-        <v>10.0</v>
-      </c>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="19">
-        <v>48.0</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6">
+        <v>1936</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D46" s="6">
-        <v>1936.0</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="4">
+        <v>46</v>
+      </c>
+      <c r="G46" s="9">
+        <v>11</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F46" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>11.0</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:8" ht="13.2">
       <c r="A47" s="19">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1935</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="6">
-        <v>1935.0</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="F47" s="4">
+        <v>45</v>
+      </c>
+      <c r="G47" s="9">
+        <v>8</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="G47" s="9">
-        <v>8.0</v>
-      </c>
-      <c r="H47" s="11" t="s">
+    </row>
+    <row r="48" spans="1:8" ht="13.2">
+      <c r="A48" s="19">
+        <v>50</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="19">
-        <v>50.0</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="6">
+        <v>1910</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D48" s="6">
-        <v>1910.0</v>
-      </c>
-      <c r="E48" s="6" t="s">
+      <c r="F48" s="4">
+        <v>5</v>
+      </c>
+      <c r="G48" s="4">
+        <v>12</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G48" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:8" ht="13.2">
       <c r="A49" s="19">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1924</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D49" s="6">
-        <v>1924.0</v>
-      </c>
-      <c r="E49" s="6" t="s">
+      <c r="F49" s="4">
+        <v>43</v>
+      </c>
+      <c r="G49" s="4">
+        <v>25</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F49" s="4">
-        <v>43.0</v>
-      </c>
-      <c r="G49" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="H49" s="11" t="s">
+    </row>
+    <row r="50" spans="1:8" ht="13.2">
+      <c r="A50" s="19">
+        <v>52</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19">
-        <v>52.0</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="D50" s="6">
+        <v>1917</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D50" s="6">
-        <v>1917.0</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="F50" s="4">
+        <v>21</v>
+      </c>
+      <c r="G50" s="9">
+        <v>14</v>
+      </c>
+      <c r="H50" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F50" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="G50" s="9">
-        <v>14.0</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:8" ht="13.2">
       <c r="A51" s="19">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="E51" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="H51" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="H51" s="11" t="s">
+    </row>
+    <row r="52" spans="1:8" ht="13.2">
+      <c r="A52" s="19">
+        <v>54</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19">
-        <v>54.0</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="6">
+        <v>1974</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D52" s="6">
-        <v>1974.0</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="4">
+        <v>107</v>
+      </c>
+      <c r="G52" s="9">
+        <v>16</v>
+      </c>
+      <c r="H52" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G52" s="9">
-        <v>16.0</v>
-      </c>
-      <c r="H52" s="11" t="s">
+    </row>
+    <row r="53" spans="1:8" ht="13.2">
+      <c r="A53" s="19">
+        <v>55</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19">
-        <v>55.0</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="D53" s="6">
+        <v>1975</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D53" s="6">
-        <v>1975.0</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="F53" s="4">
+        <v>107</v>
+      </c>
+      <c r="G53" s="9">
+        <v>17</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G53" s="9">
-        <v>17.0</v>
-      </c>
-      <c r="H53" s="11" t="s">
+    </row>
+    <row r="54" spans="1:8" ht="13.2">
+      <c r="A54" s="19">
+        <v>56</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19">
-        <v>56.0</v>
-      </c>
-      <c r="B54" s="6" t="s">
+      <c r="C54" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="D54" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D54" s="6">
-        <v>1971.0</v>
-      </c>
-      <c r="E54" s="6" t="s">
+      <c r="F54" s="4">
+        <v>107</v>
+      </c>
+      <c r="G54" s="9">
+        <v>15</v>
+      </c>
+      <c r="H54" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G54" s="9">
-        <v>15.0</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:8" ht="13.2">
       <c r="A55" s="19">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D55" s="22">
+        <v>1946</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D55" s="22">
-        <v>1946.0</v>
-      </c>
-      <c r="E55" s="6" t="s">
+      <c r="F55" s="4">
+        <v>107</v>
+      </c>
+      <c r="G55" s="9">
+        <v>8</v>
+      </c>
+      <c r="H55" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F55" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G55" s="9">
-        <v>8.0</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:8" ht="13.2">
       <c r="A56" s="19">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1947</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D56" s="6">
-        <v>1947.0</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="4">
+        <v>107</v>
+      </c>
+      <c r="G56" s="9">
+        <v>18</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F56" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>18.0</v>
-      </c>
-      <c r="H56" s="11" t="s">
+    </row>
+    <row r="57" spans="1:8" ht="13.2">
+      <c r="A57" s="19">
+        <v>59</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="19">
-        <v>59.0</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="C57" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>1974</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D57" s="6">
-        <v>1974.0</v>
-      </c>
-      <c r="E57" s="6" t="s">
+      <c r="F57" s="4">
+        <v>107</v>
+      </c>
+      <c r="G57" s="9">
+        <v>19</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F57" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="H57" s="11" t="s">
+    </row>
+    <row r="58" spans="1:8" ht="13.2">
+      <c r="A58" s="19">
+        <v>60</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="19">
-        <v>60.0</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="C58" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="D58" s="6">
+        <v>1975</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D58" s="6">
-        <v>1975.0</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="F58" s="4">
+        <v>107</v>
+      </c>
+      <c r="G58" s="9">
+        <v>20</v>
+      </c>
+      <c r="H58" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G58" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="H58" s="18" t="s">
+    </row>
+    <row r="59" spans="1:8" ht="13.2">
+      <c r="A59" s="19">
+        <v>61</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19">
-        <v>61.0</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="C59" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="6">
+        <v>1969</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D59" s="6">
-        <v>1969.0</v>
-      </c>
-      <c r="E59" s="6" t="s">
+      <c r="F59" s="4">
+        <v>107</v>
+      </c>
+      <c r="G59" s="9">
+        <v>21</v>
+      </c>
+      <c r="H59" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F59" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G59" s="9">
-        <v>21.0</v>
-      </c>
-      <c r="H59" s="11" t="s">
+    </row>
+    <row r="60" spans="1:8" ht="13.2">
+      <c r="A60" s="19">
+        <v>62</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="19">
-        <v>62.0</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="C60" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="6">
-        <v>1971.0</v>
-      </c>
-      <c r="E60" s="6" t="s">
+      <c r="F60" s="4">
+        <v>107</v>
+      </c>
+      <c r="G60" s="9">
+        <v>26</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="F60" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G60" s="9">
-        <v>26.0</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="61" ht="18.0" customHeight="1">
+    </row>
+    <row r="61" spans="1:8" ht="18" customHeight="1">
       <c r="A61" s="19">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -3233,9 +3211,9 @@
       <c r="E61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:8" ht="13.2">
       <c r="A62" s="19">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -3243,9 +3221,9 @@
       <c r="E62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:8" ht="13.2">
       <c r="A63" s="19">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -3253,9 +3231,9 @@
       <c r="E63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:8" ht="13.2">
       <c r="A64" s="19">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -3263,9 +3241,9 @@
       <c r="E64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:8" ht="13.2">
       <c r="A65" s="19">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -3273,9 +3251,9 @@
       <c r="E65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:8" ht="13.2">
       <c r="A66" s="19">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -3283,9 +3261,9 @@
       <c r="E66" s="20"/>
       <c r="H66" s="20"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:8" ht="13.2">
       <c r="A67" s="19">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -3293,9 +3271,9 @@
       <c r="E67" s="20"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:8" ht="13.2">
       <c r="A68" s="19">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -3303,9 +3281,9 @@
       <c r="E68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:8" ht="13.2">
       <c r="A69" s="19">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -3313,9 +3291,9 @@
       <c r="E69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:8" ht="13.2">
       <c r="A70" s="19">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -3323,9 +3301,9 @@
       <c r="E70" s="20"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:8" ht="13.2">
       <c r="A71" s="19">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -3333,9 +3311,9 @@
       <c r="E71" s="20"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:8" ht="13.2">
       <c r="A72" s="19">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -3343,9 +3321,9 @@
       <c r="E72" s="20"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:8" ht="13.2">
       <c r="A73" s="19">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -3353,9 +3331,9 @@
       <c r="E73" s="20"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:8" ht="13.2">
       <c r="A74" s="19">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -3363,9 +3341,9 @@
       <c r="E74" s="20"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:8" ht="13.2">
       <c r="A75" s="19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -3373,9 +3351,9 @@
       <c r="E75" s="20"/>
       <c r="H75" s="20"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:8" ht="13.2">
       <c r="A76" s="19">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -3383,9 +3361,9 @@
       <c r="E76" s="20"/>
       <c r="H76" s="20"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:8" ht="13.2">
       <c r="A77" s="19">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -3393,9 +3371,9 @@
       <c r="E77" s="20"/>
       <c r="H77" s="20"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:8" ht="13.2">
       <c r="A78" s="19">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -3403,9 +3381,9 @@
       <c r="E78" s="20"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:8" ht="13.2">
       <c r="A79" s="19">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -3413,9 +3391,9 @@
       <c r="E79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:8" ht="13.2">
       <c r="A80" s="19">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -3423,9 +3401,9 @@
       <c r="E80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:8" ht="13.2">
       <c r="A81" s="19">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -3433,9 +3411,9 @@
       <c r="E81" s="20"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:8" ht="13.2">
       <c r="A82" s="19">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
@@ -3443,9 +3421,9 @@
       <c r="E82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:8" ht="13.2">
       <c r="A83" s="19">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -3453,9 +3431,9 @@
       <c r="E83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:8" ht="13.2">
       <c r="A84" s="19">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -3463,9 +3441,9 @@
       <c r="E84" s="20"/>
       <c r="H84" s="20"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:8" ht="13.2">
       <c r="A85" s="19">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -3473,9 +3451,9 @@
       <c r="E85" s="20"/>
       <c r="H85" s="20"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:8" ht="13.2">
       <c r="A86" s="19">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -3483,9 +3461,9 @@
       <c r="E86" s="20"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:8" ht="13.2">
       <c r="A87" s="19">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -3493,9 +3471,9 @@
       <c r="E87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:8" ht="13.2">
       <c r="A88" s="19">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -3503,9 +3481,9 @@
       <c r="E88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:8" ht="13.2">
       <c r="A89" s="19">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -3513,9 +3491,9 @@
       <c r="E89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:8" ht="13.2">
       <c r="A90" s="19">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -3523,9 +3501,9 @@
       <c r="E90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:8" ht="13.2">
       <c r="A91" s="19">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -3533,9 +3511,9 @@
       <c r="E91" s="20"/>
       <c r="H91" s="20"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:8" ht="13.2">
       <c r="A92" s="19">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -3543,9 +3521,9 @@
       <c r="E92" s="20"/>
       <c r="H92" s="20"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:8" ht="13.2">
       <c r="A93" s="19">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -3553,9 +3531,9 @@
       <c r="E93" s="20"/>
       <c r="H93" s="20"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:8" ht="13.2">
       <c r="A94" s="19">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -3563,9 +3541,9 @@
       <c r="E94" s="20"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:8" ht="13.2">
       <c r="A95" s="19">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -3573,9 +3551,9 @@
       <c r="E95" s="20"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:8" ht="13.2">
       <c r="A96" s="19">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -3583,9 +3561,9 @@
       <c r="E96" s="20"/>
       <c r="H96" s="20"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:8" ht="13.2">
       <c r="A97" s="19">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -3593,9 +3571,9 @@
       <c r="E97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:8" ht="13.2">
       <c r="A98" s="19">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -3603,9 +3581,9 @@
       <c r="E98" s="20"/>
       <c r="H98" s="20"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:8" ht="13.2">
       <c r="A99" s="19">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -3613,9 +3591,9 @@
       <c r="E99" s="20"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:8" ht="13.2">
       <c r="A100" s="19">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -3623,9 +3601,9 @@
       <c r="E100" s="20"/>
       <c r="H100" s="20"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:8" ht="13.2">
       <c r="A101" s="19">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -3633,9 +3611,9 @@
       <c r="E101" s="20"/>
       <c r="H101" s="20"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:8" ht="13.2">
       <c r="A102" s="19">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -3643,9 +3621,9 @@
       <c r="E102" s="20"/>
       <c r="H102" s="20"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:8" ht="13.2">
       <c r="A103" s="19">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -3653,9 +3631,9 @@
       <c r="E103" s="20"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:8" ht="13.2">
       <c r="A104" s="19">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -3663,9 +3641,9 @@
       <c r="E104" s="20"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:8" ht="13.2">
       <c r="A105" s="19">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -3673,9 +3651,9 @@
       <c r="E105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:8" ht="13.2">
       <c r="A106" s="19">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -3683,9 +3661,9 @@
       <c r="E106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:8" ht="13.2">
       <c r="A107" s="19">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -3693,9 +3671,9 @@
       <c r="E107" s="20"/>
       <c r="H107" s="20"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:8" ht="13.2">
       <c r="A108" s="19">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -3703,9 +3681,9 @@
       <c r="E108" s="20"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:8" ht="13.2">
       <c r="A109" s="19">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -3713,9 +3691,9 @@
       <c r="E109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:8" ht="13.2">
       <c r="A110" s="19">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -3723,9 +3701,9 @@
       <c r="E110" s="20"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:8" ht="13.2">
       <c r="A111" s="19">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
@@ -3733,9 +3711,9 @@
       <c r="E111" s="20"/>
       <c r="H111" s="20"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:8" ht="13.2">
       <c r="A112" s="19">
-        <v>114.0</v>
+        <v>114</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
@@ -3743,9 +3721,9 @@
       <c r="E112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:8" ht="13.2">
       <c r="A113" s="19">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -3753,9 +3731,9 @@
       <c r="E113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:8" ht="13.2">
       <c r="A114" s="19">
-        <v>116.0</v>
+        <v>116</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -3763,9 +3741,9 @@
       <c r="E114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:8" ht="13.2">
       <c r="A115" s="19">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
@@ -3773,9 +3751,9 @@
       <c r="E115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:8" ht="13.2">
       <c r="A116" s="19">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -3783,9 +3761,9 @@
       <c r="E116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:8" ht="13.2">
       <c r="A117" s="19">
-        <v>119.0</v>
+        <v>119</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -3793,9 +3771,9 @@
       <c r="E117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:8" ht="13.2">
       <c r="A118" s="19">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -3803,9 +3781,9 @@
       <c r="E118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:8" ht="13.2">
       <c r="A119" s="19">
-        <v>121.0</v>
+        <v>121</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -3813,9 +3791,9 @@
       <c r="E119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:8" ht="13.2">
       <c r="A120" s="19">
-        <v>122.0</v>
+        <v>122</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -3823,9 +3801,9 @@
       <c r="E120" s="20"/>
       <c r="H120" s="20"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:8" ht="13.2">
       <c r="A121" s="19">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -3833,9 +3811,9 @@
       <c r="E121" s="20"/>
       <c r="H121" s="20"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:8" ht="13.2">
       <c r="A122" s="19">
-        <v>124.0</v>
+        <v>124</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -3843,9 +3821,9 @@
       <c r="E122" s="20"/>
       <c r="H122" s="20"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:8" ht="13.2">
       <c r="A123" s="19">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -3853,9 +3831,9 @@
       <c r="E123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:8" ht="13.2">
       <c r="A124" s="19">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -3863,9 +3841,9 @@
       <c r="E124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:8" ht="13.2">
       <c r="A125" s="19">
-        <v>127.0</v>
+        <v>127</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -3873,9 +3851,9 @@
       <c r="E125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:8" ht="13.2">
       <c r="A126" s="19">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -3883,9 +3861,9 @@
       <c r="E126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:8" ht="13.2">
       <c r="A127" s="19">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
@@ -3893,9 +3871,9 @@
       <c r="E127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:8" ht="13.2">
       <c r="A128" s="19">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
@@ -3903,9 +3881,9 @@
       <c r="E128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:8" ht="13.2">
       <c r="A129" s="19">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -3913,9 +3891,9 @@
       <c r="E129" s="20"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:8" ht="13.2">
       <c r="A130" s="19">
-        <v>132.0</v>
+        <v>132</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -3923,9 +3901,9 @@
       <c r="E130" s="20"/>
       <c r="H130" s="20"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:8" ht="13.2">
       <c r="A131" s="19">
-        <v>133.0</v>
+        <v>133</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -3933,9 +3911,9 @@
       <c r="E131" s="20"/>
       <c r="H131" s="20"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:8" ht="13.2">
       <c r="A132" s="19">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -3943,9 +3921,9 @@
       <c r="E132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:8" ht="13.2">
       <c r="A133" s="19">
-        <v>135.0</v>
+        <v>135</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -3953,9 +3931,9 @@
       <c r="E133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:8" ht="13.2">
       <c r="A134" s="19">
-        <v>136.0</v>
+        <v>136</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -3963,9 +3941,9 @@
       <c r="E134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:8" ht="13.2">
       <c r="A135" s="19">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -3973,9 +3951,9 @@
       <c r="E135" s="20"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:8" ht="13.2">
       <c r="A136" s="19">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -3983,9 +3961,9 @@
       <c r="E136" s="20"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:8" ht="13.2">
       <c r="A137" s="19">
-        <v>139.0</v>
+        <v>139</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -3993,9 +3971,9 @@
       <c r="E137" s="20"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:8" ht="13.2">
       <c r="A138" s="19">
-        <v>140.0</v>
+        <v>140</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -4003,9 +3981,9 @@
       <c r="E138" s="20"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:8" ht="13.2">
       <c r="A139" s="19">
-        <v>141.0</v>
+        <v>141</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -4013,9 +3991,9 @@
       <c r="E139" s="20"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:8" ht="13.2">
       <c r="A140" s="19">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -4023,9 +4001,9 @@
       <c r="E140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:8" ht="13.2">
       <c r="A141" s="19">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -4033,9 +4011,9 @@
       <c r="E141" s="20"/>
       <c r="H141" s="20"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:8" ht="13.2">
       <c r="A142" s="19">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -4043,9 +4021,9 @@
       <c r="E142" s="20"/>
       <c r="H142" s="20"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:8" ht="13.2">
       <c r="A143" s="19">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -4053,9 +4031,9 @@
       <c r="E143" s="20"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:8" ht="13.2">
       <c r="A144" s="19">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -4063,9 +4041,9 @@
       <c r="E144" s="20"/>
       <c r="H144" s="20"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:8" ht="13.2">
       <c r="A145" s="19">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -4073,9 +4051,9 @@
       <c r="E145" s="20"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:8" ht="13.2">
       <c r="A146" s="19">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -4083,9 +4061,9 @@
       <c r="E146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:8" ht="13.2">
       <c r="A147" s="19">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -4093,9 +4071,9 @@
       <c r="E147" s="20"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:8" ht="13.2">
       <c r="A148" s="19">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -4103,9 +4081,9 @@
       <c r="E148" s="20"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:8" ht="13.2">
       <c r="A149" s="19">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -4113,9 +4091,9 @@
       <c r="E149" s="20"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:8" ht="13.2">
       <c r="A150" s="19">
-        <v>152.0</v>
+        <v>152</v>
       </c>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -4123,9 +4101,9 @@
       <c r="E150" s="20"/>
       <c r="H150" s="20"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" ht="13.2">
       <c r="A151" s="19">
-        <v>153.0</v>
+        <v>153</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -4133,9 +4111,9 @@
       <c r="E151" s="20"/>
       <c r="H151" s="20"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:8" ht="13.2">
       <c r="A152" s="19">
-        <v>154.0</v>
+        <v>154</v>
       </c>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -4145,261 +4123,262 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="H3"/>
-    <hyperlink r:id="rId3" ref="H4"/>
-    <hyperlink r:id="rId4" ref="H5"/>
-    <hyperlink r:id="rId5" ref="H6"/>
-    <hyperlink r:id="rId6" ref="H7"/>
-    <hyperlink r:id="rId7" ref="H8"/>
-    <hyperlink r:id="rId8" ref="H9"/>
-    <hyperlink r:id="rId9" ref="H10"/>
-    <hyperlink r:id="rId10" ref="H11"/>
-    <hyperlink r:id="rId11" ref="H12"/>
-    <hyperlink r:id="rId12" ref="H13"/>
-    <hyperlink r:id="rId13" ref="H14"/>
-    <hyperlink r:id="rId14" ref="H15"/>
-    <hyperlink r:id="rId15" ref="H16"/>
-    <hyperlink r:id="rId16" ref="H17"/>
-    <hyperlink r:id="rId17" ref="H18"/>
-    <hyperlink r:id="rId18" ref="H19"/>
-    <hyperlink r:id="rId19" ref="H20"/>
-    <hyperlink r:id="rId20" ref="H21"/>
-    <hyperlink r:id="rId21" ref="H22"/>
-    <hyperlink r:id="rId22" ref="H23"/>
-    <hyperlink r:id="rId23" ref="H24"/>
-    <hyperlink r:id="rId24" ref="H25"/>
-    <hyperlink r:id="rId25" ref="H26"/>
-    <hyperlink r:id="rId26" ref="H27"/>
-    <hyperlink r:id="rId27" ref="H28"/>
-    <hyperlink r:id="rId28" ref="H29"/>
-    <hyperlink r:id="rId29" ref="H30"/>
-    <hyperlink r:id="rId30" ref="H31"/>
-    <hyperlink r:id="rId31" ref="H32"/>
-    <hyperlink r:id="rId32" ref="H33"/>
-    <hyperlink r:id="rId33" ref="H34"/>
-    <hyperlink r:id="rId34" ref="H35"/>
-    <hyperlink r:id="rId35" ref="H36"/>
-    <hyperlink r:id="rId36" ref="H37"/>
-    <hyperlink r:id="rId37" ref="H38"/>
-    <hyperlink r:id="rId38" ref="H39"/>
-    <hyperlink r:id="rId39" ref="H40"/>
-    <hyperlink r:id="rId40" ref="H41"/>
-    <hyperlink r:id="rId41" ref="H42"/>
-    <hyperlink r:id="rId42" ref="H43"/>
-    <hyperlink r:id="rId43" ref="H44"/>
-    <hyperlink r:id="rId44" ref="H46"/>
-    <hyperlink r:id="rId45" ref="H47"/>
-    <hyperlink r:id="rId46" ref="H48"/>
-    <hyperlink r:id="rId47" ref="H49"/>
-    <hyperlink r:id="rId48" ref="H50"/>
-    <hyperlink r:id="rId49" ref="H51"/>
-    <hyperlink r:id="rId50" ref="H52"/>
-    <hyperlink r:id="rId51" ref="H53"/>
-    <hyperlink r:id="rId52" ref="H54"/>
-    <hyperlink r:id="rId53" ref="H55"/>
-    <hyperlink r:id="rId54" ref="H56"/>
-    <hyperlink r:id="rId55" ref="H57"/>
-    <hyperlink r:id="rId56" ref="H58"/>
-    <hyperlink r:id="rId57" ref="H59"/>
-    <hyperlink r:id="rId58" ref="H60"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H46" r:id="rId44"/>
+    <hyperlink ref="H47" r:id="rId45"/>
+    <hyperlink ref="H48" r:id="rId46"/>
+    <hyperlink ref="H49" r:id="rId47"/>
+    <hyperlink ref="H50" r:id="rId48"/>
+    <hyperlink ref="H51" r:id="rId49"/>
+    <hyperlink ref="H52" r:id="rId50"/>
+    <hyperlink ref="H53" r:id="rId51"/>
+    <hyperlink ref="H54" r:id="rId52"/>
+    <hyperlink ref="H55" r:id="rId53"/>
+    <hyperlink ref="H56" r:id="rId54"/>
+    <hyperlink ref="H57" r:id="rId55"/>
+    <hyperlink ref="H58" r:id="rId56"/>
+    <hyperlink ref="H59" r:id="rId57"/>
+    <hyperlink ref="H60" r:id="rId58"/>
   </hyperlinks>
-  <drawing r:id="rId59"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="33.86"/>
-    <col customWidth="1" min="5" max="5" width="16.43"/>
+    <col min="2" max="2" width="33.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="13.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="F1" s="16"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="13.2">
       <c r="A2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>music!B2</f>
         <v>Николай Яковлевич Мясковский</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="23">
+        <v>18452</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="23">
-        <v>18452.0</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:6" ht="13.2">
       <c r="A3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="20" t="str">
         <f>music!B22</f>
         <v>Дмитрий Дмитриевич Шостакович</v>
       </c>
       <c r="C3" s="24">
-        <v>2447.0</v>
+        <v>2447</v>
       </c>
       <c r="D3" s="24">
-        <v>27615.0</v>
+        <v>27615</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="13.2">
       <c r="A4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="20" t="str">
         <f>music!B37</f>
         <v>Илья Алексеевич Шатров</v>
       </c>
       <c r="C4" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="24">
+        <v>19116</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="24">
-        <v>19116.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="13.2">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="25">
+        <v>11290</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D5" s="25">
-        <v>11290.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:6" ht="13.2">
       <c r="A6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="20" t="str">
         <f>music!B39</f>
         <v>Алексей Сергеевич Турищев</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" s="24">
+        <v>22693</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="D6" s="24">
-        <v>22693.0</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:6" ht="13.2">
       <c r="A7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="20" t="str">
         <f>music!B40</f>
         <v>Владимир Германович Богораз</v>
       </c>
       <c r="C7" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="24">
+        <v>13280</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="24">
-        <v>13280.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:6" ht="13.2">
       <c r="A8" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="20" t="str">
         <f>music!B41</f>
         <v>Василий Иванович Агапкин</v>
       </c>
       <c r="C8" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="25">
+        <v>23679</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="D8" s="25">
-        <v>23679.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:6" ht="13.2">
       <c r="A9" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="24">
-        <v>1137.0</v>
+        <v>1137</v>
       </c>
       <c r="D9" s="24">
-        <v>33143.0</v>
+        <v>33143</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.2">
       <c r="A10" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="20" t="str">
         <f>music!B44</f>
-        <v>Самуил Яковлевич Покрасс </v>
+        <v xml:space="preserve">Самуил Яковлевич Покрасс </v>
       </c>
       <c r="C10" s="6">
-        <v>1897.0</v>
+        <v>1897</v>
       </c>
       <c r="D10" s="24">
-        <v>14411.0</v>
+        <v>14411</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.2">
       <c r="A11" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="20" t="str">
         <f>music!B45</f>
@@ -4409,1323 +4388,1323 @@
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="13.2">
       <c r="A12" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="20" t="str">
         <f>music!B46</f>
         <v>Виктор Аркадьевич Белый</v>
       </c>
       <c r="C12" s="24">
-        <v>1475.0</v>
+        <v>1475</v>
       </c>
       <c r="D12" s="24">
-        <v>30381.0</v>
+        <v>30381</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.2">
       <c r="A13" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="20" t="str">
         <f>music!B48</f>
         <v>Максимилиан Осеевич Штейнберг</v>
       </c>
       <c r="C13" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="24">
+        <v>17142</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="D13" s="24">
-        <v>17142.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:6" ht="13.2">
       <c r="A14" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B14" s="20" t="str">
         <f>music!B50</f>
         <v>Александр Николаевич Вертинский</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="24">
+        <v>20961</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="24">
-        <v>20961.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="13.2">
+      <c r="A15" s="6">
+        <v>15</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="24">
+        <v>10291</v>
+      </c>
+      <c r="D15" s="24">
+        <v>32687</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C15" s="24">
-        <v>10291.0</v>
-      </c>
-      <c r="D15" s="24">
-        <v>32687.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="13.2">
       <c r="A16" s="7">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B16" s="20" t="str">
         <f>music!B52</f>
         <v>Евгений Григорьевич Мартынов</v>
       </c>
       <c r="C16" s="24">
-        <v>17675.0</v>
+        <v>17675</v>
       </c>
       <c r="D16" s="24">
-        <v>33119.0</v>
+        <v>33119</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="13.2">
       <c r="A17" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B17" s="20" t="str">
         <f>music!B53</f>
         <v>Валентин Сергеевич Левашов</v>
       </c>
       <c r="C17" s="24">
-        <v>5684.0</v>
+        <v>5684</v>
       </c>
       <c r="D17" s="24">
-        <v>34582.0</v>
+        <v>34582</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="13.2">
       <c r="A18" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="24">
-        <v>2659.0</v>
+        <v>2659</v>
       </c>
       <c r="D18" s="24">
-        <v>29191.0</v>
+        <v>29191</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="13.2">
+      <c r="A19" s="7">
+        <v>19</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="24">
+        <v>14474</v>
+      </c>
+      <c r="D19" s="24">
+        <v>36188</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7">
-        <v>19.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="24">
-        <v>14474.0</v>
-      </c>
-      <c r="D19" s="24">
-        <v>36188.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="20">
+    <row r="20" spans="1:5" ht="13.2">
       <c r="A20" s="6">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C20" s="24">
-        <v>14812.0</v>
+        <v>14812</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="13.2">
+      <c r="A21" s="7">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="25">
+        <v>7631</v>
+      </c>
+      <c r="D21" s="24">
+        <v>32745</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="25">
-        <v>7631.0</v>
-      </c>
-      <c r="D21" s="24">
-        <v>32745.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="13.2">
       <c r="A22" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B22" s="20" t="str">
         <f>music!B3</f>
         <v>Анатолий Константинович Лядов</v>
       </c>
       <c r="C22" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" s="24">
+        <v>5310</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D22" s="24">
-        <v>5310.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:5" ht="13.2">
       <c r="A23" s="6">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="25">
-        <v>5829.0</v>
+        <v>5829</v>
       </c>
       <c r="D23" s="24">
-        <v>35801.0</v>
+        <v>35801</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="13.2">
       <c r="A24" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="24">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D24" s="24">
-        <v>20295.0</v>
+        <v>20295</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="13.2">
       <c r="A25" s="7">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="24">
+        <v>16991</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="24">
-        <v>16991.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:5" ht="13.2">
       <c r="A26" s="6">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B26" s="20" t="str">
         <f>music!B60</f>
         <v>Марк Григорьевич Фрадкин</v>
       </c>
       <c r="C26" s="24">
-        <v>5225.0</v>
+        <v>5225</v>
       </c>
       <c r="D26" s="24">
-        <v>32967.0</v>
+        <v>32967</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="13.2">
       <c r="A27" s="6">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B27" s="20" t="str">
         <f>music!B12</f>
         <v>Константин Яковлевич Листов</v>
       </c>
       <c r="C27" s="24">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="D27" s="24">
-        <v>30565.0</v>
+        <v>30565</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="13.2">
       <c r="A28" s="7">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="24">
-        <v>9133.0</v>
+        <v>9133</v>
       </c>
       <c r="D28" s="24">
-        <v>35311.0</v>
+        <v>35311</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="13.2">
       <c r="A29" s="6">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="24">
-        <v>10906.0</v>
+        <v>10906</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="13.2">
       <c r="A30" s="6">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" s="24">
+        <v>24447</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D30" s="24">
-        <v>24447.0</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:5" ht="13.2">
       <c r="A31" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="24">
-        <v>3006.0</v>
+        <v>3006</v>
       </c>
       <c r="D31" s="24">
-        <v>25794.0</v>
+        <v>25794</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="13.2">
       <c r="A32" s="6">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="24">
-        <v>16667.0</v>
+        <v>16667</v>
       </c>
       <c r="D32" s="24">
-        <v>35111.0</v>
+        <v>35111</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="33" ht="35.25" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="35.25" customHeight="1">
       <c r="A33" s="7">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="24">
-        <v>7720.0</v>
+        <v>7720</v>
       </c>
       <c r="D33" s="24">
-        <v>41308.0</v>
+        <v>41308</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="13.2">
       <c r="A34" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C34" s="24">
-        <v>4897.0</v>
+        <v>4897</v>
       </c>
       <c r="D34" s="24">
-        <v>39308.0</v>
+        <v>39308</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="13.2">
       <c r="A35" s="6">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C35" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="24">
+        <v>30949</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="24">
-        <v>30949.0</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:5" ht="13.2">
       <c r="A36" s="7">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C36" s="24">
-        <v>10857.0</v>
+        <v>10857</v>
       </c>
       <c r="D36" s="24">
-        <v>44641.0</v>
+        <v>44641</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="13.2">
       <c r="A37" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>132</v>
       </c>
       <c r="C37" s="24">
-        <v>18903.0</v>
+        <v>18903</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="13.2">
       <c r="A38" s="6">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="13.2">
       <c r="A39" s="6">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="13.2">
       <c r="A40" s="7">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="13.2">
       <c r="A41" s="6">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="13.2">
       <c r="A42" s="6">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="13.2">
       <c r="A43" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="13.2">
       <c r="A44" s="6">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="13.2">
       <c r="A45" s="7">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" ht="13.2">
       <c r="A46" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" ht="13.2">
       <c r="A47" s="6">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" ht="13.2">
       <c r="A48" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" ht="13.2">
       <c r="A49" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="13.2">
       <c r="A50" s="6">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" ht="13.2">
       <c r="A51" s="6">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="13.2">
       <c r="A52" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="13.2">
       <c r="A53" s="6">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="13.2">
       <c r="A54" s="6">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="13.2">
       <c r="A55" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
       <c r="E55" s="20"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="13.2">
       <c r="A56" s="6">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="13.2">
       <c r="A57" s="7">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" ht="13.2">
       <c r="A58" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" ht="13.2">
       <c r="A59" s="6">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="13.2">
       <c r="A60" s="7">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" ht="13.2">
       <c r="A61" s="7">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" ht="13.2">
       <c r="A62" s="6">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="13.2">
       <c r="A63" s="6">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="13.2">
       <c r="A64" s="7">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" ht="13.2">
       <c r="A65" s="6">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" ht="13.2">
       <c r="A66" s="6">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" ht="13.2">
       <c r="A67" s="7">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" ht="13.2">
       <c r="A68" s="6">
-        <v>68.0</v>
-      </c>
-      <c r="B68" s="20" t="str">
+        <v>68</v>
+      </c>
+      <c r="B68" s="20">
         <f>music!B104</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" ht="13.2">
       <c r="A69" s="7">
-        <v>69.0</v>
-      </c>
-      <c r="B69" s="20" t="str">
+        <v>69</v>
+      </c>
+      <c r="B69" s="20">
         <f>music!B105</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" ht="13.2">
       <c r="A70" s="7">
-        <v>70.0</v>
-      </c>
-      <c r="B70" s="20" t="str">
+        <v>70</v>
+      </c>
+      <c r="B70" s="20">
         <f>music!B106</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" ht="13.2">
       <c r="A71" s="6">
-        <v>71.0</v>
-      </c>
-      <c r="B71" s="20" t="str">
+        <v>71</v>
+      </c>
+      <c r="B71" s="20">
         <f>music!B107</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" ht="13.2">
       <c r="A72" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="B72" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="B72" s="20">
         <f>music!B108</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" ht="13.2">
       <c r="A73" s="7">
-        <v>73.0</v>
-      </c>
-      <c r="B73" s="20" t="str">
+        <v>73</v>
+      </c>
+      <c r="B73" s="20">
         <f>music!B109</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" ht="13.2">
       <c r="A74" s="6">
-        <v>74.0</v>
-      </c>
-      <c r="B74" s="20" t="str">
+        <v>74</v>
+      </c>
+      <c r="B74" s="20">
         <f>music!B110</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" ht="13.2">
       <c r="A75" s="6">
-        <v>75.0</v>
-      </c>
-      <c r="B75" s="20" t="str">
+        <v>75</v>
+      </c>
+      <c r="B75" s="20">
         <f>music!B111</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" ht="13.2">
       <c r="A76" s="7">
-        <v>76.0</v>
-      </c>
-      <c r="B76" s="20" t="str">
+        <v>76</v>
+      </c>
+      <c r="B76" s="20">
         <f>music!B112</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" ht="13.2">
       <c r="A77" s="6">
-        <v>77.0</v>
-      </c>
-      <c r="B77" s="20" t="str">
+        <v>77</v>
+      </c>
+      <c r="B77" s="20">
         <f>music!B113</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" ht="13.2">
       <c r="A78" s="6">
-        <v>78.0</v>
-      </c>
-      <c r="B78" s="20" t="str">
+        <v>78</v>
+      </c>
+      <c r="B78" s="20">
         <f>music!B114</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" ht="13.2">
       <c r="A79" s="7">
-        <v>79.0</v>
-      </c>
-      <c r="B79" s="20" t="str">
+        <v>79</v>
+      </c>
+      <c r="B79" s="20">
         <f>music!B115</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" ht="13.2">
       <c r="A80" s="6">
-        <v>80.0</v>
-      </c>
-      <c r="B80" s="20" t="str">
+        <v>80</v>
+      </c>
+      <c r="B80" s="20">
         <f>music!B116</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:5" ht="13.2">
       <c r="A81" s="7">
-        <v>81.0</v>
-      </c>
-      <c r="B81" s="20" t="str">
+        <v>81</v>
+      </c>
+      <c r="B81" s="20">
         <f>music!B117</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" ht="13.2">
       <c r="A82" s="7">
-        <v>82.0</v>
-      </c>
-      <c r="B82" s="20" t="str">
+        <v>82</v>
+      </c>
+      <c r="B82" s="20">
         <f>music!B118</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" ht="13.2">
       <c r="A83" s="6">
-        <v>83.0</v>
-      </c>
-      <c r="B83" s="20" t="str">
+        <v>83</v>
+      </c>
+      <c r="B83" s="20">
         <f>music!B119</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:5" ht="13.2">
       <c r="A84" s="7">
-        <v>84.0</v>
-      </c>
-      <c r="B84" s="20" t="str">
+        <v>84</v>
+      </c>
+      <c r="B84" s="20">
         <f>music!B120</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:5" ht="13.2">
       <c r="A85" s="7">
-        <v>85.0</v>
-      </c>
-      <c r="B85" s="20" t="str">
+        <v>85</v>
+      </c>
+      <c r="B85" s="20">
         <f>music!B121</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" ht="13.2">
       <c r="A86" s="6">
-        <v>86.0</v>
-      </c>
-      <c r="B86" s="20" t="str">
+        <v>86</v>
+      </c>
+      <c r="B86" s="20">
         <f>music!B122</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" ht="13.2">
       <c r="A87" s="6">
-        <v>87.0</v>
-      </c>
-      <c r="B87" s="20" t="str">
+        <v>87</v>
+      </c>
+      <c r="B87" s="20">
         <f>music!B123</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:5" ht="13.2">
       <c r="A88" s="7">
-        <v>88.0</v>
-      </c>
-      <c r="B88" s="20" t="str">
+        <v>88</v>
+      </c>
+      <c r="B88" s="20">
         <f>music!B124</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" ht="13.2">
       <c r="A89" s="6">
-        <v>89.0</v>
-      </c>
-      <c r="B89" s="20" t="str">
+        <v>89</v>
+      </c>
+      <c r="B89" s="20">
         <f>music!B125</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:5" ht="13.2">
       <c r="A90" s="6">
-        <v>90.0</v>
-      </c>
-      <c r="B90" s="20" t="str">
+        <v>90</v>
+      </c>
+      <c r="B90" s="20">
         <f>music!B126</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" ht="13.2">
       <c r="A91" s="7">
-        <v>91.0</v>
-      </c>
-      <c r="B91" s="20" t="str">
+        <v>91</v>
+      </c>
+      <c r="B91" s="20">
         <f>music!B127</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" ht="13.2">
       <c r="A92" s="6">
-        <v>92.0</v>
-      </c>
-      <c r="B92" s="20" t="str">
+        <v>92</v>
+      </c>
+      <c r="B92" s="20">
         <f>music!B128</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" ht="13.2">
       <c r="A93" s="7">
-        <v>93.0</v>
-      </c>
-      <c r="B93" s="20" t="str">
+        <v>93</v>
+      </c>
+      <c r="B93" s="20">
         <f>music!B129</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" ht="13.2">
       <c r="A94" s="7">
-        <v>94.0</v>
-      </c>
-      <c r="B94" s="20" t="str">
+        <v>94</v>
+      </c>
+      <c r="B94" s="20">
         <f>music!B130</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" ht="13.2">
       <c r="A95" s="6">
-        <v>95.0</v>
-      </c>
-      <c r="B95" s="20" t="str">
+        <v>95</v>
+      </c>
+      <c r="B95" s="20">
         <f>music!B131</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" ht="13.2">
       <c r="A96" s="7">
-        <v>96.0</v>
-      </c>
-      <c r="B96" s="20" t="str">
+        <v>96</v>
+      </c>
+      <c r="B96" s="20">
         <f>music!B132</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" ht="13.2">
       <c r="A97" s="7">
-        <v>97.0</v>
-      </c>
-      <c r="B97" s="20" t="str">
+        <v>97</v>
+      </c>
+      <c r="B97" s="20">
         <f>music!B133</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" ht="13.2">
       <c r="A98" s="6">
-        <v>98.0</v>
-      </c>
-      <c r="B98" s="20" t="str">
+        <v>98</v>
+      </c>
+      <c r="B98" s="20">
         <f>music!B134</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" ht="13.2">
       <c r="A99" s="6">
-        <v>99.0</v>
-      </c>
-      <c r="B99" s="20" t="str">
+        <v>99</v>
+      </c>
+      <c r="B99" s="20">
         <f>music!B135</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" ht="13.2">
       <c r="A100" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="B100" s="20" t="str">
+        <v>100</v>
+      </c>
+      <c r="B100" s="20">
         <f>music!B136</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" ht="13.2">
       <c r="A101" s="6">
-        <v>101.0</v>
-      </c>
-      <c r="B101" s="20" t="str">
+        <v>101</v>
+      </c>
+      <c r="B101" s="20">
         <f>music!B137</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" ht="13.2">
       <c r="A102" s="6">
-        <v>102.0</v>
-      </c>
-      <c r="B102" s="20" t="str">
+        <v>102</v>
+      </c>
+      <c r="B102" s="20">
         <f>music!B138</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" ht="13.2">
       <c r="A103" s="7">
-        <v>103.0</v>
-      </c>
-      <c r="B103" s="20" t="str">
+        <v>103</v>
+      </c>
+      <c r="B103" s="20">
         <f>music!B139</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" ht="13.2">
       <c r="A104" s="6">
-        <v>104.0</v>
-      </c>
-      <c r="B104" s="20" t="str">
+        <v>104</v>
+      </c>
+      <c r="B104" s="20">
         <f>music!B140</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" ht="13.2">
       <c r="A105" s="7">
-        <v>105.0</v>
-      </c>
-      <c r="B105" s="20" t="str">
+        <v>105</v>
+      </c>
+      <c r="B105" s="20">
         <f>music!B141</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" ht="13.2">
       <c r="A106" s="7">
-        <v>106.0</v>
-      </c>
-      <c r="B106" s="20" t="str">
+        <v>106</v>
+      </c>
+      <c r="B106" s="20">
         <f>music!B142</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:5" ht="13.2">
       <c r="A107" s="6">
-        <v>107.0</v>
-      </c>
-      <c r="B107" s="20" t="str">
+        <v>107</v>
+      </c>
+      <c r="B107" s="20">
         <f>music!B143</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C107" s="20"/>
       <c r="D107" s="20"/>
       <c r="E107" s="20"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:5" ht="13.2">
       <c r="A108" s="7">
-        <v>108.0</v>
-      </c>
-      <c r="B108" s="20" t="str">
+        <v>108</v>
+      </c>
+      <c r="B108" s="20">
         <f>music!B144</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" ht="13.2">
       <c r="A109" s="7">
-        <v>109.0</v>
-      </c>
-      <c r="B109" s="20" t="str">
+        <v>109</v>
+      </c>
+      <c r="B109" s="20">
         <f>music!B145</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C109" s="20"/>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" ht="13.2">
       <c r="A110" s="20"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:5" ht="13.2">
       <c r="A111" s="20"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
       <c r="D111" s="20"/>
       <c r="E111" s="20"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" ht="13.2">
       <c r="A112" s="20"/>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" ht="13.2">
       <c r="A113" s="20"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:5" ht="13.2">
       <c r="A114" s="20"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" ht="13.2">
       <c r="A115" s="20"/>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:5" ht="13.2">
       <c r="A116" s="20"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:5" ht="13.2">
       <c r="A117" s="20"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:5" ht="13.2">
       <c r="A118" s="20"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" ht="13.2">
       <c r="A119" s="20"/>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" ht="13.2">
       <c r="A120" s="20"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
       <c r="D120" s="20"/>
       <c r="E120" s="20"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:5" ht="13.2">
       <c r="A121" s="20"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
       <c r="D121" s="20"/>
       <c r="E121" s="20"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:5" ht="13.2">
       <c r="A122" s="20"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:5" ht="13.2">
       <c r="A123" s="20"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:5" ht="13.2">
       <c r="A124" s="20"/>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -5733,498 +5712,499 @@
       <c r="E124" s="20"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.43"/>
-    <col customWidth="1" min="2" max="2" width="46.14"/>
-    <col customWidth="1" min="3" max="3" width="20.14"/>
-    <col customWidth="1" min="4" max="4" width="23.86"/>
-    <col customWidth="1" min="5" max="5" width="56.57"/>
+    <col min="1" max="1" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="46.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="56.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="E1" s="27" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="29">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="C2" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="D2" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E2" s="32" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29">
+        <v>5</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="29">
-        <v>5.0</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="D3" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="E3" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="E3" s="32" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="29">
+        <v>9</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="D4" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="E4" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="E4" s="32" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="29">
+        <v>21</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="29">
-        <v>21.0</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="D5" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="E5" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="E5" s="33" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="29">
+        <v>37</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29">
-        <v>37.0</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="C6" s="30" t="s">
         <v>295</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>296</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="33" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="29">
+        <v>38</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="29">
-        <v>38.0</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="D7" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="E7" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="E7" s="33" t="s">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="29">
+        <v>40</v>
+      </c>
+      <c r="B8" s="29" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29">
-        <v>40.0</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="C8" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E8" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="E8" s="33" t="s">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="29">
+        <v>43</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="29">
-        <v>43.0</v>
-      </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="D9" s="31" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E9" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="E9" s="33" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="29">
+        <v>45</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29">
-        <v>45.0</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="E10" s="33" t="s">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="29">
+        <v>46</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29">
-        <v>46.0</v>
-      </c>
-      <c r="B11" s="29" t="s">
+      <c r="C11" s="30" t="s">
         <v>314</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>315</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="29">
+        <v>48</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29">
-        <v>48.0</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="C12" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="E12" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="E12" s="33" t="s">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="29">
+        <v>56</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29">
-        <v>56.0</v>
-      </c>
-      <c r="B13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>321</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>322</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="33" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="29">
+        <v>58</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29">
-        <v>58.0</v>
-      </c>
-      <c r="B14" s="29" t="s">
+      <c r="C14" s="30" t="s">
         <v>324</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>325</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="29">
+        <v>69</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29">
-        <v>69.0</v>
-      </c>
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="E15" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="E15" s="33" t="s">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="29">
+        <v>107</v>
+      </c>
+      <c r="B16" s="29" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29">
-        <v>107.0</v>
-      </c>
-      <c r="B16" s="29" t="s">
+      <c r="C16" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="E16" s="33" t="s">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="29">
+        <v>111</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="29">
-        <v>111.0</v>
-      </c>
-      <c r="B17" s="29" t="s">
+      <c r="C17" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="D17" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="E17" s="33" t="s">
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="29">
+        <v>112</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29">
-        <v>112.0</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>340</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="E18" s="33" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="29">
+        <v>120</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29">
-        <v>120.0</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="C19" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="D19" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>345</v>
       </c>
-      <c r="E19" s="33" t="s">
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="29">
+        <v>126</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29">
-        <v>126.0</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="E20" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="E20" s="33" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="29">
+        <v>134</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29">
-        <v>134.0</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="E21" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="E21" s="33" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="29">
+        <v>142</v>
+      </c>
+      <c r="B22" s="29" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29">
-        <v>142.0</v>
-      </c>
-      <c r="B22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>355</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>356</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="33" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="29">
+        <v>143</v>
+      </c>
+      <c r="B23" s="29" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29">
-        <v>143.0</v>
-      </c>
-      <c r="B23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>358</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>359</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="29">
+        <v>160</v>
+      </c>
+      <c r="B24" s="29" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29">
-        <v>160.0</v>
-      </c>
-      <c r="B24" s="29" t="s">
+      <c r="C24" s="30" t="s">
         <v>361</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>362</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="29">
+        <v>163</v>
+      </c>
+      <c r="B25" s="29" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="29">
-        <v>163.0</v>
-      </c>
-      <c r="B25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>364</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>365</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="33" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="29">
+        <v>165</v>
+      </c>
+      <c r="B26" s="34" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29">
-        <v>165.0</v>
-      </c>
-      <c r="B26" s="34" t="s">
+      <c r="C26" s="30" t="s">
         <v>367</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>368</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="33" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="29">
+        <v>167</v>
+      </c>
+      <c r="B27" s="29" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29">
-        <v>167.0</v>
-      </c>
-      <c r="B27" s="29" t="s">
+      <c r="C27" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="D27" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="E27" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="E27" s="33" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="29">
+        <v>192</v>
+      </c>
+      <c r="B28" s="29" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29">
-        <v>192.0</v>
-      </c>
-      <c r="B28" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>374</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>375</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="29">
+        <v>221</v>
+      </c>
+      <c r="B29" s="29" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="29">
-        <v>221.0</v>
-      </c>
-      <c r="B29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="D29" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="E29" s="33" t="s">
         <v>379</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>380</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/history_sounds.xlsx
+++ b/data/history_sounds.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="132" yWindow="516" windowWidth="30396" windowHeight="15276"/>
+    <workbookView xWindow="132" yWindow="516" windowWidth="30396" windowHeight="15276" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="music" sheetId="1" r:id="rId1"/>
@@ -938,9 +938,6 @@
     <t>Высадка французских войск в Одессе началась 4 декабря 1918 года (по другим данным — 2 декабря 1918 года) в рамках интервенции Антанты на Юге России. Целью было поддержание порядка, борьба с большевизмом и помощь «белым» силам. Интервенты заняли город, сменив украинские войска, но уже весной 1919 года покинули его из-за неудач.</t>
   </si>
   <si>
-    <t>Отражение наступления войск наступления войск Денкина на Москву</t>
-  </si>
-  <si>
     <t>03.07.1919 г.</t>
   </si>
   <si>
@@ -1164,6 +1161,9 @@
   </si>
   <si>
     <t>Вальс «На сопках Маньчжурии»</t>
+  </si>
+  <si>
+    <t>Отражение наступления войск Денкина на Москву</t>
   </si>
 </sst>
 </file>
@@ -2601,7 +2601,7 @@
         <v>136</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D37" s="6">
         <v>1906</v>
@@ -5870,16 +5870,16 @@
         <v>43</v>
       </c>
       <c r="B9" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="D9" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E9" s="33" t="s">
         <v>307</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5887,16 +5887,16 @@
         <v>45</v>
       </c>
       <c r="B10" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>311</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5904,14 +5904,14 @@
         <v>46</v>
       </c>
       <c r="B11" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>313</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>314</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5919,16 +5919,16 @@
         <v>48</v>
       </c>
       <c r="B12" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="E12" s="33" t="s">
         <v>318</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5936,14 +5936,14 @@
         <v>56</v>
       </c>
       <c r="B13" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>320</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>321</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5951,14 +5951,14 @@
         <v>58</v>
       </c>
       <c r="B14" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>323</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>324</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5966,16 +5966,16 @@
         <v>69</v>
       </c>
       <c r="B15" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="E15" s="33" t="s">
         <v>328</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5983,16 +5983,16 @@
         <v>107</v>
       </c>
       <c r="B16" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>332</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6000,16 +6000,16 @@
         <v>111</v>
       </c>
       <c r="B17" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="D17" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>336</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6017,16 +6017,16 @@
         <v>112</v>
       </c>
       <c r="B18" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>340</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6034,16 +6034,16 @@
         <v>120</v>
       </c>
       <c r="B19" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="D19" s="31" t="s">
         <v>343</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>344</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6051,16 +6051,16 @@
         <v>126</v>
       </c>
       <c r="B20" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="E20" s="33" t="s">
         <v>348</v>
-      </c>
-      <c r="E20" s="33" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6068,16 +6068,16 @@
         <v>134</v>
       </c>
       <c r="B21" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="E21" s="33" t="s">
         <v>352</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6085,14 +6085,14 @@
         <v>142</v>
       </c>
       <c r="B22" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>354</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>355</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="33" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6100,14 +6100,14 @@
         <v>143</v>
       </c>
       <c r="B23" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="30" t="s">
         <v>357</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>358</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6115,14 +6115,14 @@
         <v>160</v>
       </c>
       <c r="B24" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>360</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>361</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6130,14 +6130,14 @@
         <v>163</v>
       </c>
       <c r="B25" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="C25" s="30" t="s">
         <v>363</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>364</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6145,14 +6145,14 @@
         <v>165</v>
       </c>
       <c r="B26" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>366</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>367</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="33" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6160,16 +6160,16 @@
         <v>167</v>
       </c>
       <c r="B27" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="30" t="s">
         <v>369</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="D27" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="E27" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6177,14 +6177,14 @@
         <v>192</v>
       </c>
       <c r="B28" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="C28" s="30" t="s">
         <v>373</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>374</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6192,16 +6192,16 @@
         <v>221</v>
       </c>
       <c r="B29" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>376</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="D29" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="E29" s="33" t="s">
         <v>378</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/data/history_sounds.xlsx
+++ b/data/history_sounds.xlsx
@@ -1,22 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="132" yWindow="516" windowWidth="30396" windowHeight="15276" activeTab="2"/>
-  </bookViews>
   <sheets>
-    <sheet name="music" sheetId="1" r:id="rId1"/>
-    <sheet name="composers" sheetId="2" r:id="rId2"/>
-    <sheet name="events" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="music" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="composers" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="events" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="374">
   <si>
     <t>№</t>
   </si>
@@ -429,6 +426,9 @@
     <t>Илья Алексеевич Шатров</t>
   </si>
   <si>
+    <t>вальс «На сопках Маньчжурии»</t>
+  </si>
+  <si>
     <t>Русский вальс, посвященный погибшим в Русско-японской войне воинам 214-го резервного Мошканского пехотного полка. В феврале 1904 полк попал в японское окружение, в критический этап командир отдал приказ "Знамя и оркестр - вперед!". Капельмейстер под колонный марш повел оркестр вперед за знаменем полка. Воодушевленные солдаты ринулись в штыковую атаку. В ходе боя полк ценой огромных потерь прорвал окружение.</t>
   </si>
   <si>
@@ -508,15 +508,6 @@
   </si>
   <si>
     <t>https://vk.com/audio474499147_456535735_0a11ffd6c6a4b1ee1e</t>
-  </si>
-  <si>
-    <t>Томас Пефферман</t>
-  </si>
-  <si>
-    <t>Ночь и Холод</t>
-  </si>
-  <si>
-    <t>Песня о побежденной Западнорусской Добровольческой армии, которая сражалась против РСФСР вместе с Фрайкором (Железная дивизия) в Прибалтике в 1918—1919 годах. Западнорусская Добровольческая армия состояла из освобожденных русских военнопленных и была создана Германской империей до конца войны.</t>
   </si>
   <si>
     <t>Виктор Аркадьевич Белый</t>
@@ -926,16 +917,7 @@
     <t>Восстание Чехословацкого корпуса (май — август 1918 г.) — это вооруженное выступление чехословацких легионеров против советской власти в ходе Гражданской войны в России, ставшее катализатором массового антибольшевистского движения на востоке страны.</t>
   </si>
   <si>
-    <t>Высадка французских интервентов в Одессе</t>
-  </si>
-  <si>
-    <t>02.12.1918 г.</t>
-  </si>
-  <si>
-    <t>04.12.1918 г.</t>
-  </si>
-  <si>
-    <t>Высадка французских войск в Одессе началась 4 декабря 1918 года (по другим данным — 2 декабря 1918 года) в рамках интервенции Антанты на Юге России. Целью было поддержание порядка, борьба с большевизмом и помощь «белым» силам. Интервенты заняли город, сменив украинские войска, но уже весной 1919 года покинули его из-за неудач.</t>
+    <t>Отражение наступления войск наступления войск Денкина на Москву</t>
   </si>
   <si>
     <t>03.07.1919 г.</t>
@@ -1158,96 +1140,82 @@
   </si>
   <si>
     <t>XXII Летние Олимпийские игры проходили с 19 июля по 3 августа 1980 года в Москве, СССР. Это были первые Игры в Восточной Европе и социалистической стране. Несмотря на бойкот более 60 стран, в соревнованиях приняли участие атлеты из 80 государств. СССР занял первое место в общекомандном зачёте</t>
-  </si>
-  <si>
-    <t>Вальс «На сопках Маньчжурии»</t>
-  </si>
-  <si>
-    <t>Отражение наступления войск Денкина на Москву</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="d\ mmmm\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="166" formatCode="d\.m\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="166" formatCode="d.m.yyyy"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="16.0"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
@@ -1257,7 +1225,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1273,25 +1241,17 @@
     </fill>
   </fills>
   <borders count="8">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1306,20 +1266,17 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
-      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1334,7 +1291,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1343,11 +1299,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1359,11 +1313,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1373,78 +1324,131 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="35">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1452,7 +1456,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1642,28 +1646,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" customWidth="1"/>
-    <col min="2" max="2" width="33.88671875" customWidth="1"/>
-    <col min="3" max="3" width="42.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="74" customWidth="1"/>
-    <col min="8" max="8" width="58.109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="4.86"/>
+    <col customWidth="1" min="2" max="2" width="33.86"/>
+    <col customWidth="1" min="3" max="3" width="42.29"/>
+    <col customWidth="1" min="4" max="4" width="24.0"/>
+    <col customWidth="1" min="5" max="5" width="74.0"/>
+    <col customWidth="1" min="8" max="8" width="58.14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1689,9 +1690,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.8">
+    <row r="2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -1700,24 +1701,24 @@
         <v>9</v>
       </c>
       <c r="D2" s="8">
-        <v>1925</v>
+        <v>1925.0</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="G2" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.2">
+    <row r="3">
       <c r="A3" s="6">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>12</v>
@@ -1726,24 +1727,24 @@
         <v>13</v>
       </c>
       <c r="D3" s="6">
-        <v>1914</v>
+        <v>1914.0</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="G3" s="9">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.2">
+    <row r="4">
       <c r="A4" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>16</v>
@@ -1758,16 +1759,16 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.2">
+    <row r="5">
       <c r="A5" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>16</v>
@@ -1776,24 +1777,24 @@
         <v>21</v>
       </c>
       <c r="D5" s="13">
-        <v>1915</v>
+        <v>1915.0</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="4">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="G5" s="9">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.2">
+    <row r="6">
       <c r="A6" s="6">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>24</v>
@@ -1802,24 +1803,24 @@
         <v>25</v>
       </c>
       <c r="D6" s="6">
-        <v>1923</v>
+        <v>1923.0</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="4">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="G6" s="9">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.2">
+    <row r="7">
       <c r="A7" s="6">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>28</v>
@@ -1828,24 +1829,24 @@
         <v>29</v>
       </c>
       <c r="D7" s="6">
-        <v>1965</v>
+        <v>1965.0</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="G7" s="9">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.2">
+    <row r="8">
       <c r="A8" s="6">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>32</v>
@@ -1854,24 +1855,24 @@
         <v>33</v>
       </c>
       <c r="D8" s="6">
-        <v>1940</v>
+        <v>1940.0</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="4">
-        <v>69</v>
+        <v>69.0</v>
       </c>
       <c r="G8" s="9">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.2">
+    <row r="9">
       <c r="A9" s="14">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
@@ -1880,24 +1881,24 @@
         <v>37</v>
       </c>
       <c r="D9" s="6">
-        <v>1929</v>
+        <v>1929.0</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="4">
-        <v>69</v>
+        <v>69.0</v>
       </c>
       <c r="G9" s="9">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.2">
+    <row r="10">
       <c r="A10" s="6">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>36</v>
@@ -1906,24 +1907,24 @@
         <v>40</v>
       </c>
       <c r="D10" s="6">
-        <v>1930</v>
+        <v>1930.0</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>69</v>
+        <v>69.0</v>
       </c>
       <c r="G10" s="9">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.2">
+    <row r="11">
       <c r="A11" s="6">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -1932,24 +1933,24 @@
         <v>43</v>
       </c>
       <c r="D11" s="15">
-        <v>15155</v>
+        <v>15155.0</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="4">
-        <v>107</v>
+        <v>107.0</v>
       </c>
       <c r="G11" s="9">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.2">
+    <row r="12">
       <c r="A12" s="6">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>46</v>
@@ -1958,24 +1959,24 @@
         <v>47</v>
       </c>
       <c r="D12" s="6">
-        <v>1942</v>
+        <v>1942.0</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="4">
-        <v>112</v>
+        <v>112.0</v>
       </c>
       <c r="G12" s="9">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.2">
+    <row r="13">
       <c r="A13" s="6">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>32</v>
@@ -1984,24 +1985,24 @@
         <v>50</v>
       </c>
       <c r="D13" s="16">
-        <v>1942</v>
+        <v>1942.0</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="4">
-        <v>112</v>
+        <v>112.0</v>
       </c>
       <c r="G13" s="9">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.2">
+    <row r="14">
       <c r="A14" s="6">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>53</v>
@@ -2010,24 +2011,24 @@
         <v>54</v>
       </c>
       <c r="D14" s="6">
-        <v>1964</v>
+        <v>1964.0</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="4">
-        <v>120</v>
+        <v>120.0</v>
       </c>
       <c r="G14" s="9">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.2">
+    <row r="15">
       <c r="A15" s="6">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>57</v>
@@ -2036,24 +2037,24 @@
         <v>58</v>
       </c>
       <c r="D15" s="6">
-        <v>1942</v>
+        <v>1942.0</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="4">
-        <v>111</v>
+        <v>111.0</v>
       </c>
       <c r="G15" s="9">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.2">
+    <row r="16">
       <c r="A16" s="6">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>61</v>
@@ -2062,24 +2063,24 @@
         <v>62</v>
       </c>
       <c r="D16" s="6">
-        <v>2018</v>
+        <v>2018.0</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="4">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="G16" s="9">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.2">
+    <row r="17">
       <c r="A17" s="6">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>24</v>
@@ -2088,24 +2089,24 @@
         <v>65</v>
       </c>
       <c r="D17" s="6">
-        <v>1938</v>
+        <v>1938.0</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F17" s="4">
-        <v>134</v>
+        <v>134.0</v>
       </c>
       <c r="G17" s="9">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.2">
+    <row r="18">
       <c r="A18" s="6">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>32</v>
@@ -2114,24 +2115,24 @@
         <v>68</v>
       </c>
       <c r="D18" s="6">
-        <v>1945</v>
+        <v>1945.0</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="4">
-        <v>134</v>
+        <v>134.0</v>
       </c>
       <c r="G18" s="9">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.2">
+    <row r="19">
       <c r="A19" s="6">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>71</v>
@@ -2140,24 +2141,24 @@
         <v>72</v>
       </c>
       <c r="D19" s="17">
-        <v>1923</v>
+        <v>1923.0</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F19" s="4">
-        <v>56</v>
+        <v>56.0</v>
       </c>
       <c r="G19" s="9">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.2">
+    <row r="20">
       <c r="A20" s="19">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>75</v>
@@ -2166,24 +2167,24 @@
         <v>76</v>
       </c>
       <c r="D20" s="6">
-        <v>1951</v>
+        <v>1951.0</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="F20" s="4">
-        <v>142</v>
+        <v>142.0</v>
       </c>
       <c r="G20" s="9">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.2">
+    <row r="21">
       <c r="A21" s="19">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>79</v>
@@ -2192,24 +2193,24 @@
         <v>80</v>
       </c>
       <c r="D21" s="6">
-        <v>1953</v>
+        <v>1953.0</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="4">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="G21" s="9">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.2">
+    <row r="22">
       <c r="A22" s="19">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>57</v>
@@ -2218,24 +2219,24 @@
         <v>83</v>
       </c>
       <c r="D22" s="15">
-        <v>22555</v>
+        <v>22555.0</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="F22" s="4">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="G22" s="9">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.2">
+    <row r="23">
       <c r="A23" s="19">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>86</v>
@@ -2244,24 +2245,24 @@
         <v>87</v>
       </c>
       <c r="D23" s="6">
-        <v>1983</v>
+        <v>1983.0</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>88</v>
       </c>
       <c r="F23" s="4">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="G23" s="9">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.2">
+    <row r="24">
       <c r="A24" s="19">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
@@ -2270,24 +2271,24 @@
         <v>90</v>
       </c>
       <c r="D24" s="6">
-        <v>1971</v>
+        <v>1971.0</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="4">
-        <v>163</v>
+        <v>163.0</v>
       </c>
       <c r="G24" s="4">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.2">
+    <row r="25">
       <c r="A25" s="19">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>93</v>
@@ -2296,24 +2297,24 @@
         <v>94</v>
       </c>
       <c r="D25" s="6">
-        <v>1961</v>
+        <v>1961.0</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>95</v>
       </c>
       <c r="F25" s="4">
-        <v>163</v>
+        <v>163.0</v>
       </c>
       <c r="G25" s="9">
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.2">
+    <row r="26">
       <c r="A26" s="19">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>61</v>
@@ -2322,24 +2323,24 @@
         <v>97</v>
       </c>
       <c r="D26" s="6">
-        <v>1958</v>
+        <v>1958.0</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
       </c>
       <c r="F26" s="4">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="G26" s="9">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.2">
+    <row r="27">
       <c r="A27" s="19">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>79</v>
@@ -2354,18 +2355,18 @@
         <v>102</v>
       </c>
       <c r="F27" s="4">
-        <v>165</v>
+        <v>165.0</v>
       </c>
       <c r="G27" s="9">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.2">
+    <row r="28">
       <c r="A28" s="19">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
@@ -2374,24 +2375,24 @@
         <v>104</v>
       </c>
       <c r="D28" s="6">
-        <v>1979</v>
+        <v>1979.0</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
       </c>
       <c r="F28" s="4">
-        <v>165</v>
+        <v>165.0</v>
       </c>
       <c r="G28" s="9">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.2">
+    <row r="29">
       <c r="A29" s="19">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>107</v>
@@ -2400,24 +2401,24 @@
         <v>108</v>
       </c>
       <c r="D29" s="6">
-        <v>1960</v>
+        <v>1960.0</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>109</v>
       </c>
       <c r="F29" s="4">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G29" s="9">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.2">
+    <row r="30">
       <c r="A30" s="19">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>111</v>
@@ -2426,24 +2427,24 @@
         <v>112</v>
       </c>
       <c r="D30" s="6">
-        <v>1957</v>
+        <v>1957.0</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
       </c>
       <c r="F30" s="4">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G30" s="9">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.2">
+    <row r="31">
       <c r="A31" s="19">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>115</v>
@@ -2452,24 +2453,24 @@
         <v>116</v>
       </c>
       <c r="D31" s="6">
-        <v>1947</v>
+        <v>1947.0</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="4">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="G31" s="9">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.2">
+    <row r="32">
       <c r="A32" s="19">
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
@@ -2478,24 +2479,24 @@
         <v>120</v>
       </c>
       <c r="D32" s="6">
-        <v>1977</v>
+        <v>1977.0</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
       </c>
       <c r="F32" s="4">
-        <v>160</v>
+        <v>160.0</v>
       </c>
       <c r="G32" s="9">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.2">
+    <row r="33">
       <c r="A33" s="19">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>61</v>
@@ -2504,46 +2505,46 @@
         <v>123</v>
       </c>
       <c r="D33" s="6">
-        <v>1980</v>
+        <v>1980.0</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>124</v>
       </c>
       <c r="F33" s="4">
-        <v>221</v>
+        <v>221.0</v>
       </c>
       <c r="G33" s="9">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.2">
+    <row r="34">
       <c r="A34" s="19">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="6">
-        <v>1981</v>
+        <v>1981.0</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
       </c>
       <c r="F34" s="4">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.2">
+    <row r="35">
       <c r="A35" s="19">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>57</v>
@@ -2552,24 +2553,24 @@
         <v>129</v>
       </c>
       <c r="D35" s="6">
-        <v>1957</v>
+        <v>1957.0</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>130</v>
       </c>
       <c r="F35" s="4">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="G35" s="9">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.2">
+    <row r="36">
       <c r="A36" s="19">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>132</v>
@@ -2578,632 +2579,616 @@
         <v>133</v>
       </c>
       <c r="D36" s="6">
-        <v>1981</v>
+        <v>1981.0</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="4">
-        <v>192</v>
+        <v>192.0</v>
       </c>
       <c r="G36" s="9">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.2">
+    <row r="37">
       <c r="A37" s="19">
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>379</v>
+        <v>137</v>
       </c>
       <c r="D37" s="6">
-        <v>1906</v>
+        <v>1906.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G37" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="13.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="19">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D38" s="6">
-        <v>1904</v>
+        <v>1904.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G38" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="H38" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19">
+        <v>41.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1904.0</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="13.2">
-      <c r="A39" s="19">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1904</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="F39" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G39" s="9">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="13.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="19">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G40" s="9">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="13.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" s="19">
-        <v>43</v>
+        <v>43.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D41" s="6">
-        <v>1912</v>
+        <v>1912.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G41" s="9">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="13.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="19">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1904.0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19">
+        <v>45.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D42" s="6">
-        <v>1904</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F42" s="4">
-        <v>1</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="13.2">
-      <c r="A43" s="19">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="C43" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D43" s="6">
-        <v>1905</v>
+        <v>1905.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="4">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="13.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="19">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D44" s="6">
-        <v>1920</v>
+        <v>1920.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="4">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="G44" s="9">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="13.2">
-      <c r="A45" s="19">
-        <v>47</v>
-      </c>
-      <c r="B45" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C45" s="6" t="s">
+    </row>
+    <row r="45">
+      <c r="A45" s="19"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="H45" s="20"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="19">
+        <v>48.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="6">
-        <v>1933</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F45" s="4">
-        <v>40</v>
-      </c>
-      <c r="G45" s="9">
-        <v>10</v>
-      </c>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="13.2">
-      <c r="A46" s="19">
-        <v>48</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="D46" s="6">
+        <v>1936.0</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="F46" s="4">
+        <v>46.0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>11.0</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D46" s="6">
-        <v>1936</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F46" s="4">
-        <v>46</v>
-      </c>
-      <c r="G46" s="9">
-        <v>11</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="13.2">
+    </row>
+    <row r="47">
       <c r="A47" s="19">
-        <v>49</v>
+        <v>49.0</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1935.0</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="4">
+        <v>45.0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D47" s="6">
-        <v>1935</v>
-      </c>
-      <c r="E47" s="6" t="s">
+    </row>
+    <row r="48">
+      <c r="A48" s="19">
+        <v>50.0</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="4">
-        <v>45</v>
-      </c>
-      <c r="G47" s="9">
-        <v>8</v>
-      </c>
-      <c r="H47" s="11" t="s">
+      <c r="C48" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="13.2">
-      <c r="A48" s="19">
-        <v>50</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="D48" s="6">
+        <v>1910.0</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="F48" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="G48" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="6">
-        <v>1910</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F48" s="4">
-        <v>5</v>
-      </c>
-      <c r="G48" s="4">
-        <v>12</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="13.2">
+    </row>
+    <row r="49">
       <c r="A49" s="19">
-        <v>51</v>
+        <v>51.0</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1924.0</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" s="4">
+        <v>43.0</v>
+      </c>
+      <c r="G49" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="6">
-        <v>1924</v>
-      </c>
-      <c r="E49" s="6" t="s">
+    </row>
+    <row r="50">
+      <c r="A50" s="19">
+        <v>52.0</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="4">
-        <v>43</v>
-      </c>
-      <c r="G49" s="4">
-        <v>25</v>
-      </c>
-      <c r="H49" s="11" t="s">
+      <c r="C50" s="6" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="13.2">
-      <c r="A50" s="19">
-        <v>52</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="D50" s="6">
+        <v>1917.0</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="F50" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>14.0</v>
+      </c>
+      <c r="H50" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D50" s="6">
-        <v>1917</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F50" s="4">
-        <v>21</v>
-      </c>
-      <c r="G50" s="9">
-        <v>14</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="13.2">
+    </row>
+    <row r="51">
       <c r="A51" s="19">
-        <v>53</v>
+        <v>53.0</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="H51" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E51" s="6" t="s">
+    </row>
+    <row r="52">
+      <c r="A52" s="19">
+        <v>54.0</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="C52" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="13.2">
-      <c r="A52" s="19">
-        <v>54</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="D52" s="6">
+        <v>1974.0</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="F52" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>16.0</v>
+      </c>
+      <c r="H52" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="6">
-        <v>1974</v>
-      </c>
-      <c r="E52" s="6" t="s">
+    </row>
+    <row r="53">
+      <c r="A53" s="19">
+        <v>55.0</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F52" s="4">
-        <v>107</v>
-      </c>
-      <c r="G52" s="9">
-        <v>16</v>
-      </c>
-      <c r="H52" s="11" t="s">
+      <c r="C53" s="6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="13.2">
-      <c r="A53" s="19">
-        <v>55</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="D53" s="6">
+        <v>1975.0</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="F53" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>17.0</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D53" s="6">
-        <v>1975</v>
-      </c>
-      <c r="E53" s="6" t="s">
+    </row>
+    <row r="54">
+      <c r="A54" s="19">
+        <v>56.0</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F53" s="4">
-        <v>107</v>
-      </c>
-      <c r="G53" s="9">
-        <v>17</v>
-      </c>
-      <c r="H53" s="11" t="s">
+      <c r="C54" s="21" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="13.2">
-      <c r="A54" s="19">
-        <v>56</v>
-      </c>
-      <c r="B54" s="6" t="s">
+      <c r="D54" s="6">
+        <v>1971.0</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="F54" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>15.0</v>
+      </c>
+      <c r="H54" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D54" s="6">
-        <v>1971</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="4">
-        <v>107</v>
-      </c>
-      <c r="G54" s="9">
-        <v>15</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="13.2">
+    </row>
+    <row r="55">
       <c r="A55" s="19">
-        <v>57</v>
+        <v>57.0</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D55" s="22">
+        <v>1946.0</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H55" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D55" s="22">
-        <v>1946</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F55" s="4">
-        <v>107</v>
-      </c>
-      <c r="G55" s="9">
-        <v>8</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="13.2">
+    </row>
+    <row r="56">
       <c r="A56" s="19">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1947.0</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>18.0</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D56" s="6">
-        <v>1947</v>
-      </c>
-      <c r="E56" s="6" t="s">
+    </row>
+    <row r="57">
+      <c r="A57" s="19">
+        <v>59.0</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F56" s="4">
-        <v>107</v>
-      </c>
-      <c r="G56" s="9">
-        <v>18</v>
-      </c>
-      <c r="H56" s="11" t="s">
+      <c r="C57" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="13.2">
-      <c r="A57" s="19">
-        <v>59</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>1974.0</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="F57" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>19.0</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="D57" s="6">
-        <v>1974</v>
-      </c>
-      <c r="E57" s="6" t="s">
+    </row>
+    <row r="58">
+      <c r="A58" s="19">
+        <v>60.0</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F57" s="4">
-        <v>107</v>
-      </c>
-      <c r="G57" s="9">
-        <v>19</v>
-      </c>
-      <c r="H57" s="11" t="s">
+      <c r="C58" s="6" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="13.2">
-      <c r="A58" s="19">
-        <v>60</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="D58" s="6">
+        <v>1975.0</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="F58" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>20.0</v>
+      </c>
+      <c r="H58" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D58" s="6">
-        <v>1975</v>
-      </c>
-      <c r="E58" s="6" t="s">
+    </row>
+    <row r="59">
+      <c r="A59" s="19">
+        <v>61.0</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F58" s="4">
-        <v>107</v>
-      </c>
-      <c r="G58" s="9">
-        <v>20</v>
-      </c>
-      <c r="H58" s="18" t="s">
+      <c r="C59" s="6" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="13.2">
-      <c r="A59" s="19">
-        <v>61</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="D59" s="6">
+        <v>1969.0</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="F59" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>21.0</v>
+      </c>
+      <c r="H59" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="D59" s="6">
-        <v>1969</v>
-      </c>
-      <c r="E59" s="6" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" s="19">
+        <v>62.0</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F59" s="4">
-        <v>107</v>
-      </c>
-      <c r="G59" s="9">
-        <v>21</v>
-      </c>
-      <c r="H59" s="11" t="s">
+      <c r="C60" s="6" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="13.2">
-      <c r="A60" s="19">
-        <v>62</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="D60" s="6">
+        <v>1971.0</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="F60" s="4">
+        <v>107.0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>26.0</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D60" s="6">
-        <v>1971</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F60" s="4">
-        <v>107</v>
-      </c>
-      <c r="G60" s="9">
-        <v>26</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="18" customHeight="1">
+    </row>
+    <row r="61" ht="18.0" customHeight="1">
       <c r="A61" s="19">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -3211,9 +3196,9 @@
       <c r="E61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62" spans="1:8" ht="13.2">
+    <row r="62">
       <c r="A62" s="19">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -3221,9 +3206,9 @@
       <c r="E62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63" spans="1:8" ht="13.2">
+    <row r="63">
       <c r="A63" s="19">
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -3231,9 +3216,9 @@
       <c r="E63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64" spans="1:8" ht="13.2">
+    <row r="64">
       <c r="A64" s="19">
-        <v>66</v>
+        <v>66.0</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -3241,9 +3226,9 @@
       <c r="E64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65" spans="1:8" ht="13.2">
+    <row r="65">
       <c r="A65" s="19">
-        <v>67</v>
+        <v>67.0</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -3251,9 +3236,9 @@
       <c r="E65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66" spans="1:8" ht="13.2">
+    <row r="66">
       <c r="A66" s="19">
-        <v>68</v>
+        <v>68.0</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -3261,9 +3246,9 @@
       <c r="E66" s="20"/>
       <c r="H66" s="20"/>
     </row>
-    <row r="67" spans="1:8" ht="13.2">
+    <row r="67">
       <c r="A67" s="19">
-        <v>69</v>
+        <v>69.0</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -3271,9 +3256,9 @@
       <c r="E67" s="20"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68" spans="1:8" ht="13.2">
+    <row r="68">
       <c r="A68" s="19">
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -3281,9 +3266,9 @@
       <c r="E68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69" spans="1:8" ht="13.2">
+    <row r="69">
       <c r="A69" s="19">
-        <v>71</v>
+        <v>71.0</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -3291,9 +3276,9 @@
       <c r="E69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70" spans="1:8" ht="13.2">
+    <row r="70">
       <c r="A70" s="19">
-        <v>72</v>
+        <v>72.0</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -3301,9 +3286,9 @@
       <c r="E70" s="20"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71" spans="1:8" ht="13.2">
+    <row r="71">
       <c r="A71" s="19">
-        <v>73</v>
+        <v>73.0</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -3311,9 +3296,9 @@
       <c r="E71" s="20"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72" spans="1:8" ht="13.2">
+    <row r="72">
       <c r="A72" s="19">
-        <v>74</v>
+        <v>74.0</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -3321,9 +3306,9 @@
       <c r="E72" s="20"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73" spans="1:8" ht="13.2">
+    <row r="73">
       <c r="A73" s="19">
-        <v>75</v>
+        <v>75.0</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -3331,9 +3316,9 @@
       <c r="E73" s="20"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74" spans="1:8" ht="13.2">
+    <row r="74">
       <c r="A74" s="19">
-        <v>76</v>
+        <v>76.0</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -3341,9 +3326,9 @@
       <c r="E74" s="20"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75" spans="1:8" ht="13.2">
+    <row r="75">
       <c r="A75" s="19">
-        <v>77</v>
+        <v>77.0</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -3351,9 +3336,9 @@
       <c r="E75" s="20"/>
       <c r="H75" s="20"/>
     </row>
-    <row r="76" spans="1:8" ht="13.2">
+    <row r="76">
       <c r="A76" s="19">
-        <v>78</v>
+        <v>78.0</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -3361,9 +3346,9 @@
       <c r="E76" s="20"/>
       <c r="H76" s="20"/>
     </row>
-    <row r="77" spans="1:8" ht="13.2">
+    <row r="77">
       <c r="A77" s="19">
-        <v>79</v>
+        <v>79.0</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -3371,9 +3356,9 @@
       <c r="E77" s="20"/>
       <c r="H77" s="20"/>
     </row>
-    <row r="78" spans="1:8" ht="13.2">
+    <row r="78">
       <c r="A78" s="19">
-        <v>80</v>
+        <v>80.0</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -3381,9 +3366,9 @@
       <c r="E78" s="20"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79" spans="1:8" ht="13.2">
+    <row r="79">
       <c r="A79" s="19">
-        <v>81</v>
+        <v>81.0</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -3391,9 +3376,9 @@
       <c r="E79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80" spans="1:8" ht="13.2">
+    <row r="80">
       <c r="A80" s="19">
-        <v>82</v>
+        <v>82.0</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -3401,9 +3386,9 @@
       <c r="E80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81" spans="1:8" ht="13.2">
+    <row r="81">
       <c r="A81" s="19">
-        <v>83</v>
+        <v>83.0</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -3411,9 +3396,9 @@
       <c r="E81" s="20"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82" spans="1:8" ht="13.2">
+    <row r="82">
       <c r="A82" s="19">
-        <v>84</v>
+        <v>84.0</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
@@ -3421,9 +3406,9 @@
       <c r="E82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83" spans="1:8" ht="13.2">
+    <row r="83">
       <c r="A83" s="19">
-        <v>85</v>
+        <v>85.0</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -3431,9 +3416,9 @@
       <c r="E83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84" spans="1:8" ht="13.2">
+    <row r="84">
       <c r="A84" s="19">
-        <v>86</v>
+        <v>86.0</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -3441,9 +3426,9 @@
       <c r="E84" s="20"/>
       <c r="H84" s="20"/>
     </row>
-    <row r="85" spans="1:8" ht="13.2">
+    <row r="85">
       <c r="A85" s="19">
-        <v>87</v>
+        <v>87.0</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -3451,9 +3436,9 @@
       <c r="E85" s="20"/>
       <c r="H85" s="20"/>
     </row>
-    <row r="86" spans="1:8" ht="13.2">
+    <row r="86">
       <c r="A86" s="19">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -3461,9 +3446,9 @@
       <c r="E86" s="20"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87" spans="1:8" ht="13.2">
+    <row r="87">
       <c r="A87" s="19">
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -3471,9 +3456,9 @@
       <c r="E87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88" spans="1:8" ht="13.2">
+    <row r="88">
       <c r="A88" s="19">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -3481,9 +3466,9 @@
       <c r="E88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89" spans="1:8" ht="13.2">
+    <row r="89">
       <c r="A89" s="19">
-        <v>91</v>
+        <v>91.0</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -3491,9 +3476,9 @@
       <c r="E89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90" spans="1:8" ht="13.2">
+    <row r="90">
       <c r="A90" s="19">
-        <v>92</v>
+        <v>92.0</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -3501,9 +3486,9 @@
       <c r="E90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91" spans="1:8" ht="13.2">
+    <row r="91">
       <c r="A91" s="19">
-        <v>93</v>
+        <v>93.0</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -3511,9 +3496,9 @@
       <c r="E91" s="20"/>
       <c r="H91" s="20"/>
     </row>
-    <row r="92" spans="1:8" ht="13.2">
+    <row r="92">
       <c r="A92" s="19">
-        <v>94</v>
+        <v>94.0</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -3521,9 +3506,9 @@
       <c r="E92" s="20"/>
       <c r="H92" s="20"/>
     </row>
-    <row r="93" spans="1:8" ht="13.2">
+    <row r="93">
       <c r="A93" s="19">
-        <v>95</v>
+        <v>95.0</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -3531,9 +3516,9 @@
       <c r="E93" s="20"/>
       <c r="H93" s="20"/>
     </row>
-    <row r="94" spans="1:8" ht="13.2">
+    <row r="94">
       <c r="A94" s="19">
-        <v>96</v>
+        <v>96.0</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -3541,9 +3526,9 @@
       <c r="E94" s="20"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95" spans="1:8" ht="13.2">
+    <row r="95">
       <c r="A95" s="19">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -3551,9 +3536,9 @@
       <c r="E95" s="20"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96" spans="1:8" ht="13.2">
+    <row r="96">
       <c r="A96" s="19">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -3561,9 +3546,9 @@
       <c r="E96" s="20"/>
       <c r="H96" s="20"/>
     </row>
-    <row r="97" spans="1:8" ht="13.2">
+    <row r="97">
       <c r="A97" s="19">
-        <v>99</v>
+        <v>99.0</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -3571,9 +3556,9 @@
       <c r="E97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98" spans="1:8" ht="13.2">
+    <row r="98">
       <c r="A98" s="19">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -3581,9 +3566,9 @@
       <c r="E98" s="20"/>
       <c r="H98" s="20"/>
     </row>
-    <row r="99" spans="1:8" ht="13.2">
+    <row r="99">
       <c r="A99" s="19">
-        <v>101</v>
+        <v>101.0</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -3591,9 +3576,9 @@
       <c r="E99" s="20"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100" spans="1:8" ht="13.2">
+    <row r="100">
       <c r="A100" s="19">
-        <v>102</v>
+        <v>102.0</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -3601,9 +3586,9 @@
       <c r="E100" s="20"/>
       <c r="H100" s="20"/>
     </row>
-    <row r="101" spans="1:8" ht="13.2">
+    <row r="101">
       <c r="A101" s="19">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -3611,9 +3596,9 @@
       <c r="E101" s="20"/>
       <c r="H101" s="20"/>
     </row>
-    <row r="102" spans="1:8" ht="13.2">
+    <row r="102">
       <c r="A102" s="19">
-        <v>104</v>
+        <v>104.0</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -3621,9 +3606,9 @@
       <c r="E102" s="20"/>
       <c r="H102" s="20"/>
     </row>
-    <row r="103" spans="1:8" ht="13.2">
+    <row r="103">
       <c r="A103" s="19">
-        <v>105</v>
+        <v>105.0</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -3631,9 +3616,9 @@
       <c r="E103" s="20"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104" spans="1:8" ht="13.2">
+    <row r="104">
       <c r="A104" s="19">
-        <v>106</v>
+        <v>106.0</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -3641,9 +3626,9 @@
       <c r="E104" s="20"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105" spans="1:8" ht="13.2">
+    <row r="105">
       <c r="A105" s="19">
-        <v>107</v>
+        <v>107.0</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -3651,9 +3636,9 @@
       <c r="E105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106" spans="1:8" ht="13.2">
+    <row r="106">
       <c r="A106" s="19">
-        <v>108</v>
+        <v>108.0</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -3661,9 +3646,9 @@
       <c r="E106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107" spans="1:8" ht="13.2">
+    <row r="107">
       <c r="A107" s="19">
-        <v>109</v>
+        <v>109.0</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -3671,9 +3656,9 @@
       <c r="E107" s="20"/>
       <c r="H107" s="20"/>
     </row>
-    <row r="108" spans="1:8" ht="13.2">
+    <row r="108">
       <c r="A108" s="19">
-        <v>110</v>
+        <v>110.0</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -3681,9 +3666,9 @@
       <c r="E108" s="20"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109" spans="1:8" ht="13.2">
+    <row r="109">
       <c r="A109" s="19">
-        <v>111</v>
+        <v>111.0</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -3691,9 +3676,9 @@
       <c r="E109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110" spans="1:8" ht="13.2">
+    <row r="110">
       <c r="A110" s="19">
-        <v>112</v>
+        <v>112.0</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -3701,9 +3686,9 @@
       <c r="E110" s="20"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111" spans="1:8" ht="13.2">
+    <row r="111">
       <c r="A111" s="19">
-        <v>113</v>
+        <v>113.0</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
@@ -3711,9 +3696,9 @@
       <c r="E111" s="20"/>
       <c r="H111" s="20"/>
     </row>
-    <row r="112" spans="1:8" ht="13.2">
+    <row r="112">
       <c r="A112" s="19">
-        <v>114</v>
+        <v>114.0</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
@@ -3721,9 +3706,9 @@
       <c r="E112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113" spans="1:8" ht="13.2">
+    <row r="113">
       <c r="A113" s="19">
-        <v>115</v>
+        <v>115.0</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -3731,9 +3716,9 @@
       <c r="E113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114" spans="1:8" ht="13.2">
+    <row r="114">
       <c r="A114" s="19">
-        <v>116</v>
+        <v>116.0</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -3741,9 +3726,9 @@
       <c r="E114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115" spans="1:8" ht="13.2">
+    <row r="115">
       <c r="A115" s="19">
-        <v>117</v>
+        <v>117.0</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
@@ -3751,9 +3736,9 @@
       <c r="E115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116" spans="1:8" ht="13.2">
+    <row r="116">
       <c r="A116" s="19">
-        <v>118</v>
+        <v>118.0</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -3761,9 +3746,9 @@
       <c r="E116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117" spans="1:8" ht="13.2">
+    <row r="117">
       <c r="A117" s="19">
-        <v>119</v>
+        <v>119.0</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -3771,9 +3756,9 @@
       <c r="E117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118" spans="1:8" ht="13.2">
+    <row r="118">
       <c r="A118" s="19">
-        <v>120</v>
+        <v>120.0</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -3781,9 +3766,9 @@
       <c r="E118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119" spans="1:8" ht="13.2">
+    <row r="119">
       <c r="A119" s="19">
-        <v>121</v>
+        <v>121.0</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -3791,9 +3776,9 @@
       <c r="E119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120" spans="1:8" ht="13.2">
+    <row r="120">
       <c r="A120" s="19">
-        <v>122</v>
+        <v>122.0</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -3801,9 +3786,9 @@
       <c r="E120" s="20"/>
       <c r="H120" s="20"/>
     </row>
-    <row r="121" spans="1:8" ht="13.2">
+    <row r="121">
       <c r="A121" s="19">
-        <v>123</v>
+        <v>123.0</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -3811,9 +3796,9 @@
       <c r="E121" s="20"/>
       <c r="H121" s="20"/>
     </row>
-    <row r="122" spans="1:8" ht="13.2">
+    <row r="122">
       <c r="A122" s="19">
-        <v>124</v>
+        <v>124.0</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -3821,9 +3806,9 @@
       <c r="E122" s="20"/>
       <c r="H122" s="20"/>
     </row>
-    <row r="123" spans="1:8" ht="13.2">
+    <row r="123">
       <c r="A123" s="19">
-        <v>125</v>
+        <v>125.0</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -3831,9 +3816,9 @@
       <c r="E123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124" spans="1:8" ht="13.2">
+    <row r="124">
       <c r="A124" s="19">
-        <v>126</v>
+        <v>126.0</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -3841,9 +3826,9 @@
       <c r="E124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125" spans="1:8" ht="13.2">
+    <row r="125">
       <c r="A125" s="19">
-        <v>127</v>
+        <v>127.0</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -3851,9 +3836,9 @@
       <c r="E125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126" spans="1:8" ht="13.2">
+    <row r="126">
       <c r="A126" s="19">
-        <v>128</v>
+        <v>128.0</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -3861,9 +3846,9 @@
       <c r="E126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127" spans="1:8" ht="13.2">
+    <row r="127">
       <c r="A127" s="19">
-        <v>129</v>
+        <v>129.0</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
@@ -3871,9 +3856,9 @@
       <c r="E127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128" spans="1:8" ht="13.2">
+    <row r="128">
       <c r="A128" s="19">
-        <v>130</v>
+        <v>130.0</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
@@ -3881,9 +3866,9 @@
       <c r="E128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129" spans="1:8" ht="13.2">
+    <row r="129">
       <c r="A129" s="19">
-        <v>131</v>
+        <v>131.0</v>
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -3891,9 +3876,9 @@
       <c r="E129" s="20"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130" spans="1:8" ht="13.2">
+    <row r="130">
       <c r="A130" s="19">
-        <v>132</v>
+        <v>132.0</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -3901,9 +3886,9 @@
       <c r="E130" s="20"/>
       <c r="H130" s="20"/>
     </row>
-    <row r="131" spans="1:8" ht="13.2">
+    <row r="131">
       <c r="A131" s="19">
-        <v>133</v>
+        <v>133.0</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -3911,9 +3896,9 @@
       <c r="E131" s="20"/>
       <c r="H131" s="20"/>
     </row>
-    <row r="132" spans="1:8" ht="13.2">
+    <row r="132">
       <c r="A132" s="19">
-        <v>134</v>
+        <v>134.0</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -3921,9 +3906,9 @@
       <c r="E132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133" spans="1:8" ht="13.2">
+    <row r="133">
       <c r="A133" s="19">
-        <v>135</v>
+        <v>135.0</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -3931,9 +3916,9 @@
       <c r="E133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134" spans="1:8" ht="13.2">
+    <row r="134">
       <c r="A134" s="19">
-        <v>136</v>
+        <v>136.0</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -3941,9 +3926,9 @@
       <c r="E134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135" spans="1:8" ht="13.2">
+    <row r="135">
       <c r="A135" s="19">
-        <v>137</v>
+        <v>137.0</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -3951,9 +3936,9 @@
       <c r="E135" s="20"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136" spans="1:8" ht="13.2">
+    <row r="136">
       <c r="A136" s="19">
-        <v>138</v>
+        <v>138.0</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -3961,9 +3946,9 @@
       <c r="E136" s="20"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137" spans="1:8" ht="13.2">
+    <row r="137">
       <c r="A137" s="19">
-        <v>139</v>
+        <v>139.0</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -3971,9 +3956,9 @@
       <c r="E137" s="20"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138" spans="1:8" ht="13.2">
+    <row r="138">
       <c r="A138" s="19">
-        <v>140</v>
+        <v>140.0</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -3981,9 +3966,9 @@
       <c r="E138" s="20"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139" spans="1:8" ht="13.2">
+    <row r="139">
       <c r="A139" s="19">
-        <v>141</v>
+        <v>141.0</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -3991,9 +3976,9 @@
       <c r="E139" s="20"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140" spans="1:8" ht="13.2">
+    <row r="140">
       <c r="A140" s="19">
-        <v>142</v>
+        <v>142.0</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -4001,9 +3986,9 @@
       <c r="E140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141" spans="1:8" ht="13.2">
+    <row r="141">
       <c r="A141" s="19">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -4011,9 +3996,9 @@
       <c r="E141" s="20"/>
       <c r="H141" s="20"/>
     </row>
-    <row r="142" spans="1:8" ht="13.2">
+    <row r="142">
       <c r="A142" s="19">
-        <v>144</v>
+        <v>144.0</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -4021,9 +4006,9 @@
       <c r="E142" s="20"/>
       <c r="H142" s="20"/>
     </row>
-    <row r="143" spans="1:8" ht="13.2">
+    <row r="143">
       <c r="A143" s="19">
-        <v>145</v>
+        <v>145.0</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -4031,9 +4016,9 @@
       <c r="E143" s="20"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144" spans="1:8" ht="13.2">
+    <row r="144">
       <c r="A144" s="19">
-        <v>146</v>
+        <v>146.0</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -4041,9 +4026,9 @@
       <c r="E144" s="20"/>
       <c r="H144" s="20"/>
     </row>
-    <row r="145" spans="1:8" ht="13.2">
+    <row r="145">
       <c r="A145" s="19">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -4051,9 +4036,9 @@
       <c r="E145" s="20"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146" spans="1:8" ht="13.2">
+    <row r="146">
       <c r="A146" s="19">
-        <v>148</v>
+        <v>148.0</v>
       </c>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -4061,9 +4046,9 @@
       <c r="E146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147" spans="1:8" ht="13.2">
+    <row r="147">
       <c r="A147" s="19">
-        <v>149</v>
+        <v>149.0</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -4071,9 +4056,9 @@
       <c r="E147" s="20"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148" spans="1:8" ht="13.2">
+    <row r="148">
       <c r="A148" s="19">
-        <v>150</v>
+        <v>150.0</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -4081,9 +4066,9 @@
       <c r="E148" s="20"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149" spans="1:8" ht="13.2">
+    <row r="149">
       <c r="A149" s="19">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -4091,9 +4076,9 @@
       <c r="E149" s="20"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150" spans="1:8" ht="13.2">
+    <row r="150">
       <c r="A150" s="19">
-        <v>152</v>
+        <v>152.0</v>
       </c>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -4101,9 +4086,9 @@
       <c r="E150" s="20"/>
       <c r="H150" s="20"/>
     </row>
-    <row r="151" spans="1:8" ht="13.2">
+    <row r="151">
       <c r="A151" s="19">
-        <v>153</v>
+        <v>153.0</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -4111,9 +4096,9 @@
       <c r="E151" s="20"/>
       <c r="H151" s="20"/>
     </row>
-    <row r="152" spans="1:8" ht="13.2">
+    <row r="152">
       <c r="A152" s="19">
-        <v>154</v>
+        <v>154.0</v>
       </c>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -4123,1588 +4108,1587 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1"/>
-    <hyperlink ref="H3" r:id="rId2"/>
-    <hyperlink ref="H4" r:id="rId3"/>
-    <hyperlink ref="H5" r:id="rId4"/>
-    <hyperlink ref="H6" r:id="rId5"/>
-    <hyperlink ref="H7" r:id="rId6"/>
-    <hyperlink ref="H8" r:id="rId7"/>
-    <hyperlink ref="H9" r:id="rId8"/>
-    <hyperlink ref="H10" r:id="rId9"/>
-    <hyperlink ref="H11" r:id="rId10"/>
-    <hyperlink ref="H12" r:id="rId11"/>
-    <hyperlink ref="H13" r:id="rId12"/>
-    <hyperlink ref="H14" r:id="rId13"/>
-    <hyperlink ref="H15" r:id="rId14"/>
-    <hyperlink ref="H16" r:id="rId15"/>
-    <hyperlink ref="H17" r:id="rId16"/>
-    <hyperlink ref="H18" r:id="rId17"/>
-    <hyperlink ref="H19" r:id="rId18"/>
-    <hyperlink ref="H20" r:id="rId19"/>
-    <hyperlink ref="H21" r:id="rId20"/>
-    <hyperlink ref="H22" r:id="rId21"/>
-    <hyperlink ref="H23" r:id="rId22"/>
-    <hyperlink ref="H24" r:id="rId23"/>
-    <hyperlink ref="H25" r:id="rId24"/>
-    <hyperlink ref="H26" r:id="rId25"/>
-    <hyperlink ref="H27" r:id="rId26"/>
-    <hyperlink ref="H28" r:id="rId27"/>
-    <hyperlink ref="H29" r:id="rId28"/>
-    <hyperlink ref="H30" r:id="rId29"/>
-    <hyperlink ref="H31" r:id="rId30"/>
-    <hyperlink ref="H32" r:id="rId31"/>
-    <hyperlink ref="H33" r:id="rId32"/>
-    <hyperlink ref="H34" r:id="rId33"/>
-    <hyperlink ref="H35" r:id="rId34"/>
-    <hyperlink ref="H36" r:id="rId35"/>
-    <hyperlink ref="H37" r:id="rId36"/>
-    <hyperlink ref="H38" r:id="rId37"/>
-    <hyperlink ref="H39" r:id="rId38"/>
-    <hyperlink ref="H40" r:id="rId39"/>
-    <hyperlink ref="H41" r:id="rId40"/>
-    <hyperlink ref="H42" r:id="rId41"/>
-    <hyperlink ref="H43" r:id="rId42"/>
-    <hyperlink ref="H44" r:id="rId43"/>
-    <hyperlink ref="H46" r:id="rId44"/>
-    <hyperlink ref="H47" r:id="rId45"/>
-    <hyperlink ref="H48" r:id="rId46"/>
-    <hyperlink ref="H49" r:id="rId47"/>
-    <hyperlink ref="H50" r:id="rId48"/>
-    <hyperlink ref="H51" r:id="rId49"/>
-    <hyperlink ref="H52" r:id="rId50"/>
-    <hyperlink ref="H53" r:id="rId51"/>
-    <hyperlink ref="H54" r:id="rId52"/>
-    <hyperlink ref="H55" r:id="rId53"/>
-    <hyperlink ref="H56" r:id="rId54"/>
-    <hyperlink ref="H57" r:id="rId55"/>
-    <hyperlink ref="H58" r:id="rId56"/>
-    <hyperlink ref="H59" r:id="rId57"/>
-    <hyperlink ref="H60" r:id="rId58"/>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="H4"/>
+    <hyperlink r:id="rId4" ref="H5"/>
+    <hyperlink r:id="rId5" ref="H6"/>
+    <hyperlink r:id="rId6" ref="H7"/>
+    <hyperlink r:id="rId7" ref="H8"/>
+    <hyperlink r:id="rId8" ref="H9"/>
+    <hyperlink r:id="rId9" ref="H10"/>
+    <hyperlink r:id="rId10" ref="H11"/>
+    <hyperlink r:id="rId11" ref="H12"/>
+    <hyperlink r:id="rId12" ref="H13"/>
+    <hyperlink r:id="rId13" ref="H14"/>
+    <hyperlink r:id="rId14" ref="H15"/>
+    <hyperlink r:id="rId15" ref="H16"/>
+    <hyperlink r:id="rId16" ref="H17"/>
+    <hyperlink r:id="rId17" ref="H18"/>
+    <hyperlink r:id="rId18" ref="H19"/>
+    <hyperlink r:id="rId19" ref="H20"/>
+    <hyperlink r:id="rId20" ref="H21"/>
+    <hyperlink r:id="rId21" ref="H22"/>
+    <hyperlink r:id="rId22" ref="H23"/>
+    <hyperlink r:id="rId23" ref="H24"/>
+    <hyperlink r:id="rId24" ref="H25"/>
+    <hyperlink r:id="rId25" ref="H26"/>
+    <hyperlink r:id="rId26" ref="H27"/>
+    <hyperlink r:id="rId27" ref="H28"/>
+    <hyperlink r:id="rId28" ref="H29"/>
+    <hyperlink r:id="rId29" ref="H30"/>
+    <hyperlink r:id="rId30" ref="H31"/>
+    <hyperlink r:id="rId31" ref="H32"/>
+    <hyperlink r:id="rId32" ref="H33"/>
+    <hyperlink r:id="rId33" ref="H34"/>
+    <hyperlink r:id="rId34" ref="H35"/>
+    <hyperlink r:id="rId35" ref="H36"/>
+    <hyperlink r:id="rId36" ref="H37"/>
+    <hyperlink r:id="rId37" ref="H38"/>
+    <hyperlink r:id="rId38" ref="H39"/>
+    <hyperlink r:id="rId39" ref="H40"/>
+    <hyperlink r:id="rId40" ref="H41"/>
+    <hyperlink r:id="rId41" ref="H42"/>
+    <hyperlink r:id="rId42" ref="H43"/>
+    <hyperlink r:id="rId43" ref="H44"/>
+    <hyperlink r:id="rId44" ref="H46"/>
+    <hyperlink r:id="rId45" ref="H47"/>
+    <hyperlink r:id="rId46" ref="H48"/>
+    <hyperlink r:id="rId47" ref="H49"/>
+    <hyperlink r:id="rId48" ref="H50"/>
+    <hyperlink r:id="rId49" ref="H51"/>
+    <hyperlink r:id="rId50" ref="H52"/>
+    <hyperlink r:id="rId51" ref="H53"/>
+    <hyperlink r:id="rId52" ref="H54"/>
+    <hyperlink r:id="rId53" ref="H55"/>
+    <hyperlink r:id="rId54" ref="H56"/>
+    <hyperlink r:id="rId55" ref="H57"/>
+    <hyperlink r:id="rId56" ref="H58"/>
+    <hyperlink r:id="rId57" ref="H59"/>
+    <hyperlink r:id="rId58" ref="H60"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId59"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="33.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="33.86"/>
+    <col customWidth="1" min="5" max="5" width="16.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.2">
+    <row r="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>226</v>
-      </c>
       <c r="F1" s="16"/>
     </row>
-    <row r="2" spans="1:6" ht="13.2">
+    <row r="2">
       <c r="A2" s="7">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>music!B2</f>
         <v>Николай Яковлевич Мясковский</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D2" s="23">
-        <v>18452</v>
+        <v>18452.0</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="13.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="6">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B3" s="20" t="str">
         <f>music!B22</f>
         <v>Дмитрий Дмитриевич Шостакович</v>
       </c>
       <c r="C3" s="24">
-        <v>2447</v>
+        <v>2447.0</v>
       </c>
       <c r="D3" s="24">
-        <v>27615</v>
+        <v>27615.0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="13.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B4" s="20" t="str">
         <f>music!B37</f>
         <v>Илья Алексеевич Шатров</v>
       </c>
       <c r="C4" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="24">
+        <v>19116.0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="D4" s="24">
-        <v>19116</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D5" s="25">
+        <v>11290.0</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="13.2">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="25">
-        <v>11290</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.2">
+    <row r="6">
       <c r="A6" s="6">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B6" s="20" t="str">
         <f>music!B39</f>
         <v>Алексей Сергеевич Турищев</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D6" s="24">
-        <v>22693</v>
+        <v>22693.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="13.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="6">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B7" s="20" t="str">
         <f>music!B40</f>
         <v>Владимир Германович Богораз</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D7" s="24">
-        <v>13280</v>
+        <v>13280.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="13.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="7">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B8" s="20" t="str">
         <f>music!B41</f>
         <v>Василий Иванович Агапкин</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D8" s="25">
-        <v>23679</v>
+        <v>23679.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="13.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="6">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="24">
-        <v>1137</v>
+        <v>1137.0</v>
       </c>
       <c r="D9" s="24">
-        <v>33143</v>
+        <v>33143.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="13.2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="7">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="B10" s="20" t="str">
         <f>music!B44</f>
-        <v xml:space="preserve">Самуил Яковлевич Покрасс </v>
+        <v>Самуил Яковлевич Покрасс </v>
       </c>
       <c r="C10" s="6">
-        <v>1897</v>
+        <v>1897.0</v>
       </c>
       <c r="D10" s="24">
-        <v>14411</v>
+        <v>14411.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="13.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="7">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="B11" s="20" t="str">
         <f>music!B45</f>
-        <v>Томас Пефферман</v>
+        <v/>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="13.2">
+    <row r="12">
       <c r="A12" s="6">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="B12" s="20" t="str">
         <f>music!B46</f>
         <v>Виктор Аркадьевич Белый</v>
       </c>
       <c r="C12" s="24">
-        <v>1475</v>
+        <v>1475.0</v>
       </c>
       <c r="D12" s="24">
-        <v>30381</v>
+        <v>30381.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="13.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="7">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="B13" s="20" t="str">
         <f>music!B48</f>
         <v>Максимилиан Осеевич Штейнберг</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" s="24">
-        <v>17142</v>
+        <v>17142.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="13.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="6">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="B14" s="20" t="str">
         <f>music!B50</f>
         <v>Александр Николаевич Вертинский</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="24">
+        <v>20961.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="24">
+        <v>10291.0</v>
+      </c>
+      <c r="D15" s="24">
+        <v>32687.0</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D14" s="24">
-        <v>20961</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="13.2">
-      <c r="A15" s="6">
-        <v>15</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="24">
-        <v>10291</v>
-      </c>
-      <c r="D15" s="24">
-        <v>32687</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="13.2">
+    </row>
+    <row r="16">
       <c r="A16" s="7">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="B16" s="20" t="str">
         <f>music!B52</f>
         <v>Евгений Григорьевич Мартынов</v>
       </c>
       <c r="C16" s="24">
-        <v>17675</v>
+        <v>17675.0</v>
       </c>
       <c r="D16" s="24">
-        <v>33119</v>
+        <v>33119.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="13.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="6">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="B17" s="20" t="str">
         <f>music!B53</f>
         <v>Валентин Сергеевич Левашов</v>
       </c>
       <c r="C17" s="24">
-        <v>5684</v>
+        <v>5684.0</v>
       </c>
       <c r="D17" s="24">
-        <v>34582</v>
+        <v>34582.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="13.2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="6">
-        <v>18</v>
+        <v>18.0</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="24">
-        <v>2659</v>
+        <v>2659.0</v>
       </c>
       <c r="D18" s="24">
-        <v>29191</v>
+        <v>29191.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="13.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="7">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C19" s="24">
-        <v>14474</v>
+        <v>14474.0</v>
       </c>
       <c r="D19" s="24">
-        <v>36188</v>
+        <v>36188.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="13.2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="6">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C20" s="24">
-        <v>14812</v>
+        <v>14812.0</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="13.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="7">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="25">
-        <v>7631</v>
+        <v>7631.0</v>
       </c>
       <c r="D21" s="24">
-        <v>32745</v>
+        <v>32745.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="13.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="7">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="B22" s="20" t="str">
         <f>music!B3</f>
         <v>Анатолий Константинович Лядов</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D22" s="24">
-        <v>5310</v>
+        <v>5310.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="13.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="6">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="25">
-        <v>5829</v>
+        <v>5829.0</v>
       </c>
       <c r="D23" s="24">
-        <v>35801</v>
+        <v>35801.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="13.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="7">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="24">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="D24" s="24">
-        <v>20295</v>
+        <v>20295.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="13.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="7">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D25" s="24">
-        <v>16991</v>
+        <v>16991.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="13.2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="6">
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="B26" s="20" t="str">
         <f>music!B60</f>
         <v>Марк Григорьевич Фрадкин</v>
       </c>
       <c r="C26" s="24">
-        <v>5225</v>
+        <v>5225.0</v>
       </c>
       <c r="D26" s="24">
-        <v>32967</v>
+        <v>32967.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="13.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="6">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="B27" s="20" t="str">
         <f>music!B12</f>
         <v>Константин Яковлевич Листов</v>
       </c>
       <c r="C27" s="24">
-        <v>263</v>
+        <v>263.0</v>
       </c>
       <c r="D27" s="24">
-        <v>30565</v>
+        <v>30565.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="13.2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="7">
-        <v>28</v>
+        <v>28.0</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="24">
-        <v>9133</v>
+        <v>9133.0</v>
       </c>
       <c r="D28" s="24">
-        <v>35311</v>
+        <v>35311.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="13.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="6">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="24">
-        <v>10906</v>
+        <v>10906.0</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="13.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" s="6">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D30" s="24">
-        <v>24447</v>
+        <v>24447.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="13.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="7">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="24">
-        <v>3006</v>
+        <v>3006.0</v>
       </c>
       <c r="D31" s="24">
-        <v>25794</v>
+        <v>25794.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="13.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="6">
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="24">
-        <v>16667</v>
+        <v>16667.0</v>
       </c>
       <c r="D32" s="24">
-        <v>35111</v>
+        <v>35111.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="35.25" customHeight="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" ht="35.25" customHeight="1">
       <c r="A33" s="7">
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="24">
-        <v>7720</v>
+        <v>7720.0</v>
       </c>
       <c r="D33" s="24">
-        <v>41308</v>
+        <v>41308.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="13.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="7">
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C34" s="24">
-        <v>4897</v>
+        <v>4897.0</v>
       </c>
       <c r="D34" s="24">
-        <v>39308</v>
+        <v>39308.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="13.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="6">
-        <v>35</v>
+        <v>35.0</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D35" s="24">
-        <v>30949</v>
+        <v>30949.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="13.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="7">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C36" s="24">
-        <v>10857</v>
+        <v>10857.0</v>
       </c>
       <c r="D36" s="24">
-        <v>44641</v>
+        <v>44641.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="13.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="7">
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>132</v>
       </c>
       <c r="C37" s="24">
-        <v>18903</v>
+        <v>18903.0</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="13.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="6">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
     </row>
-    <row r="39" spans="1:5" ht="13.2">
+    <row r="39">
       <c r="A39" s="6">
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
     </row>
-    <row r="40" spans="1:5" ht="13.2">
+    <row r="40">
       <c r="A40" s="7">
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
     </row>
-    <row r="41" spans="1:5" ht="13.2">
+    <row r="41">
       <c r="A41" s="6">
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
     </row>
-    <row r="42" spans="1:5" ht="13.2">
+    <row r="42">
       <c r="A42" s="6">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
     </row>
-    <row r="43" spans="1:5" ht="13.2">
+    <row r="43">
       <c r="A43" s="7">
-        <v>43</v>
+        <v>43.0</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
     </row>
-    <row r="44" spans="1:5" ht="13.2">
+    <row r="44">
       <c r="A44" s="6">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
     </row>
-    <row r="45" spans="1:5" ht="13.2">
+    <row r="45">
       <c r="A45" s="7">
-        <v>45</v>
+        <v>45.0</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
     </row>
-    <row r="46" spans="1:5" ht="13.2">
+    <row r="46">
       <c r="A46" s="7">
-        <v>46</v>
+        <v>46.0</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
     </row>
-    <row r="47" spans="1:5" ht="13.2">
+    <row r="47">
       <c r="A47" s="6">
-        <v>47</v>
+        <v>47.0</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
     </row>
-    <row r="48" spans="1:5" ht="13.2">
+    <row r="48">
       <c r="A48" s="7">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
     </row>
-    <row r="49" spans="1:5" ht="13.2">
+    <row r="49">
       <c r="A49" s="7">
-        <v>49</v>
+        <v>49.0</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:5" ht="13.2">
+    <row r="50">
       <c r="A50" s="6">
-        <v>50</v>
+        <v>50.0</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:5" ht="13.2">
+    <row r="51">
       <c r="A51" s="6">
-        <v>51</v>
+        <v>51.0</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
-    <row r="52" spans="1:5" ht="13.2">
+    <row r="52">
       <c r="A52" s="7">
-        <v>52</v>
+        <v>52.0</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:5" ht="13.2">
+    <row r="53">
       <c r="A53" s="6">
-        <v>53</v>
+        <v>53.0</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
     </row>
-    <row r="54" spans="1:5" ht="13.2">
+    <row r="54">
       <c r="A54" s="6">
-        <v>54</v>
+        <v>54.0</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
     </row>
-    <row r="55" spans="1:5" ht="13.2">
+    <row r="55">
       <c r="A55" s="7">
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
       <c r="E55" s="20"/>
     </row>
-    <row r="56" spans="1:5" ht="13.2">
+    <row r="56">
       <c r="A56" s="6">
-        <v>56</v>
+        <v>56.0</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
     </row>
-    <row r="57" spans="1:5" ht="13.2">
+    <row r="57">
       <c r="A57" s="7">
-        <v>57</v>
+        <v>57.0</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
     </row>
-    <row r="58" spans="1:5" ht="13.2">
+    <row r="58">
       <c r="A58" s="7">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
     </row>
-    <row r="59" spans="1:5" ht="13.2">
+    <row r="59">
       <c r="A59" s="6">
-        <v>59</v>
+        <v>59.0</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
     </row>
-    <row r="60" spans="1:5" ht="13.2">
+    <row r="60">
       <c r="A60" s="7">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
     </row>
-    <row r="61" spans="1:5" ht="13.2">
+    <row r="61">
       <c r="A61" s="7">
-        <v>61</v>
+        <v>61.0</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
     </row>
-    <row r="62" spans="1:5" ht="13.2">
+    <row r="62">
       <c r="A62" s="6">
-        <v>62</v>
+        <v>62.0</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
     </row>
-    <row r="63" spans="1:5" ht="13.2">
+    <row r="63">
       <c r="A63" s="6">
-        <v>63</v>
+        <v>63.0</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
     </row>
-    <row r="64" spans="1:5" ht="13.2">
+    <row r="64">
       <c r="A64" s="7">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
-    <row r="65" spans="1:5" ht="13.2">
+    <row r="65">
       <c r="A65" s="6">
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
     </row>
-    <row r="66" spans="1:5" ht="13.2">
+    <row r="66">
       <c r="A66" s="6">
-        <v>66</v>
+        <v>66.0</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
     </row>
-    <row r="67" spans="1:5" ht="13.2">
+    <row r="67">
       <c r="A67" s="7">
-        <v>67</v>
+        <v>67.0</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
     </row>
-    <row r="68" spans="1:5" ht="13.2">
+    <row r="68">
       <c r="A68" s="6">
-        <v>68</v>
-      </c>
-      <c r="B68" s="20">
+        <v>68.0</v>
+      </c>
+      <c r="B68" s="20" t="str">
         <f>music!B104</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
     </row>
-    <row r="69" spans="1:5" ht="13.2">
+    <row r="69">
       <c r="A69" s="7">
-        <v>69</v>
-      </c>
-      <c r="B69" s="20">
+        <v>69.0</v>
+      </c>
+      <c r="B69" s="20" t="str">
         <f>music!B105</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
     </row>
-    <row r="70" spans="1:5" ht="13.2">
+    <row r="70">
       <c r="A70" s="7">
-        <v>70</v>
-      </c>
-      <c r="B70" s="20">
+        <v>70.0</v>
+      </c>
+      <c r="B70" s="20" t="str">
         <f>music!B106</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
     </row>
-    <row r="71" spans="1:5" ht="13.2">
+    <row r="71">
       <c r="A71" s="6">
-        <v>71</v>
-      </c>
-      <c r="B71" s="20">
+        <v>71.0</v>
+      </c>
+      <c r="B71" s="20" t="str">
         <f>music!B107</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
     </row>
-    <row r="72" spans="1:5" ht="13.2">
+    <row r="72">
       <c r="A72" s="7">
-        <v>72</v>
-      </c>
-      <c r="B72" s="20">
+        <v>72.0</v>
+      </c>
+      <c r="B72" s="20" t="str">
         <f>music!B108</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
     </row>
-    <row r="73" spans="1:5" ht="13.2">
+    <row r="73">
       <c r="A73" s="7">
-        <v>73</v>
-      </c>
-      <c r="B73" s="20">
+        <v>73.0</v>
+      </c>
+      <c r="B73" s="20" t="str">
         <f>music!B109</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
     </row>
-    <row r="74" spans="1:5" ht="13.2">
+    <row r="74">
       <c r="A74" s="6">
-        <v>74</v>
-      </c>
-      <c r="B74" s="20">
+        <v>74.0</v>
+      </c>
+      <c r="B74" s="20" t="str">
         <f>music!B110</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
     </row>
-    <row r="75" spans="1:5" ht="13.2">
+    <row r="75">
       <c r="A75" s="6">
-        <v>75</v>
-      </c>
-      <c r="B75" s="20">
+        <v>75.0</v>
+      </c>
+      <c r="B75" s="20" t="str">
         <f>music!B111</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
     </row>
-    <row r="76" spans="1:5" ht="13.2">
+    <row r="76">
       <c r="A76" s="7">
-        <v>76</v>
-      </c>
-      <c r="B76" s="20">
+        <v>76.0</v>
+      </c>
+      <c r="B76" s="20" t="str">
         <f>music!B112</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
     </row>
-    <row r="77" spans="1:5" ht="13.2">
+    <row r="77">
       <c r="A77" s="6">
-        <v>77</v>
-      </c>
-      <c r="B77" s="20">
+        <v>77.0</v>
+      </c>
+      <c r="B77" s="20" t="str">
         <f>music!B113</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
     </row>
-    <row r="78" spans="1:5" ht="13.2">
+    <row r="78">
       <c r="A78" s="6">
-        <v>78</v>
-      </c>
-      <c r="B78" s="20">
+        <v>78.0</v>
+      </c>
+      <c r="B78" s="20" t="str">
         <f>music!B114</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
     </row>
-    <row r="79" spans="1:5" ht="13.2">
+    <row r="79">
       <c r="A79" s="7">
-        <v>79</v>
-      </c>
-      <c r="B79" s="20">
+        <v>79.0</v>
+      </c>
+      <c r="B79" s="20" t="str">
         <f>music!B115</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
     </row>
-    <row r="80" spans="1:5" ht="13.2">
+    <row r="80">
       <c r="A80" s="6">
-        <v>80</v>
-      </c>
-      <c r="B80" s="20">
+        <v>80.0</v>
+      </c>
+      <c r="B80" s="20" t="str">
         <f>music!B116</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
     </row>
-    <row r="81" spans="1:5" ht="13.2">
+    <row r="81">
       <c r="A81" s="7">
-        <v>81</v>
-      </c>
-      <c r="B81" s="20">
+        <v>81.0</v>
+      </c>
+      <c r="B81" s="20" t="str">
         <f>music!B117</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
     </row>
-    <row r="82" spans="1:5" ht="13.2">
+    <row r="82">
       <c r="A82" s="7">
-        <v>82</v>
-      </c>
-      <c r="B82" s="20">
+        <v>82.0</v>
+      </c>
+      <c r="B82" s="20" t="str">
         <f>music!B118</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
     </row>
-    <row r="83" spans="1:5" ht="13.2">
+    <row r="83">
       <c r="A83" s="6">
-        <v>83</v>
-      </c>
-      <c r="B83" s="20">
+        <v>83.0</v>
+      </c>
+      <c r="B83" s="20" t="str">
         <f>music!B119</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
     </row>
-    <row r="84" spans="1:5" ht="13.2">
+    <row r="84">
       <c r="A84" s="7">
-        <v>84</v>
-      </c>
-      <c r="B84" s="20">
+        <v>84.0</v>
+      </c>
+      <c r="B84" s="20" t="str">
         <f>music!B120</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
     </row>
-    <row r="85" spans="1:5" ht="13.2">
+    <row r="85">
       <c r="A85" s="7">
-        <v>85</v>
-      </c>
-      <c r="B85" s="20">
+        <v>85.0</v>
+      </c>
+      <c r="B85" s="20" t="str">
         <f>music!B121</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
     </row>
-    <row r="86" spans="1:5" ht="13.2">
+    <row r="86">
       <c r="A86" s="6">
-        <v>86</v>
-      </c>
-      <c r="B86" s="20">
+        <v>86.0</v>
+      </c>
+      <c r="B86" s="20" t="str">
         <f>music!B122</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
     </row>
-    <row r="87" spans="1:5" ht="13.2">
+    <row r="87">
       <c r="A87" s="6">
-        <v>87</v>
-      </c>
-      <c r="B87" s="20">
+        <v>87.0</v>
+      </c>
+      <c r="B87" s="20" t="str">
         <f>music!B123</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
     </row>
-    <row r="88" spans="1:5" ht="13.2">
+    <row r="88">
       <c r="A88" s="7">
-        <v>88</v>
-      </c>
-      <c r="B88" s="20">
+        <v>88.0</v>
+      </c>
+      <c r="B88" s="20" t="str">
         <f>music!B124</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
     </row>
-    <row r="89" spans="1:5" ht="13.2">
+    <row r="89">
       <c r="A89" s="6">
-        <v>89</v>
-      </c>
-      <c r="B89" s="20">
+        <v>89.0</v>
+      </c>
+      <c r="B89" s="20" t="str">
         <f>music!B125</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
     </row>
-    <row r="90" spans="1:5" ht="13.2">
+    <row r="90">
       <c r="A90" s="6">
-        <v>90</v>
-      </c>
-      <c r="B90" s="20">
+        <v>90.0</v>
+      </c>
+      <c r="B90" s="20" t="str">
         <f>music!B126</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
     </row>
-    <row r="91" spans="1:5" ht="13.2">
+    <row r="91">
       <c r="A91" s="7">
-        <v>91</v>
-      </c>
-      <c r="B91" s="20">
+        <v>91.0</v>
+      </c>
+      <c r="B91" s="20" t="str">
         <f>music!B127</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
     </row>
-    <row r="92" spans="1:5" ht="13.2">
+    <row r="92">
       <c r="A92" s="6">
-        <v>92</v>
-      </c>
-      <c r="B92" s="20">
+        <v>92.0</v>
+      </c>
+      <c r="B92" s="20" t="str">
         <f>music!B128</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
     </row>
-    <row r="93" spans="1:5" ht="13.2">
+    <row r="93">
       <c r="A93" s="7">
-        <v>93</v>
-      </c>
-      <c r="B93" s="20">
+        <v>93.0</v>
+      </c>
+      <c r="B93" s="20" t="str">
         <f>music!B129</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
     </row>
-    <row r="94" spans="1:5" ht="13.2">
+    <row r="94">
       <c r="A94" s="7">
-        <v>94</v>
-      </c>
-      <c r="B94" s="20">
+        <v>94.0</v>
+      </c>
+      <c r="B94" s="20" t="str">
         <f>music!B130</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
     </row>
-    <row r="95" spans="1:5" ht="13.2">
+    <row r="95">
       <c r="A95" s="6">
-        <v>95</v>
-      </c>
-      <c r="B95" s="20">
+        <v>95.0</v>
+      </c>
+      <c r="B95" s="20" t="str">
         <f>music!B131</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
     </row>
-    <row r="96" spans="1:5" ht="13.2">
+    <row r="96">
       <c r="A96" s="7">
-        <v>96</v>
-      </c>
-      <c r="B96" s="20">
+        <v>96.0</v>
+      </c>
+      <c r="B96" s="20" t="str">
         <f>music!B132</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
     </row>
-    <row r="97" spans="1:5" ht="13.2">
+    <row r="97">
       <c r="A97" s="7">
-        <v>97</v>
-      </c>
-      <c r="B97" s="20">
+        <v>97.0</v>
+      </c>
+      <c r="B97" s="20" t="str">
         <f>music!B133</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
     </row>
-    <row r="98" spans="1:5" ht="13.2">
+    <row r="98">
       <c r="A98" s="6">
-        <v>98</v>
-      </c>
-      <c r="B98" s="20">
+        <v>98.0</v>
+      </c>
+      <c r="B98" s="20" t="str">
         <f>music!B134</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
     </row>
-    <row r="99" spans="1:5" ht="13.2">
+    <row r="99">
       <c r="A99" s="6">
-        <v>99</v>
-      </c>
-      <c r="B99" s="20">
+        <v>99.0</v>
+      </c>
+      <c r="B99" s="20" t="str">
         <f>music!B135</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
     </row>
-    <row r="100" spans="1:5" ht="13.2">
+    <row r="100">
       <c r="A100" s="7">
-        <v>100</v>
-      </c>
-      <c r="B100" s="20">
+        <v>100.0</v>
+      </c>
+      <c r="B100" s="20" t="str">
         <f>music!B136</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
     </row>
-    <row r="101" spans="1:5" ht="13.2">
+    <row r="101">
       <c r="A101" s="6">
-        <v>101</v>
-      </c>
-      <c r="B101" s="20">
+        <v>101.0</v>
+      </c>
+      <c r="B101" s="20" t="str">
         <f>music!B137</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
     </row>
-    <row r="102" spans="1:5" ht="13.2">
+    <row r="102">
       <c r="A102" s="6">
-        <v>102</v>
-      </c>
-      <c r="B102" s="20">
+        <v>102.0</v>
+      </c>
+      <c r="B102" s="20" t="str">
         <f>music!B138</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
     </row>
-    <row r="103" spans="1:5" ht="13.2">
+    <row r="103">
       <c r="A103" s="7">
-        <v>103</v>
-      </c>
-      <c r="B103" s="20">
+        <v>103.0</v>
+      </c>
+      <c r="B103" s="20" t="str">
         <f>music!B139</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
     </row>
-    <row r="104" spans="1:5" ht="13.2">
+    <row r="104">
       <c r="A104" s="6">
-        <v>104</v>
-      </c>
-      <c r="B104" s="20">
+        <v>104.0</v>
+      </c>
+      <c r="B104" s="20" t="str">
         <f>music!B140</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
     </row>
-    <row r="105" spans="1:5" ht="13.2">
+    <row r="105">
       <c r="A105" s="7">
-        <v>105</v>
-      </c>
-      <c r="B105" s="20">
+        <v>105.0</v>
+      </c>
+      <c r="B105" s="20" t="str">
         <f>music!B141</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
     </row>
-    <row r="106" spans="1:5" ht="13.2">
+    <row r="106">
       <c r="A106" s="7">
-        <v>106</v>
-      </c>
-      <c r="B106" s="20">
+        <v>106.0</v>
+      </c>
+      <c r="B106" s="20" t="str">
         <f>music!B142</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
-    <row r="107" spans="1:5" ht="13.2">
+    <row r="107">
       <c r="A107" s="6">
-        <v>107</v>
-      </c>
-      <c r="B107" s="20">
+        <v>107.0</v>
+      </c>
+      <c r="B107" s="20" t="str">
         <f>music!B143</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C107" s="20"/>
       <c r="D107" s="20"/>
       <c r="E107" s="20"/>
     </row>
-    <row r="108" spans="1:5" ht="13.2">
+    <row r="108">
       <c r="A108" s="7">
-        <v>108</v>
-      </c>
-      <c r="B108" s="20">
+        <v>108.0</v>
+      </c>
+      <c r="B108" s="20" t="str">
         <f>music!B144</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
     </row>
-    <row r="109" spans="1:5" ht="13.2">
+    <row r="109">
       <c r="A109" s="7">
-        <v>109</v>
-      </c>
-      <c r="B109" s="20">
+        <v>109.0</v>
+      </c>
+      <c r="B109" s="20" t="str">
         <f>music!B145</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C109" s="20"/>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
     </row>
-    <row r="110" spans="1:5" ht="13.2">
+    <row r="110">
       <c r="A110" s="20"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
     </row>
-    <row r="111" spans="1:5" ht="13.2">
+    <row r="111">
       <c r="A111" s="20"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
       <c r="D111" s="20"/>
       <c r="E111" s="20"/>
     </row>
-    <row r="112" spans="1:5" ht="13.2">
+    <row r="112">
       <c r="A112" s="20"/>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
     </row>
-    <row r="113" spans="1:5" ht="13.2">
+    <row r="113">
       <c r="A113" s="20"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
     </row>
-    <row r="114" spans="1:5" ht="13.2">
+    <row r="114">
       <c r="A114" s="20"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
     </row>
-    <row r="115" spans="1:5" ht="13.2">
+    <row r="115">
       <c r="A115" s="20"/>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
     </row>
-    <row r="116" spans="1:5" ht="13.2">
+    <row r="116">
       <c r="A116" s="20"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
     </row>
-    <row r="117" spans="1:5" ht="13.2">
+    <row r="117">
       <c r="A117" s="20"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
     </row>
-    <row r="118" spans="1:5" ht="13.2">
+    <row r="118">
       <c r="A118" s="20"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
     </row>
-    <row r="119" spans="1:5" ht="13.2">
+    <row r="119">
       <c r="A119" s="20"/>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
     </row>
-    <row r="120" spans="1:5" ht="13.2">
+    <row r="120">
       <c r="A120" s="20"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
       <c r="D120" s="20"/>
       <c r="E120" s="20"/>
     </row>
-    <row r="121" spans="1:5" ht="13.2">
+    <row r="121">
       <c r="A121" s="20"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
       <c r="D121" s="20"/>
       <c r="E121" s="20"/>
     </row>
-    <row r="122" spans="1:5" ht="13.2">
+    <row r="122">
       <c r="A122" s="20"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
     </row>
-    <row r="123" spans="1:5" ht="13.2">
+    <row r="123">
       <c r="A123" s="20"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
     </row>
-    <row r="124" spans="1:5" ht="13.2">
+    <row r="124">
       <c r="A124" s="20"/>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -5712,499 +5696,488 @@
       <c r="E124" s="20"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" customWidth="1"/>
-    <col min="2" max="2" width="46.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" customWidth="1"/>
-    <col min="5" max="5" width="56.5546875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="5.43"/>
+    <col customWidth="1" min="2" max="2" width="46.14"/>
+    <col customWidth="1" min="3" max="3" width="20.14"/>
+    <col customWidth="1" min="4" max="4" width="23.86"/>
+    <col customWidth="1" min="5" max="5" width="56.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="D1" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="E1" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="27" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="29">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="C2" s="30" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="29">
-        <v>1</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="D2" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="E2" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="D2" s="31" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="29">
+        <v>5.0</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="C3" s="30" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="29">
-        <v>5</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="D3" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="E3" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="D3" s="31" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="29">
+        <v>9.0</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="29">
-        <v>9</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="D4" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="E4" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="31" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="29">
+        <v>21.0</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="29">
-        <v>21</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="D5" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="E5" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="31" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="29">
+        <v>37.0</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="C6" s="30" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="29">
-        <v>37</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>295</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="33" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29">
+        <v>38.0</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="29">
-        <v>38</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="D7" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="E7" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="31" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="33"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29">
+        <v>43.0</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="C9" s="30" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="29">
-        <v>40</v>
-      </c>
-      <c r="B8" s="29" t="s">
+      <c r="D9" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="E9" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="D8" s="31" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="29">
+        <v>45.0</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="C10" s="30" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="29">
-        <v>43</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>380</v>
-      </c>
-      <c r="C9" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="E9" s="33" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="29">
+        <v>46.0</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="29">
-        <v>45</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="C11" s="30" t="s">
         <v>308</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="29">
-        <v>46</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>313</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29">
+        <v>48.0</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29">
+        <v>56.0</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="29">
-        <v>48</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>315</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="29">
-        <v>56</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>320</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="33" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="29">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="33" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29">
+        <v>69.0</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29">
+        <v>107.0</v>
+      </c>
+      <c r="B16" s="29" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="29">
-        <v>69</v>
-      </c>
-      <c r="B15" s="29" t="s">
+      <c r="C16" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="E15" s="33" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" s="29">
+        <v>111.0</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="29">
-        <v>107</v>
-      </c>
-      <c r="B16" s="29" t="s">
+      <c r="C17" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="D17" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="E16" s="33" t="s">
+    </row>
+    <row r="18">
+      <c r="A18" s="29">
+        <v>112.0</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="29">
-        <v>111</v>
-      </c>
-      <c r="B17" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>335</v>
       </c>
-      <c r="E17" s="33" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="29">
+        <v>120.0</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="29">
-        <v>112</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="C19" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D19" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>339</v>
       </c>
-      <c r="E18" s="33" t="s">
+    </row>
+    <row r="20">
+      <c r="A20" s="29">
+        <v>126.0</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="29">
-        <v>120</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="E20" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="E19" s="33" t="s">
+    </row>
+    <row r="21">
+      <c r="A21" s="29">
+        <v>134.0</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="29">
-        <v>126</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="E21" s="33" t="s">
         <v>347</v>
       </c>
-      <c r="E20" s="33" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" s="29">
+        <v>142.0</v>
+      </c>
+      <c r="B22" s="29" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="29">
-        <v>134</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>349</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="29">
-        <v>142</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>354</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="33" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="29">
-        <v>143</v>
+        <v>143.0</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="29">
-        <v>160</v>
+        <v>160.0</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="29">
-        <v>163</v>
+        <v>163.0</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="33" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="29">
-        <v>165</v>
+        <v>165.0</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="33" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29">
+        <v>167.0</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29">
+        <v>192.0</v>
+      </c>
+      <c r="B28" s="29" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="29">
-        <v>167</v>
-      </c>
-      <c r="B27" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>368</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="29">
-        <v>192</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>372</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>373</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="33" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="29">
-        <v>221</v>
+        <v>221.0</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/history_sounds.xlsx
+++ b/data/history_sounds.xlsx
@@ -1,14 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="132" yWindow="516" windowWidth="30396" windowHeight="15276"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="music" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="composers" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="events" sheetId="3" r:id="rId7"/>
+    <sheet name="music" sheetId="1" r:id="rId1"/>
+    <sheet name="composers" sheetId="2" r:id="rId2"/>
+    <sheet name="events" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -426,9 +429,6 @@
     <t>Илья Алексеевич Шатров</t>
   </si>
   <si>
-    <t>вальс «На сопках Маньчжурии»</t>
-  </si>
-  <si>
     <t>Русский вальс, посвященный погибшим в Русско-японской войне воинам 214-го резервного Мошканского пехотного полка. В феврале 1904 полк попал в японское окружение, в критический этап командир отдал приказ "Знамя и оркестр - вперед!". Капельмейстер под колонный марш повел оркестр вперед за знаменем полка. Воодушевленные солдаты ринулись в штыковую атаку. В ходе боя полк ценой огромных потерь прорвал окружение.</t>
   </si>
   <si>
@@ -1140,82 +1140,93 @@
   </si>
   <si>
     <t>XXII Летние Олимпийские игры проходили с 19 июля по 3 августа 1980 года в Москве, СССР. Это были первые Игры в Восточной Европе и социалистической стране. Несмотря на бойкот более 60 стран, в соревнованиях приняли участие атлеты из 80 государств. СССР занял первое место в общекомандном зачёте</t>
+  </si>
+  <si>
+    <t>Вальс «На сопках Маньчжурии»</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="d mmmm yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
-    <numFmt numFmtId="166" formatCode="d.m.yyyy"/>
+    <numFmt numFmtId="164" formatCode="d\ mmmm\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="166" formatCode="d\.m\.yyyy"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="13">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
@@ -1225,7 +1236,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1241,17 +1252,25 @@
     </fill>
   </fills>
   <borders count="8">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -1266,17 +1285,20 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1291,6 +1313,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1299,9 +1322,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1313,8 +1338,11 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1324,131 +1352,78 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1456,7 +1431,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1646,25 +1621,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H152"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.86"/>
-    <col customWidth="1" min="2" max="2" width="33.86"/>
-    <col customWidth="1" min="3" max="3" width="42.29"/>
-    <col customWidth="1" min="4" max="4" width="24.0"/>
-    <col customWidth="1" min="5" max="5" width="74.0"/>
-    <col customWidth="1" min="8" max="8" width="58.14"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="74" customWidth="1"/>
+    <col min="8" max="8" width="58.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="13.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1690,9 +1668,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="13.8">
       <c r="A2" s="6">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -1701,24 +1679,24 @@
         <v>9</v>
       </c>
       <c r="D2" s="8">
-        <v>1925.0</v>
+        <v>1925</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="9">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="13.2">
       <c r="A3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>12</v>
@@ -1727,24 +1705,24 @@
         <v>13</v>
       </c>
       <c r="D3" s="6">
-        <v>1914.0</v>
+        <v>1914</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G3" s="9">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" ht="13.2">
       <c r="A4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>16</v>
@@ -1759,16 +1737,16 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" ht="13.2">
       <c r="A5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>16</v>
@@ -1777,24 +1755,24 @@
         <v>21</v>
       </c>
       <c r="D5" s="13">
-        <v>1915.0</v>
+        <v>1915</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="4">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="G5" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" ht="13.2">
       <c r="A6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>24</v>
@@ -1803,24 +1781,24 @@
         <v>25</v>
       </c>
       <c r="D6" s="6">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="G6" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" ht="13.2">
       <c r="A7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>28</v>
@@ -1829,24 +1807,24 @@
         <v>29</v>
       </c>
       <c r="D7" s="6">
-        <v>1965.0</v>
+        <v>1965</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="G7" s="9">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" ht="13.2">
       <c r="A8" s="6">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>32</v>
@@ -1855,24 +1833,24 @@
         <v>33</v>
       </c>
       <c r="D8" s="6">
-        <v>1940.0</v>
+        <v>1940</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G8" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" ht="13.2">
       <c r="A9" s="14">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
@@ -1881,24 +1859,24 @@
         <v>37</v>
       </c>
       <c r="D9" s="6">
-        <v>1929.0</v>
+        <v>1929</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G9" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" ht="13.2">
       <c r="A10" s="6">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>36</v>
@@ -1907,24 +1885,24 @@
         <v>40</v>
       </c>
       <c r="D10" s="6">
-        <v>1930.0</v>
+        <v>1930</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="4">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="G10" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" ht="13.2">
       <c r="A11" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -1933,24 +1911,24 @@
         <v>43</v>
       </c>
       <c r="D11" s="15">
-        <v>15155.0</v>
+        <v>15155</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="4">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="G11" s="9">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" ht="13.2">
       <c r="A12" s="6">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>46</v>
@@ -1959,24 +1937,24 @@
         <v>47</v>
       </c>
       <c r="D12" s="6">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="4">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="G12" s="9">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" ht="13.2">
       <c r="A13" s="6">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>32</v>
@@ -1985,24 +1963,24 @@
         <v>50</v>
       </c>
       <c r="D13" s="16">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>51</v>
       </c>
       <c r="F13" s="4">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="G13" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" ht="13.2">
       <c r="A14" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>53</v>
@@ -2011,24 +1989,24 @@
         <v>54</v>
       </c>
       <c r="D14" s="6">
-        <v>1964.0</v>
+        <v>1964</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="4">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G14" s="9">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" ht="13.2">
       <c r="A15" s="6">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>57</v>
@@ -2037,24 +2015,24 @@
         <v>58</v>
       </c>
       <c r="D15" s="6">
-        <v>1942.0</v>
+        <v>1942</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="4">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="G15" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" ht="13.2">
       <c r="A16" s="6">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>61</v>
@@ -2063,24 +2041,24 @@
         <v>62</v>
       </c>
       <c r="D16" s="6">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="4">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="G16" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" ht="13.2">
       <c r="A17" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>24</v>
@@ -2089,24 +2067,24 @@
         <v>65</v>
       </c>
       <c r="D17" s="6">
-        <v>1938.0</v>
+        <v>1938</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F17" s="4">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="G17" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" ht="13.2">
       <c r="A18" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>32</v>
@@ -2115,24 +2093,24 @@
         <v>68</v>
       </c>
       <c r="D18" s="6">
-        <v>1945.0</v>
+        <v>1945</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="4">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="G18" s="9">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" ht="13.2">
       <c r="A19" s="6">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>71</v>
@@ -2141,24 +2119,24 @@
         <v>72</v>
       </c>
       <c r="D19" s="17">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>73</v>
       </c>
       <c r="F19" s="4">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="G19" s="9">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" ht="13.2">
       <c r="A20" s="19">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>75</v>
@@ -2167,24 +2145,24 @@
         <v>76</v>
       </c>
       <c r="D20" s="6">
-        <v>1951.0</v>
+        <v>1951</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="F20" s="4">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="G20" s="9">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" ht="13.2">
       <c r="A21" s="19">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>79</v>
@@ -2193,24 +2171,24 @@
         <v>80</v>
       </c>
       <c r="D21" s="6">
-        <v>1953.0</v>
+        <v>1953</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="4">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="G21" s="9">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" ht="13.2">
       <c r="A22" s="19">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>57</v>
@@ -2219,24 +2197,24 @@
         <v>83</v>
       </c>
       <c r="D22" s="15">
-        <v>22555.0</v>
+        <v>22555</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="F22" s="4">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" ht="13.2">
       <c r="A23" s="19">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>86</v>
@@ -2245,24 +2223,24 @@
         <v>87</v>
       </c>
       <c r="D23" s="6">
-        <v>1983.0</v>
+        <v>1983</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>88</v>
       </c>
       <c r="F23" s="4">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="G23" s="9">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" ht="13.2">
       <c r="A24" s="19">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
@@ -2271,24 +2249,24 @@
         <v>90</v>
       </c>
       <c r="D24" s="6">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="4">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="G24" s="4">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" ht="13.2">
       <c r="A25" s="19">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>93</v>
@@ -2297,24 +2275,24 @@
         <v>94</v>
       </c>
       <c r="D25" s="6">
-        <v>1961.0</v>
+        <v>1961</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>95</v>
       </c>
       <c r="F25" s="4">
-        <v>163.0</v>
+        <v>163</v>
       </c>
       <c r="G25" s="9">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" ht="13.2">
       <c r="A26" s="19">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>61</v>
@@ -2323,24 +2301,24 @@
         <v>97</v>
       </c>
       <c r="D26" s="6">
-        <v>1958.0</v>
+        <v>1958</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
       </c>
       <c r="F26" s="4">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="G26" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" ht="13.2">
       <c r="A27" s="19">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>79</v>
@@ -2355,18 +2333,18 @@
         <v>102</v>
       </c>
       <c r="F27" s="4">
-        <v>165.0</v>
+        <v>165</v>
       </c>
       <c r="G27" s="9">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" ht="13.2">
       <c r="A28" s="19">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
@@ -2375,24 +2353,24 @@
         <v>104</v>
       </c>
       <c r="D28" s="6">
-        <v>1979.0</v>
+        <v>1979</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
       </c>
       <c r="F28" s="4">
-        <v>165.0</v>
+        <v>165</v>
       </c>
       <c r="G28" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" ht="13.2">
       <c r="A29" s="19">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>107</v>
@@ -2401,24 +2379,24 @@
         <v>108</v>
       </c>
       <c r="D29" s="6">
-        <v>1960.0</v>
+        <v>1960</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>109</v>
       </c>
       <c r="F29" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G29" s="9">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" ht="13.2">
       <c r="A30" s="19">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>111</v>
@@ -2427,24 +2405,24 @@
         <v>112</v>
       </c>
       <c r="D30" s="6">
-        <v>1957.0</v>
+        <v>1957</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
       </c>
       <c r="F30" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G30" s="9">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" ht="13.2">
       <c r="A31" s="19">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>115</v>
@@ -2453,24 +2431,24 @@
         <v>116</v>
       </c>
       <c r="D31" s="6">
-        <v>1947.0</v>
+        <v>1947</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="4">
-        <v>167.0</v>
+        <v>167</v>
       </c>
       <c r="G31" s="9">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" ht="13.2">
       <c r="A32" s="19">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>119</v>
@@ -2479,24 +2457,24 @@
         <v>120</v>
       </c>
       <c r="D32" s="6">
-        <v>1977.0</v>
+        <v>1977</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
       </c>
       <c r="F32" s="4">
-        <v>160.0</v>
+        <v>160</v>
       </c>
       <c r="G32" s="9">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:8" ht="13.2">
       <c r="A33" s="19">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>61</v>
@@ -2505,46 +2483,46 @@
         <v>123</v>
       </c>
       <c r="D33" s="6">
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>124</v>
       </c>
       <c r="F33" s="4">
-        <v>221.0</v>
+        <v>221</v>
       </c>
       <c r="G33" s="9">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" ht="13.2">
       <c r="A34" s="19">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="6">
-        <v>1981.0</v>
+        <v>1981</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
       </c>
       <c r="F34" s="4">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" ht="13.2">
       <c r="A35" s="19">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>57</v>
@@ -2553,24 +2531,24 @@
         <v>129</v>
       </c>
       <c r="D35" s="6">
-        <v>1957.0</v>
+        <v>1957</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>130</v>
       </c>
       <c r="F35" s="4">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G35" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" ht="13.2">
       <c r="A36" s="19">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>132</v>
@@ -2579,222 +2557,222 @@
         <v>133</v>
       </c>
       <c r="D36" s="6">
-        <v>1981.0</v>
+        <v>1981</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
       </c>
       <c r="F36" s="4">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="G36" s="9">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" ht="13.2">
       <c r="A37" s="19">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>136</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1906</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="6">
-        <v>1906.0</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9">
+        <v>3</v>
+      </c>
+      <c r="H37" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="F37" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="H37" s="11" t="s">
+    </row>
+    <row r="38" spans="1:8" ht="13.2">
+      <c r="A38" s="19">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19">
-        <v>40.0</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="D38" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D38" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9">
+        <v>4</v>
+      </c>
+      <c r="H38" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F38" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="H38" s="11" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="13.2">
+      <c r="A39" s="19">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19">
-        <v>41.0</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="D39" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>5</v>
+      </c>
+      <c r="H39" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D39" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="H39" s="11" t="s">
+    </row>
+    <row r="40" spans="1:8" ht="13.2">
+      <c r="A40" s="19">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="19">
-        <v>42.0</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>6</v>
+      </c>
+      <c r="H40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F40" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>6.0</v>
-      </c>
-      <c r="H40" s="11" t="s">
+    </row>
+    <row r="41" spans="1:8" ht="13.2">
+      <c r="A41" s="19">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19">
-        <v>43.0</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D41" s="6">
+        <v>1912</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="6">
-        <v>1912.0</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>7</v>
+      </c>
+      <c r="H41" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F41" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>7.0</v>
-      </c>
-      <c r="H41" s="11" t="s">
+    </row>
+    <row r="42" spans="1:8" ht="13.2">
+      <c r="A42" s="19">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19">
-        <v>44.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="6">
+        <v>1904</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="6">
-        <v>1904.0</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H42" s="11" t="s">
+    </row>
+    <row r="43" spans="1:8" ht="13.2">
+      <c r="A43" s="19">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="D43" s="6">
+        <v>1905</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D43" s="6">
-        <v>1905.0</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:8" ht="13.2">
       <c r="A44" s="19">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1920</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D44" s="6">
-        <v>1920.0</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="F44" s="4">
+        <v>45</v>
+      </c>
+      <c r="G44" s="9">
+        <v>9</v>
+      </c>
+      <c r="H44" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F44" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:8" ht="13.2">
       <c r="A45" s="19"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -2802,393 +2780,393 @@
       <c r="E45" s="6"/>
       <c r="H45" s="20"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:8" ht="13.2">
       <c r="A46" s="19">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6">
+        <v>1936</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D46" s="6">
-        <v>1936.0</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="4">
+        <v>46</v>
+      </c>
+      <c r="G46" s="9">
+        <v>11</v>
+      </c>
+      <c r="H46" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F46" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>11.0</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:8" ht="13.2">
       <c r="A47" s="19">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1935</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="6">
-        <v>1935.0</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="F47" s="4">
+        <v>45</v>
+      </c>
+      <c r="G47" s="9">
+        <v>8</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F47" s="4">
-        <v>45.0</v>
-      </c>
-      <c r="G47" s="9">
-        <v>8.0</v>
-      </c>
-      <c r="H47" s="11" t="s">
+    </row>
+    <row r="48" spans="1:8" ht="13.2">
+      <c r="A48" s="19">
+        <v>50</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="19">
-        <v>50.0</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="6">
+        <v>1910</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D48" s="6">
-        <v>1910.0</v>
-      </c>
-      <c r="E48" s="6" t="s">
+      <c r="F48" s="4">
+        <v>5</v>
+      </c>
+      <c r="G48" s="4">
+        <v>12</v>
+      </c>
+      <c r="H48" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="F48" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G48" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:8" ht="13.2">
       <c r="A49" s="19">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1924</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="6">
-        <v>1924.0</v>
-      </c>
-      <c r="E49" s="6" t="s">
+      <c r="F49" s="4">
+        <v>43</v>
+      </c>
+      <c r="G49" s="4">
+        <v>25</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F49" s="4">
-        <v>43.0</v>
-      </c>
-      <c r="G49" s="4">
-        <v>25.0</v>
-      </c>
-      <c r="H49" s="11" t="s">
+    </row>
+    <row r="50" spans="1:8" ht="13.2">
+      <c r="A50" s="19">
+        <v>52</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19">
-        <v>52.0</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="D50" s="6">
+        <v>1917</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D50" s="6">
-        <v>1917.0</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="F50" s="4">
+        <v>21</v>
+      </c>
+      <c r="G50" s="9">
+        <v>14</v>
+      </c>
+      <c r="H50" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="F50" s="4">
-        <v>21.0</v>
-      </c>
-      <c r="G50" s="9">
-        <v>14.0</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:8" ht="13.2">
       <c r="A51" s="19">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="E51" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="H51" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="H51" s="11" t="s">
+    </row>
+    <row r="52" spans="1:8" ht="13.2">
+      <c r="A52" s="19">
+        <v>54</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19">
-        <v>54.0</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="D52" s="6">
+        <v>1974</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D52" s="6">
-        <v>1974.0</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="4">
+        <v>107</v>
+      </c>
+      <c r="G52" s="9">
+        <v>16</v>
+      </c>
+      <c r="H52" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="F52" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G52" s="9">
-        <v>16.0</v>
-      </c>
-      <c r="H52" s="11" t="s">
+    </row>
+    <row r="53" spans="1:8" ht="13.2">
+      <c r="A53" s="19">
+        <v>55</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19">
-        <v>55.0</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="D53" s="6">
+        <v>1975</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="6">
-        <v>1975.0</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="F53" s="4">
+        <v>107</v>
+      </c>
+      <c r="G53" s="9">
+        <v>17</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="F53" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G53" s="9">
-        <v>17.0</v>
-      </c>
-      <c r="H53" s="11" t="s">
+    </row>
+    <row r="54" spans="1:8" ht="13.2">
+      <c r="A54" s="19">
+        <v>56</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19">
-        <v>56.0</v>
-      </c>
-      <c r="B54" s="6" t="s">
+      <c r="C54" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="D54" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D54" s="6">
-        <v>1971.0</v>
-      </c>
-      <c r="E54" s="6" t="s">
+      <c r="F54" s="4">
+        <v>107</v>
+      </c>
+      <c r="G54" s="9">
+        <v>15</v>
+      </c>
+      <c r="H54" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="F54" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G54" s="9">
-        <v>15.0</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:8" ht="13.2">
       <c r="A55" s="19">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D55" s="22">
+        <v>1946</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D55" s="22">
-        <v>1946.0</v>
-      </c>
-      <c r="E55" s="6" t="s">
+      <c r="F55" s="4">
+        <v>107</v>
+      </c>
+      <c r="G55" s="9">
+        <v>8</v>
+      </c>
+      <c r="H55" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F55" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G55" s="9">
-        <v>8.0</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:8" ht="13.2">
       <c r="A56" s="19">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1947</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D56" s="6">
-        <v>1947.0</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="4">
+        <v>107</v>
+      </c>
+      <c r="G56" s="9">
+        <v>18</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F56" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>18.0</v>
-      </c>
-      <c r="H56" s="11" t="s">
+    </row>
+    <row r="57" spans="1:8" ht="13.2">
+      <c r="A57" s="19">
+        <v>59</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="19">
-        <v>59.0</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="C57" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>1974</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D57" s="6">
-        <v>1974.0</v>
-      </c>
-      <c r="E57" s="6" t="s">
+      <c r="F57" s="4">
+        <v>107</v>
+      </c>
+      <c r="G57" s="9">
+        <v>19</v>
+      </c>
+      <c r="H57" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="H57" s="11" t="s">
+    </row>
+    <row r="58" spans="1:8" ht="13.2">
+      <c r="A58" s="19">
+        <v>60</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="19">
-        <v>60.0</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="C58" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="D58" s="6">
+        <v>1975</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D58" s="6">
-        <v>1975.0</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="F58" s="4">
+        <v>107</v>
+      </c>
+      <c r="G58" s="9">
+        <v>20</v>
+      </c>
+      <c r="H58" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F58" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G58" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="H58" s="18" t="s">
+    </row>
+    <row r="59" spans="1:8" ht="13.2">
+      <c r="A59" s="19">
+        <v>61</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19">
-        <v>61.0</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="C59" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="6">
+        <v>1969</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D59" s="6">
-        <v>1969.0</v>
-      </c>
-      <c r="E59" s="6" t="s">
+      <c r="F59" s="4">
+        <v>107</v>
+      </c>
+      <c r="G59" s="9">
+        <v>21</v>
+      </c>
+      <c r="H59" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F59" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G59" s="9">
-        <v>21.0</v>
-      </c>
-      <c r="H59" s="11" t="s">
+    </row>
+    <row r="60" spans="1:8" ht="13.2">
+      <c r="A60" s="19">
+        <v>62</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="19">
-        <v>62.0</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="C60" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6">
+        <v>1971</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D60" s="6">
-        <v>1971.0</v>
-      </c>
-      <c r="E60" s="6" t="s">
+      <c r="F60" s="4">
+        <v>107</v>
+      </c>
+      <c r="G60" s="9">
+        <v>26</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F60" s="4">
-        <v>107.0</v>
-      </c>
-      <c r="G60" s="9">
-        <v>26.0</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61" ht="18.0" customHeight="1">
+    </row>
+    <row r="61" spans="1:8" ht="18" customHeight="1">
       <c r="A61" s="19">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -3196,9 +3174,9 @@
       <c r="E61" s="20"/>
       <c r="H61" s="20"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:8" ht="13.2">
       <c r="A62" s="19">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
@@ -3206,9 +3184,9 @@
       <c r="E62" s="20"/>
       <c r="H62" s="20"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:8" ht="13.2">
       <c r="A63" s="19">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -3216,9 +3194,9 @@
       <c r="E63" s="20"/>
       <c r="H63" s="20"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:8" ht="13.2">
       <c r="A64" s="19">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
@@ -3226,9 +3204,9 @@
       <c r="E64" s="20"/>
       <c r="H64" s="20"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:8" ht="13.2">
       <c r="A65" s="19">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -3236,9 +3214,9 @@
       <c r="E65" s="20"/>
       <c r="H65" s="20"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:8" ht="13.2">
       <c r="A66" s="19">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -3246,9 +3224,9 @@
       <c r="E66" s="20"/>
       <c r="H66" s="20"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:8" ht="13.2">
       <c r="A67" s="19">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -3256,9 +3234,9 @@
       <c r="E67" s="20"/>
       <c r="H67" s="20"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:8" ht="13.2">
       <c r="A68" s="19">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -3266,9 +3244,9 @@
       <c r="E68" s="20"/>
       <c r="H68" s="20"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:8" ht="13.2">
       <c r="A69" s="19">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -3276,9 +3254,9 @@
       <c r="E69" s="20"/>
       <c r="H69" s="20"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:8" ht="13.2">
       <c r="A70" s="19">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -3286,9 +3264,9 @@
       <c r="E70" s="20"/>
       <c r="H70" s="20"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:8" ht="13.2">
       <c r="A71" s="19">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -3296,9 +3274,9 @@
       <c r="E71" s="20"/>
       <c r="H71" s="20"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:8" ht="13.2">
       <c r="A72" s="19">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -3306,9 +3284,9 @@
       <c r="E72" s="20"/>
       <c r="H72" s="20"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:8" ht="13.2">
       <c r="A73" s="19">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -3316,9 +3294,9 @@
       <c r="E73" s="20"/>
       <c r="H73" s="20"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:8" ht="13.2">
       <c r="A74" s="19">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -3326,9 +3304,9 @@
       <c r="E74" s="20"/>
       <c r="H74" s="20"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:8" ht="13.2">
       <c r="A75" s="19">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -3336,9 +3314,9 @@
       <c r="E75" s="20"/>
       <c r="H75" s="20"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:8" ht="13.2">
       <c r="A76" s="19">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
@@ -3346,9 +3324,9 @@
       <c r="E76" s="20"/>
       <c r="H76" s="20"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:8" ht="13.2">
       <c r="A77" s="19">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
@@ -3356,9 +3334,9 @@
       <c r="E77" s="20"/>
       <c r="H77" s="20"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:8" ht="13.2">
       <c r="A78" s="19">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -3366,9 +3344,9 @@
       <c r="E78" s="20"/>
       <c r="H78" s="20"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:8" ht="13.2">
       <c r="A79" s="19">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
@@ -3376,9 +3354,9 @@
       <c r="E79" s="20"/>
       <c r="H79" s="20"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:8" ht="13.2">
       <c r="A80" s="19">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -3386,9 +3364,9 @@
       <c r="E80" s="20"/>
       <c r="H80" s="20"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:8" ht="13.2">
       <c r="A81" s="19">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -3396,9 +3374,9 @@
       <c r="E81" s="20"/>
       <c r="H81" s="20"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:8" ht="13.2">
       <c r="A82" s="19">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
@@ -3406,9 +3384,9 @@
       <c r="E82" s="20"/>
       <c r="H82" s="20"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:8" ht="13.2">
       <c r="A83" s="19">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
@@ -3416,9 +3394,9 @@
       <c r="E83" s="20"/>
       <c r="H83" s="20"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:8" ht="13.2">
       <c r="A84" s="19">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -3426,9 +3404,9 @@
       <c r="E84" s="20"/>
       <c r="H84" s="20"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:8" ht="13.2">
       <c r="A85" s="19">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -3436,9 +3414,9 @@
       <c r="E85" s="20"/>
       <c r="H85" s="20"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:8" ht="13.2">
       <c r="A86" s="19">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -3446,9 +3424,9 @@
       <c r="E86" s="20"/>
       <c r="H86" s="20"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:8" ht="13.2">
       <c r="A87" s="19">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -3456,9 +3434,9 @@
       <c r="E87" s="20"/>
       <c r="H87" s="20"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:8" ht="13.2">
       <c r="A88" s="19">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -3466,9 +3444,9 @@
       <c r="E88" s="20"/>
       <c r="H88" s="20"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:8" ht="13.2">
       <c r="A89" s="19">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -3476,9 +3454,9 @@
       <c r="E89" s="20"/>
       <c r="H89" s="20"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:8" ht="13.2">
       <c r="A90" s="19">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -3486,9 +3464,9 @@
       <c r="E90" s="20"/>
       <c r="H90" s="20"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:8" ht="13.2">
       <c r="A91" s="19">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -3496,9 +3474,9 @@
       <c r="E91" s="20"/>
       <c r="H91" s="20"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:8" ht="13.2">
       <c r="A92" s="19">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -3506,9 +3484,9 @@
       <c r="E92" s="20"/>
       <c r="H92" s="20"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:8" ht="13.2">
       <c r="A93" s="19">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -3516,9 +3494,9 @@
       <c r="E93" s="20"/>
       <c r="H93" s="20"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:8" ht="13.2">
       <c r="A94" s="19">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -3526,9 +3504,9 @@
       <c r="E94" s="20"/>
       <c r="H94" s="20"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:8" ht="13.2">
       <c r="A95" s="19">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -3536,9 +3514,9 @@
       <c r="E95" s="20"/>
       <c r="H95" s="20"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:8" ht="13.2">
       <c r="A96" s="19">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -3546,9 +3524,9 @@
       <c r="E96" s="20"/>
       <c r="H96" s="20"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:8" ht="13.2">
       <c r="A97" s="19">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -3556,9 +3534,9 @@
       <c r="E97" s="20"/>
       <c r="H97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:8" ht="13.2">
       <c r="A98" s="19">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -3566,9 +3544,9 @@
       <c r="E98" s="20"/>
       <c r="H98" s="20"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:8" ht="13.2">
       <c r="A99" s="19">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -3576,9 +3554,9 @@
       <c r="E99" s="20"/>
       <c r="H99" s="20"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:8" ht="13.2">
       <c r="A100" s="19">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -3586,9 +3564,9 @@
       <c r="E100" s="20"/>
       <c r="H100" s="20"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:8" ht="13.2">
       <c r="A101" s="19">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -3596,9 +3574,9 @@
       <c r="E101" s="20"/>
       <c r="H101" s="20"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:8" ht="13.2">
       <c r="A102" s="19">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -3606,9 +3584,9 @@
       <c r="E102" s="20"/>
       <c r="H102" s="20"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:8" ht="13.2">
       <c r="A103" s="19">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -3616,9 +3594,9 @@
       <c r="E103" s="20"/>
       <c r="H103" s="20"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:8" ht="13.2">
       <c r="A104" s="19">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -3626,9 +3604,9 @@
       <c r="E104" s="20"/>
       <c r="H104" s="20"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:8" ht="13.2">
       <c r="A105" s="19">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -3636,9 +3614,9 @@
       <c r="E105" s="20"/>
       <c r="H105" s="20"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:8" ht="13.2">
       <c r="A106" s="19">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -3646,9 +3624,9 @@
       <c r="E106" s="20"/>
       <c r="H106" s="20"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:8" ht="13.2">
       <c r="A107" s="19">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -3656,9 +3634,9 @@
       <c r="E107" s="20"/>
       <c r="H107" s="20"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:8" ht="13.2">
       <c r="A108" s="19">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -3666,9 +3644,9 @@
       <c r="E108" s="20"/>
       <c r="H108" s="20"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:8" ht="13.2">
       <c r="A109" s="19">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
@@ -3676,9 +3654,9 @@
       <c r="E109" s="20"/>
       <c r="H109" s="20"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:8" ht="13.2">
       <c r="A110" s="19">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -3686,9 +3664,9 @@
       <c r="E110" s="20"/>
       <c r="H110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:8" ht="13.2">
       <c r="A111" s="19">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
@@ -3696,9 +3674,9 @@
       <c r="E111" s="20"/>
       <c r="H111" s="20"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:8" ht="13.2">
       <c r="A112" s="19">
-        <v>114.0</v>
+        <v>114</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
@@ -3706,9 +3684,9 @@
       <c r="E112" s="20"/>
       <c r="H112" s="20"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:8" ht="13.2">
       <c r="A113" s="19">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -3716,9 +3694,9 @@
       <c r="E113" s="20"/>
       <c r="H113" s="20"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:8" ht="13.2">
       <c r="A114" s="19">
-        <v>116.0</v>
+        <v>116</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -3726,9 +3704,9 @@
       <c r="E114" s="20"/>
       <c r="H114" s="20"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:8" ht="13.2">
       <c r="A115" s="19">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
@@ -3736,9 +3714,9 @@
       <c r="E115" s="20"/>
       <c r="H115" s="20"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:8" ht="13.2">
       <c r="A116" s="19">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -3746,9 +3724,9 @@
       <c r="E116" s="20"/>
       <c r="H116" s="20"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:8" ht="13.2">
       <c r="A117" s="19">
-        <v>119.0</v>
+        <v>119</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
@@ -3756,9 +3734,9 @@
       <c r="E117" s="20"/>
       <c r="H117" s="20"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:8" ht="13.2">
       <c r="A118" s="19">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -3766,9 +3744,9 @@
       <c r="E118" s="20"/>
       <c r="H118" s="20"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:8" ht="13.2">
       <c r="A119" s="19">
-        <v>121.0</v>
+        <v>121</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
@@ -3776,9 +3754,9 @@
       <c r="E119" s="20"/>
       <c r="H119" s="20"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:8" ht="13.2">
       <c r="A120" s="19">
-        <v>122.0</v>
+        <v>122</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -3786,9 +3764,9 @@
       <c r="E120" s="20"/>
       <c r="H120" s="20"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:8" ht="13.2">
       <c r="A121" s="19">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -3796,9 +3774,9 @@
       <c r="E121" s="20"/>
       <c r="H121" s="20"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:8" ht="13.2">
       <c r="A122" s="19">
-        <v>124.0</v>
+        <v>124</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -3806,9 +3784,9 @@
       <c r="E122" s="20"/>
       <c r="H122" s="20"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:8" ht="13.2">
       <c r="A123" s="19">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -3816,9 +3794,9 @@
       <c r="E123" s="20"/>
       <c r="H123" s="20"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:8" ht="13.2">
       <c r="A124" s="19">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -3826,9 +3804,9 @@
       <c r="E124" s="20"/>
       <c r="H124" s="20"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:8" ht="13.2">
       <c r="A125" s="19">
-        <v>127.0</v>
+        <v>127</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -3836,9 +3814,9 @@
       <c r="E125" s="20"/>
       <c r="H125" s="20"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:8" ht="13.2">
       <c r="A126" s="19">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
@@ -3846,9 +3824,9 @@
       <c r="E126" s="20"/>
       <c r="H126" s="20"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:8" ht="13.2">
       <c r="A127" s="19">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
@@ -3856,9 +3834,9 @@
       <c r="E127" s="20"/>
       <c r="H127" s="20"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:8" ht="13.2">
       <c r="A128" s="19">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
@@ -3866,9 +3844,9 @@
       <c r="E128" s="20"/>
       <c r="H128" s="20"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:8" ht="13.2">
       <c r="A129" s="19">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -3876,9 +3854,9 @@
       <c r="E129" s="20"/>
       <c r="H129" s="20"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:8" ht="13.2">
       <c r="A130" s="19">
-        <v>132.0</v>
+        <v>132</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -3886,9 +3864,9 @@
       <c r="E130" s="20"/>
       <c r="H130" s="20"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:8" ht="13.2">
       <c r="A131" s="19">
-        <v>133.0</v>
+        <v>133</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -3896,9 +3874,9 @@
       <c r="E131" s="20"/>
       <c r="H131" s="20"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:8" ht="13.2">
       <c r="A132" s="19">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -3906,9 +3884,9 @@
       <c r="E132" s="20"/>
       <c r="H132" s="20"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:8" ht="13.2">
       <c r="A133" s="19">
-        <v>135.0</v>
+        <v>135</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -3916,9 +3894,9 @@
       <c r="E133" s="20"/>
       <c r="H133" s="20"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:8" ht="13.2">
       <c r="A134" s="19">
-        <v>136.0</v>
+        <v>136</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -3926,9 +3904,9 @@
       <c r="E134" s="20"/>
       <c r="H134" s="20"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:8" ht="13.2">
       <c r="A135" s="19">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -3936,9 +3914,9 @@
       <c r="E135" s="20"/>
       <c r="H135" s="20"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:8" ht="13.2">
       <c r="A136" s="19">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -3946,9 +3924,9 @@
       <c r="E136" s="20"/>
       <c r="H136" s="20"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:8" ht="13.2">
       <c r="A137" s="19">
-        <v>139.0</v>
+        <v>139</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -3956,9 +3934,9 @@
       <c r="E137" s="20"/>
       <c r="H137" s="20"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:8" ht="13.2">
       <c r="A138" s="19">
-        <v>140.0</v>
+        <v>140</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -3966,9 +3944,9 @@
       <c r="E138" s="20"/>
       <c r="H138" s="20"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:8" ht="13.2">
       <c r="A139" s="19">
-        <v>141.0</v>
+        <v>141</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -3976,9 +3954,9 @@
       <c r="E139" s="20"/>
       <c r="H139" s="20"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:8" ht="13.2">
       <c r="A140" s="19">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -3986,9 +3964,9 @@
       <c r="E140" s="20"/>
       <c r="H140" s="20"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:8" ht="13.2">
       <c r="A141" s="19">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -3996,9 +3974,9 @@
       <c r="E141" s="20"/>
       <c r="H141" s="20"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:8" ht="13.2">
       <c r="A142" s="19">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -4006,9 +3984,9 @@
       <c r="E142" s="20"/>
       <c r="H142" s="20"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:8" ht="13.2">
       <c r="A143" s="19">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -4016,9 +3994,9 @@
       <c r="E143" s="20"/>
       <c r="H143" s="20"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:8" ht="13.2">
       <c r="A144" s="19">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -4026,9 +4004,9 @@
       <c r="E144" s="20"/>
       <c r="H144" s="20"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:8" ht="13.2">
       <c r="A145" s="19">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -4036,9 +4014,9 @@
       <c r="E145" s="20"/>
       <c r="H145" s="20"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:8" ht="13.2">
       <c r="A146" s="19">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -4046,9 +4024,9 @@
       <c r="E146" s="20"/>
       <c r="H146" s="20"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:8" ht="13.2">
       <c r="A147" s="19">
-        <v>149.0</v>
+        <v>149</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -4056,9 +4034,9 @@
       <c r="E147" s="20"/>
       <c r="H147" s="20"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:8" ht="13.2">
       <c r="A148" s="19">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -4066,9 +4044,9 @@
       <c r="E148" s="20"/>
       <c r="H148" s="20"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:8" ht="13.2">
       <c r="A149" s="19">
-        <v>151.0</v>
+        <v>151</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -4076,9 +4054,9 @@
       <c r="E149" s="20"/>
       <c r="H149" s="20"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:8" ht="13.2">
       <c r="A150" s="19">
-        <v>152.0</v>
+        <v>152</v>
       </c>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -4086,9 +4064,9 @@
       <c r="E150" s="20"/>
       <c r="H150" s="20"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:8" ht="13.2">
       <c r="A151" s="19">
-        <v>153.0</v>
+        <v>153</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -4096,9 +4074,9 @@
       <c r="E151" s="20"/>
       <c r="H151" s="20"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:8" ht="13.2">
       <c r="A152" s="19">
-        <v>154.0</v>
+        <v>154</v>
       </c>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -4108,1587 +4086,1588 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="H3"/>
-    <hyperlink r:id="rId3" ref="H4"/>
-    <hyperlink r:id="rId4" ref="H5"/>
-    <hyperlink r:id="rId5" ref="H6"/>
-    <hyperlink r:id="rId6" ref="H7"/>
-    <hyperlink r:id="rId7" ref="H8"/>
-    <hyperlink r:id="rId8" ref="H9"/>
-    <hyperlink r:id="rId9" ref="H10"/>
-    <hyperlink r:id="rId10" ref="H11"/>
-    <hyperlink r:id="rId11" ref="H12"/>
-    <hyperlink r:id="rId12" ref="H13"/>
-    <hyperlink r:id="rId13" ref="H14"/>
-    <hyperlink r:id="rId14" ref="H15"/>
-    <hyperlink r:id="rId15" ref="H16"/>
-    <hyperlink r:id="rId16" ref="H17"/>
-    <hyperlink r:id="rId17" ref="H18"/>
-    <hyperlink r:id="rId18" ref="H19"/>
-    <hyperlink r:id="rId19" ref="H20"/>
-    <hyperlink r:id="rId20" ref="H21"/>
-    <hyperlink r:id="rId21" ref="H22"/>
-    <hyperlink r:id="rId22" ref="H23"/>
-    <hyperlink r:id="rId23" ref="H24"/>
-    <hyperlink r:id="rId24" ref="H25"/>
-    <hyperlink r:id="rId25" ref="H26"/>
-    <hyperlink r:id="rId26" ref="H27"/>
-    <hyperlink r:id="rId27" ref="H28"/>
-    <hyperlink r:id="rId28" ref="H29"/>
-    <hyperlink r:id="rId29" ref="H30"/>
-    <hyperlink r:id="rId30" ref="H31"/>
-    <hyperlink r:id="rId31" ref="H32"/>
-    <hyperlink r:id="rId32" ref="H33"/>
-    <hyperlink r:id="rId33" ref="H34"/>
-    <hyperlink r:id="rId34" ref="H35"/>
-    <hyperlink r:id="rId35" ref="H36"/>
-    <hyperlink r:id="rId36" ref="H37"/>
-    <hyperlink r:id="rId37" ref="H38"/>
-    <hyperlink r:id="rId38" ref="H39"/>
-    <hyperlink r:id="rId39" ref="H40"/>
-    <hyperlink r:id="rId40" ref="H41"/>
-    <hyperlink r:id="rId41" ref="H42"/>
-    <hyperlink r:id="rId42" ref="H43"/>
-    <hyperlink r:id="rId43" ref="H44"/>
-    <hyperlink r:id="rId44" ref="H46"/>
-    <hyperlink r:id="rId45" ref="H47"/>
-    <hyperlink r:id="rId46" ref="H48"/>
-    <hyperlink r:id="rId47" ref="H49"/>
-    <hyperlink r:id="rId48" ref="H50"/>
-    <hyperlink r:id="rId49" ref="H51"/>
-    <hyperlink r:id="rId50" ref="H52"/>
-    <hyperlink r:id="rId51" ref="H53"/>
-    <hyperlink r:id="rId52" ref="H54"/>
-    <hyperlink r:id="rId53" ref="H55"/>
-    <hyperlink r:id="rId54" ref="H56"/>
-    <hyperlink r:id="rId55" ref="H57"/>
-    <hyperlink r:id="rId56" ref="H58"/>
-    <hyperlink r:id="rId57" ref="H59"/>
-    <hyperlink r:id="rId58" ref="H60"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H46" r:id="rId44"/>
+    <hyperlink ref="H47" r:id="rId45"/>
+    <hyperlink ref="H48" r:id="rId46"/>
+    <hyperlink ref="H49" r:id="rId47"/>
+    <hyperlink ref="H50" r:id="rId48"/>
+    <hyperlink ref="H51" r:id="rId49"/>
+    <hyperlink ref="H52" r:id="rId50"/>
+    <hyperlink ref="H53" r:id="rId51"/>
+    <hyperlink ref="H54" r:id="rId52"/>
+    <hyperlink ref="H55" r:id="rId53"/>
+    <hyperlink ref="H56" r:id="rId54"/>
+    <hyperlink ref="H57" r:id="rId55"/>
+    <hyperlink ref="H58" r:id="rId56"/>
+    <hyperlink ref="H59" r:id="rId57"/>
+    <hyperlink ref="H60" r:id="rId58"/>
   </hyperlinks>
-  <drawing r:id="rId59"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="33.86"/>
-    <col customWidth="1" min="5" max="5" width="16.43"/>
+    <col min="2" max="2" width="33.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="13.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="F1" s="16"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="13.2">
       <c r="A2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>music!B2</f>
         <v>Николай Яковлевич Мясковский</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="23">
+        <v>18452</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="23">
-        <v>18452.0</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:6" ht="13.2">
       <c r="A3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="20" t="str">
         <f>music!B22</f>
         <v>Дмитрий Дмитриевич Шостакович</v>
       </c>
       <c r="C3" s="24">
-        <v>2447.0</v>
+        <v>2447</v>
       </c>
       <c r="D3" s="24">
-        <v>27615.0</v>
+        <v>27615</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="13.2">
       <c r="A4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="20" t="str">
         <f>music!B37</f>
         <v>Илья Алексеевич Шатров</v>
       </c>
       <c r="C4" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="24">
+        <v>19116</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="24">
-        <v>19116.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="13.2">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="25">
+        <v>11290</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="25">
-        <v>11290.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:6" ht="13.2">
       <c r="A6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="20" t="str">
         <f>music!B39</f>
         <v>Алексей Сергеевич Турищев</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D6" s="24">
+        <v>22693</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D6" s="24">
-        <v>22693.0</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:6" ht="13.2">
       <c r="A7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="20" t="str">
         <f>music!B40</f>
         <v>Владимир Германович Богораз</v>
       </c>
       <c r="C7" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="24">
+        <v>13280</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D7" s="24">
-        <v>13280.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:6" ht="13.2">
       <c r="A8" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="20" t="str">
         <f>music!B41</f>
         <v>Василий Иванович Агапкин</v>
       </c>
       <c r="C8" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="25">
+        <v>23679</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="25">
-        <v>23679.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:6" ht="13.2">
       <c r="A9" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="24">
-        <v>1137.0</v>
+        <v>1137</v>
       </c>
       <c r="D9" s="24">
-        <v>33143.0</v>
+        <v>33143</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.2">
       <c r="A10" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="20" t="str">
         <f>music!B44</f>
-        <v>Самуил Яковлевич Покрасс </v>
+        <v xml:space="preserve">Самуил Яковлевич Покрасс </v>
       </c>
       <c r="C10" s="6">
-        <v>1897.0</v>
+        <v>1897</v>
       </c>
       <c r="D10" s="24">
-        <v>14411.0</v>
+        <v>14411</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.2">
       <c r="A11" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="20" t="str">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20">
         <f>music!B45</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="13.2">
       <c r="A12" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="20" t="str">
         <f>music!B46</f>
         <v>Виктор Аркадьевич Белый</v>
       </c>
       <c r="C12" s="24">
-        <v>1475.0</v>
+        <v>1475</v>
       </c>
       <c r="D12" s="24">
-        <v>30381.0</v>
+        <v>30381</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.2">
       <c r="A13" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="20" t="str">
         <f>music!B48</f>
         <v>Максимилиан Осеевич Штейнберг</v>
       </c>
       <c r="C13" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="24">
+        <v>17142</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="24">
-        <v>17142.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:6" ht="13.2">
       <c r="A14" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B14" s="20" t="str">
         <f>music!B50</f>
         <v>Александр Николаевич Вертинский</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="24">
+        <v>20961</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D14" s="24">
-        <v>20961.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="13.2">
+      <c r="A15" s="6">
+        <v>15</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="24">
+        <v>10291</v>
+      </c>
+      <c r="D15" s="24">
+        <v>32687</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C15" s="24">
-        <v>10291.0</v>
-      </c>
-      <c r="D15" s="24">
-        <v>32687.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="13.2">
       <c r="A16" s="7">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B16" s="20" t="str">
         <f>music!B52</f>
         <v>Евгений Григорьевич Мартынов</v>
       </c>
       <c r="C16" s="24">
-        <v>17675.0</v>
+        <v>17675</v>
       </c>
       <c r="D16" s="24">
-        <v>33119.0</v>
+        <v>33119</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="13.2">
       <c r="A17" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B17" s="20" t="str">
         <f>music!B53</f>
         <v>Валентин Сергеевич Левашов</v>
       </c>
       <c r="C17" s="24">
-        <v>5684.0</v>
+        <v>5684</v>
       </c>
       <c r="D17" s="24">
-        <v>34582.0</v>
+        <v>34582</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="13.2">
       <c r="A18" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="24">
-        <v>2659.0</v>
+        <v>2659</v>
       </c>
       <c r="D18" s="24">
-        <v>29191.0</v>
+        <v>29191</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="13.2">
+      <c r="A19" s="7">
+        <v>19</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="24">
+        <v>14474</v>
+      </c>
+      <c r="D19" s="24">
+        <v>36188</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7">
-        <v>19.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" s="24">
-        <v>14474.0</v>
-      </c>
-      <c r="D19" s="24">
-        <v>36188.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="20">
+    <row r="20" spans="1:5" ht="13.2">
       <c r="A20" s="6">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="24">
-        <v>14812.0</v>
+        <v>14812</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="13.2">
+      <c r="A21" s="7">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" s="25">
+        <v>7631</v>
+      </c>
+      <c r="D21" s="24">
+        <v>32745</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" s="25">
-        <v>7631.0</v>
-      </c>
-      <c r="D21" s="24">
-        <v>32745.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="13.2">
       <c r="A22" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B22" s="20" t="str">
         <f>music!B3</f>
         <v>Анатолий Константинович Лядов</v>
       </c>
       <c r="C22" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="24">
+        <v>5310</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="24">
-        <v>5310.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:5" ht="13.2">
       <c r="A23" s="6">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="25">
-        <v>5829.0</v>
+        <v>5829</v>
       </c>
       <c r="D23" s="24">
-        <v>35801.0</v>
+        <v>35801</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="13.2">
       <c r="A24" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="24">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D24" s="24">
-        <v>20295.0</v>
+        <v>20295</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="13.2">
       <c r="A25" s="7">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" s="24">
+        <v>16991</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D25" s="24">
-        <v>16991.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:5" ht="13.2">
       <c r="A26" s="6">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B26" s="20" t="str">
         <f>music!B60</f>
         <v>Марк Григорьевич Фрадкин</v>
       </c>
       <c r="C26" s="24">
-        <v>5225.0</v>
+        <v>5225</v>
       </c>
       <c r="D26" s="24">
-        <v>32967.0</v>
+        <v>32967</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="13.2">
       <c r="A27" s="6">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B27" s="20" t="str">
         <f>music!B12</f>
         <v>Константин Яковлевич Листов</v>
       </c>
       <c r="C27" s="24">
-        <v>263.0</v>
+        <v>263</v>
       </c>
       <c r="D27" s="24">
-        <v>30565.0</v>
+        <v>30565</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="13.2">
       <c r="A28" s="7">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="24">
-        <v>9133.0</v>
+        <v>9133</v>
       </c>
       <c r="D28" s="24">
-        <v>35311.0</v>
+        <v>35311</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="13.2">
       <c r="A29" s="6">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="24">
-        <v>10906.0</v>
+        <v>10906</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="13.2">
       <c r="A30" s="6">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="D30" s="24">
+        <v>24447</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D30" s="24">
-        <v>24447.0</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:5" ht="13.2">
       <c r="A31" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="24">
-        <v>3006.0</v>
+        <v>3006</v>
       </c>
       <c r="D31" s="24">
-        <v>25794.0</v>
+        <v>25794</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="13.2">
       <c r="A32" s="6">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="24">
-        <v>16667.0</v>
+        <v>16667</v>
       </c>
       <c r="D32" s="24">
-        <v>35111.0</v>
+        <v>35111</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="33" ht="35.25" customHeight="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="35.25" customHeight="1">
       <c r="A33" s="7">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="24">
-        <v>7720.0</v>
+        <v>7720</v>
       </c>
       <c r="D33" s="24">
-        <v>41308.0</v>
+        <v>41308</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="13.2">
       <c r="A34" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C34" s="24">
-        <v>4897.0</v>
+        <v>4897</v>
       </c>
       <c r="D34" s="24">
-        <v>39308.0</v>
+        <v>39308</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="13.2">
       <c r="A35" s="6">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C35" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35" s="24">
+        <v>30949</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D35" s="24">
-        <v>30949.0</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:5" ht="13.2">
       <c r="A36" s="7">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C36" s="24">
-        <v>10857.0</v>
+        <v>10857</v>
       </c>
       <c r="D36" s="24">
-        <v>44641.0</v>
+        <v>44641</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="13.2">
       <c r="A37" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>132</v>
       </c>
       <c r="C37" s="24">
-        <v>18903.0</v>
+        <v>18903</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="13.2">
       <c r="A38" s="6">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="13.2">
       <c r="A39" s="6">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="13.2">
       <c r="A40" s="7">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="13.2">
       <c r="A41" s="6">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="13.2">
       <c r="A42" s="6">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="13.2">
       <c r="A43" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="13.2">
       <c r="A44" s="6">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="13.2">
       <c r="A45" s="7">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" ht="13.2">
       <c r="A46" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" ht="13.2">
       <c r="A47" s="6">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" ht="13.2">
       <c r="A48" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" ht="13.2">
       <c r="A49" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="13.2">
       <c r="A50" s="6">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" ht="13.2">
       <c r="A51" s="6">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="13.2">
       <c r="A52" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="13.2">
       <c r="A53" s="6">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="13.2">
       <c r="A54" s="6">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="13.2">
       <c r="A55" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
       <c r="E55" s="20"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="13.2">
       <c r="A56" s="6">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="13.2">
       <c r="A57" s="7">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" ht="13.2">
       <c r="A58" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" ht="13.2">
       <c r="A59" s="6">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="13.2">
       <c r="A60" s="7">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" ht="13.2">
       <c r="A61" s="7">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" ht="13.2">
       <c r="A62" s="6">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="13.2">
       <c r="A63" s="6">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="13.2">
       <c r="A64" s="7">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" ht="13.2">
       <c r="A65" s="6">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" ht="13.2">
       <c r="A66" s="6">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" ht="13.2">
       <c r="A67" s="7">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" ht="13.2">
       <c r="A68" s="6">
-        <v>68.0</v>
-      </c>
-      <c r="B68" s="20" t="str">
+        <v>68</v>
+      </c>
+      <c r="B68" s="20">
         <f>music!B104</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" ht="13.2">
       <c r="A69" s="7">
-        <v>69.0</v>
-      </c>
-      <c r="B69" s="20" t="str">
+        <v>69</v>
+      </c>
+      <c r="B69" s="20">
         <f>music!B105</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" ht="13.2">
       <c r="A70" s="7">
-        <v>70.0</v>
-      </c>
-      <c r="B70" s="20" t="str">
+        <v>70</v>
+      </c>
+      <c r="B70" s="20">
         <f>music!B106</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" ht="13.2">
       <c r="A71" s="6">
-        <v>71.0</v>
-      </c>
-      <c r="B71" s="20" t="str">
+        <v>71</v>
+      </c>
+      <c r="B71" s="20">
         <f>music!B107</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" ht="13.2">
       <c r="A72" s="7">
-        <v>72.0</v>
-      </c>
-      <c r="B72" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="B72" s="20">
         <f>music!B108</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" ht="13.2">
       <c r="A73" s="7">
-        <v>73.0</v>
-      </c>
-      <c r="B73" s="20" t="str">
+        <v>73</v>
+      </c>
+      <c r="B73" s="20">
         <f>music!B109</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" ht="13.2">
       <c r="A74" s="6">
-        <v>74.0</v>
-      </c>
-      <c r="B74" s="20" t="str">
+        <v>74</v>
+      </c>
+      <c r="B74" s="20">
         <f>music!B110</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" ht="13.2">
       <c r="A75" s="6">
-        <v>75.0</v>
-      </c>
-      <c r="B75" s="20" t="str">
+        <v>75</v>
+      </c>
+      <c r="B75" s="20">
         <f>music!B111</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" ht="13.2">
       <c r="A76" s="7">
-        <v>76.0</v>
-      </c>
-      <c r="B76" s="20" t="str">
+        <v>76</v>
+      </c>
+      <c r="B76" s="20">
         <f>music!B112</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" ht="13.2">
       <c r="A77" s="6">
-        <v>77.0</v>
-      </c>
-      <c r="B77" s="20" t="str">
+        <v>77</v>
+      </c>
+      <c r="B77" s="20">
         <f>music!B113</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" ht="13.2">
       <c r="A78" s="6">
-        <v>78.0</v>
-      </c>
-      <c r="B78" s="20" t="str">
+        <v>78</v>
+      </c>
+      <c r="B78" s="20">
         <f>music!B114</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" ht="13.2">
       <c r="A79" s="7">
-        <v>79.0</v>
-      </c>
-      <c r="B79" s="20" t="str">
+        <v>79</v>
+      </c>
+      <c r="B79" s="20">
         <f>music!B115</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" ht="13.2">
       <c r="A80" s="6">
-        <v>80.0</v>
-      </c>
-      <c r="B80" s="20" t="str">
+        <v>80</v>
+      </c>
+      <c r="B80" s="20">
         <f>music!B116</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:5" ht="13.2">
       <c r="A81" s="7">
-        <v>81.0</v>
-      </c>
-      <c r="B81" s="20" t="str">
+        <v>81</v>
+      </c>
+      <c r="B81" s="20">
         <f>music!B117</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" ht="13.2">
       <c r="A82" s="7">
-        <v>82.0</v>
-      </c>
-      <c r="B82" s="20" t="str">
+        <v>82</v>
+      </c>
+      <c r="B82" s="20">
         <f>music!B118</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" ht="13.2">
       <c r="A83" s="6">
-        <v>83.0</v>
-      </c>
-      <c r="B83" s="20" t="str">
+        <v>83</v>
+      </c>
+      <c r="B83" s="20">
         <f>music!B119</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:5" ht="13.2">
       <c r="A84" s="7">
-        <v>84.0</v>
-      </c>
-      <c r="B84" s="20" t="str">
+        <v>84</v>
+      </c>
+      <c r="B84" s="20">
         <f>music!B120</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:5" ht="13.2">
       <c r="A85" s="7">
-        <v>85.0</v>
-      </c>
-      <c r="B85" s="20" t="str">
+        <v>85</v>
+      </c>
+      <c r="B85" s="20">
         <f>music!B121</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" ht="13.2">
       <c r="A86" s="6">
-        <v>86.0</v>
-      </c>
-      <c r="B86" s="20" t="str">
+        <v>86</v>
+      </c>
+      <c r="B86" s="20">
         <f>music!B122</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" ht="13.2">
       <c r="A87" s="6">
-        <v>87.0</v>
-      </c>
-      <c r="B87" s="20" t="str">
+        <v>87</v>
+      </c>
+      <c r="B87" s="20">
         <f>music!B123</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:5" ht="13.2">
       <c r="A88" s="7">
-        <v>88.0</v>
-      </c>
-      <c r="B88" s="20" t="str">
+        <v>88</v>
+      </c>
+      <c r="B88" s="20">
         <f>music!B124</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" ht="13.2">
       <c r="A89" s="6">
-        <v>89.0</v>
-      </c>
-      <c r="B89" s="20" t="str">
+        <v>89</v>
+      </c>
+      <c r="B89" s="20">
         <f>music!B125</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:5" ht="13.2">
       <c r="A90" s="6">
-        <v>90.0</v>
-      </c>
-      <c r="B90" s="20" t="str">
+        <v>90</v>
+      </c>
+      <c r="B90" s="20">
         <f>music!B126</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" ht="13.2">
       <c r="A91" s="7">
-        <v>91.0</v>
-      </c>
-      <c r="B91" s="20" t="str">
+        <v>91</v>
+      </c>
+      <c r="B91" s="20">
         <f>music!B127</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" ht="13.2">
       <c r="A92" s="6">
-        <v>92.0</v>
-      </c>
-      <c r="B92" s="20" t="str">
+        <v>92</v>
+      </c>
+      <c r="B92" s="20">
         <f>music!B128</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" ht="13.2">
       <c r="A93" s="7">
-        <v>93.0</v>
-      </c>
-      <c r="B93" s="20" t="str">
+        <v>93</v>
+      </c>
+      <c r="B93" s="20">
         <f>music!B129</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" ht="13.2">
       <c r="A94" s="7">
-        <v>94.0</v>
-      </c>
-      <c r="B94" s="20" t="str">
+        <v>94</v>
+      </c>
+      <c r="B94" s="20">
         <f>music!B130</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" ht="13.2">
       <c r="A95" s="6">
-        <v>95.0</v>
-      </c>
-      <c r="B95" s="20" t="str">
+        <v>95</v>
+      </c>
+      <c r="B95" s="20">
         <f>music!B131</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" ht="13.2">
       <c r="A96" s="7">
-        <v>96.0</v>
-      </c>
-      <c r="B96" s="20" t="str">
+        <v>96</v>
+      </c>
+      <c r="B96" s="20">
         <f>music!B132</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" ht="13.2">
       <c r="A97" s="7">
-        <v>97.0</v>
-      </c>
-      <c r="B97" s="20" t="str">
+        <v>97</v>
+      </c>
+      <c r="B97" s="20">
         <f>music!B133</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" ht="13.2">
       <c r="A98" s="6">
-        <v>98.0</v>
-      </c>
-      <c r="B98" s="20" t="str">
+        <v>98</v>
+      </c>
+      <c r="B98" s="20">
         <f>music!B134</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" ht="13.2">
       <c r="A99" s="6">
-        <v>99.0</v>
-      </c>
-      <c r="B99" s="20" t="str">
+        <v>99</v>
+      </c>
+      <c r="B99" s="20">
         <f>music!B135</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" ht="13.2">
       <c r="A100" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="B100" s="20" t="str">
+        <v>100</v>
+      </c>
+      <c r="B100" s="20">
         <f>music!B136</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" ht="13.2">
       <c r="A101" s="6">
-        <v>101.0</v>
-      </c>
-      <c r="B101" s="20" t="str">
+        <v>101</v>
+      </c>
+      <c r="B101" s="20">
         <f>music!B137</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" ht="13.2">
       <c r="A102" s="6">
-        <v>102.0</v>
-      </c>
-      <c r="B102" s="20" t="str">
+        <v>102</v>
+      </c>
+      <c r="B102" s="20">
         <f>music!B138</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" ht="13.2">
       <c r="A103" s="7">
-        <v>103.0</v>
-      </c>
-      <c r="B103" s="20" t="str">
+        <v>103</v>
+      </c>
+      <c r="B103" s="20">
         <f>music!B139</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" ht="13.2">
       <c r="A104" s="6">
-        <v>104.0</v>
-      </c>
-      <c r="B104" s="20" t="str">
+        <v>104</v>
+      </c>
+      <c r="B104" s="20">
         <f>music!B140</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" ht="13.2">
       <c r="A105" s="7">
-        <v>105.0</v>
-      </c>
-      <c r="B105" s="20" t="str">
+        <v>105</v>
+      </c>
+      <c r="B105" s="20">
         <f>music!B141</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" ht="13.2">
       <c r="A106" s="7">
-        <v>106.0</v>
-      </c>
-      <c r="B106" s="20" t="str">
+        <v>106</v>
+      </c>
+      <c r="B106" s="20">
         <f>music!B142</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:5" ht="13.2">
       <c r="A107" s="6">
-        <v>107.0</v>
-      </c>
-      <c r="B107" s="20" t="str">
+        <v>107</v>
+      </c>
+      <c r="B107" s="20">
         <f>music!B143</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C107" s="20"/>
       <c r="D107" s="20"/>
       <c r="E107" s="20"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:5" ht="13.2">
       <c r="A108" s="7">
-        <v>108.0</v>
-      </c>
-      <c r="B108" s="20" t="str">
+        <v>108</v>
+      </c>
+      <c r="B108" s="20">
         <f>music!B144</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" ht="13.2">
       <c r="A109" s="7">
-        <v>109.0</v>
-      </c>
-      <c r="B109" s="20" t="str">
+        <v>109</v>
+      </c>
+      <c r="B109" s="20">
         <f>music!B145</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C109" s="20"/>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" ht="13.2">
       <c r="A110" s="20"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:5" ht="13.2">
       <c r="A111" s="20"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
       <c r="D111" s="20"/>
       <c r="E111" s="20"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" ht="13.2">
       <c r="A112" s="20"/>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" ht="13.2">
       <c r="A113" s="20"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:5" ht="13.2">
       <c r="A114" s="20"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" ht="13.2">
       <c r="A115" s="20"/>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:5" ht="13.2">
       <c r="A116" s="20"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:5" ht="13.2">
       <c r="A117" s="20"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:5" ht="13.2">
       <c r="A118" s="20"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" ht="13.2">
       <c r="A119" s="20"/>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" ht="13.2">
       <c r="A120" s="20"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
       <c r="D120" s="20"/>
       <c r="E120" s="20"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:5" ht="13.2">
       <c r="A121" s="20"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
       <c r="D121" s="20"/>
       <c r="E121" s="20"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:5" ht="13.2">
       <c r="A122" s="20"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:5" ht="13.2">
       <c r="A123" s="20"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:5" ht="13.2">
       <c r="A124" s="20"/>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
@@ -5696,488 +5675,489 @@
       <c r="E124" s="20"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.43"/>
-    <col customWidth="1" min="2" max="2" width="46.14"/>
-    <col customWidth="1" min="3" max="3" width="20.14"/>
-    <col customWidth="1" min="4" max="4" width="23.86"/>
-    <col customWidth="1" min="5" max="5" width="56.57"/>
+    <col min="1" max="1" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="46.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="5" max="5" width="56.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5">
       <c r="A1" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="27" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="29">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="C2" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="D2" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="E2" s="32" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29">
+        <v>5</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="29">
-        <v>5.0</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="D3" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="E3" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="E3" s="32" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="29">
+        <v>9</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="D4" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="E4" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="E4" s="32" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="29">
+        <v>21</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="29">
-        <v>21.0</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="D5" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="E5" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="E5" s="33" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="29">
+        <v>37</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29">
-        <v>37.0</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="C6" s="30" t="s">
         <v>292</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>293</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="33" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="29">
+        <v>38</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="29">
-        <v>38.0</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="D7" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="E7" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="E7" s="33" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="29"/>
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>
       <c r="E8" s="33"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9" s="29">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B9" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="D9" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="E9" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="33" t="s">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="29">
+        <v>45</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29">
-        <v>45.0</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>304</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="33" t="s">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="29">
+        <v>46</v>
+      </c>
+      <c r="B11" s="29" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29">
-        <v>46.0</v>
-      </c>
-      <c r="B11" s="29" t="s">
+      <c r="C11" s="30" t="s">
         <v>307</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>308</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="29">
+        <v>48</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29">
-        <v>48.0</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="C12" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="E12" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="E12" s="33" t="s">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="29">
+        <v>56</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29">
-        <v>56.0</v>
-      </c>
-      <c r="B13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>314</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>315</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="29">
+        <v>58</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29">
-        <v>58.0</v>
-      </c>
-      <c r="B14" s="29" t="s">
+      <c r="C14" s="30" t="s">
         <v>317</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>318</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="29">
+        <v>69</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29">
-        <v>69.0</v>
-      </c>
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="E15" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="E15" s="33" t="s">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="29">
+        <v>107</v>
+      </c>
+      <c r="B16" s="29" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29">
-        <v>107.0</v>
-      </c>
-      <c r="B16" s="29" t="s">
+      <c r="C16" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="E16" s="33" t="s">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="29">
+        <v>111</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="29">
-        <v>111.0</v>
-      </c>
-      <c r="B17" s="29" t="s">
+      <c r="C17" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="D17" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="E17" s="33" t="s">
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="29">
+        <v>112</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29">
-        <v>112.0</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="E18" s="33" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="29">
+        <v>120</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29">
-        <v>120.0</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="C19" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="D19" s="31" t="s">
         <v>337</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="E19" s="33" t="s">
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="29">
+        <v>126</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29">
-        <v>126.0</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>340</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="D20" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="E20" s="33" t="s">
         <v>342</v>
       </c>
-      <c r="E20" s="33" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="29">
+        <v>134</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29">
-        <v>134.0</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>344</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>345</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="E21" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="E21" s="33" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="29">
+        <v>142</v>
+      </c>
+      <c r="B22" s="29" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29">
-        <v>142.0</v>
-      </c>
-      <c r="B22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>348</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>349</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="33" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="29">
+        <v>143</v>
+      </c>
+      <c r="B23" s="29" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29">
-        <v>143.0</v>
-      </c>
-      <c r="B23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>351</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>352</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="29">
+        <v>160</v>
+      </c>
+      <c r="B24" s="29" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29">
-        <v>160.0</v>
-      </c>
-      <c r="B24" s="29" t="s">
+      <c r="C24" s="30" t="s">
         <v>354</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>355</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="29">
+        <v>163</v>
+      </c>
+      <c r="B25" s="29" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="29">
-        <v>163.0</v>
-      </c>
-      <c r="B25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>357</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>358</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="33" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="29">
+        <v>165</v>
+      </c>
+      <c r="B26" s="34" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29">
-        <v>165.0</v>
-      </c>
-      <c r="B26" s="34" t="s">
+      <c r="C26" s="30" t="s">
         <v>360</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>361</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="33" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="29">
+        <v>167</v>
+      </c>
+      <c r="B27" s="29" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29">
-        <v>167.0</v>
-      </c>
-      <c r="B27" s="29" t="s">
+      <c r="C27" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="D27" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="E27" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="E27" s="33" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="29">
+        <v>192</v>
+      </c>
+      <c r="B28" s="29" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29">
-        <v>192.0</v>
-      </c>
-      <c r="B28" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>367</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>368</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="33" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="29">
+        <v>221</v>
+      </c>
+      <c r="B29" s="29" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="29">
-        <v>221.0</v>
-      </c>
-      <c r="B29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="D29" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="E29" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="E29" s="33" t="s">
-        <v>373</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>